--- a/06_Office_Related/01_NSO_work/06_SL_to_PIVOT_to_Compare_with_WP/TN WP 2026-27/SL 2.0/Salem.xlsx
+++ b/06_Office_Related/01_NSO_work/06_SL_to_PIVOT_to_Compare_with_WP/TN WP 2026-27/SL 2.0/Salem.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\TN\TN_2026-27\02 Sample List - TN 2026-27\2.0\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Grv\Grv\05 GIT\01_masterRepo\06_Office_Related\01_NSO_work\06_SL_to_PIVOT_to_Compare_with_WP\TN WP 2026-27\SL 2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F322681D-4C00-4054-B5E4-5BC94869D760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4479248-8A5F-468E-9415-D294DD2D2E7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="198">
   <si>
     <t>State Sample</t>
   </si>
@@ -259,9 +259,6 @@
     <t>Total = 154</t>
   </si>
   <si>
-    <t>PADDY--K</t>
-  </si>
-  <si>
     <t>JOWAR -(K)</t>
   </si>
   <si>
@@ -613,7 +610,16 @@
     <t>@ A Group # B Group Villages</t>
   </si>
   <si>
-    <t>48</t>
+    <t>Gingelly (R)</t>
+  </si>
+  <si>
+    <t>Adiyanur</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>Pethanayakkan palayam</t>
   </si>
 </sst>
 </file>
@@ -709,7 +715,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -866,6 +872,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -873,7 +894,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -946,9 +967,6 @@
     <xf numFmtId="1" fontId="5" fillId="2" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="5" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1033,14 +1051,14 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="1" fontId="5" fillId="2" borderId="6" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1053,7 +1071,19 @@
     <xf numFmtId="49" fontId="5" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1092,12 +1122,6 @@
     <xf numFmtId="49" fontId="5" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1128,14 +1152,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1453,109 +1480,109 @@
     <col min="4" max="9" width="8.6640625" style="2" customWidth="1"/>
     <col min="10" max="10" width="9.5546875" style="2" customWidth="1"/>
     <col min="11" max="11" width="14.109375" style="2" customWidth="1"/>
-    <col min="12" max="12" width="25" style="35" customWidth="1"/>
+    <col min="12" max="12" width="25" style="34" customWidth="1"/>
     <col min="13" max="16384" width="20.6640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="83" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
-      <c r="E1" s="82"/>
-      <c r="F1" s="82"/>
-      <c r="G1" s="82"/>
-      <c r="H1" s="82"/>
-      <c r="I1" s="82"/>
-      <c r="J1" s="82"/>
-      <c r="K1" s="82"/>
-      <c r="L1" s="59"/>
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="83"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="83"/>
+      <c r="L1" s="57"/>
     </row>
     <row r="2" spans="1:12" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="82" t="s">
+      <c r="A2" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="82"/>
-      <c r="C2" s="82"/>
-      <c r="D2" s="82"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="82"/>
-      <c r="G2" s="82"/>
-      <c r="H2" s="82"/>
-      <c r="I2" s="82"/>
-      <c r="J2" s="82"/>
-      <c r="K2" s="82"/>
-      <c r="L2" s="59"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
+      <c r="H2" s="83"/>
+      <c r="I2" s="83"/>
+      <c r="J2" s="83"/>
+      <c r="K2" s="83"/>
+      <c r="L2" s="57"/>
     </row>
     <row r="3" spans="1:12" s="5" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="60" t="s">
+      <c r="A3" s="58" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="60"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60" t="s">
+      <c r="B3" s="58"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="I3" s="60"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="58"/>
-      <c r="L3" s="59"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="59"/>
+      <c r="L3" s="57"/>
     </row>
     <row r="4" spans="1:12" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="58"/>
-      <c r="B4" s="58"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60" t="s">
+      <c r="A4" s="59"/>
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="60"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="87" t="s">
-        <v>178</v>
-      </c>
-      <c r="K4" s="87"/>
-      <c r="L4" s="87"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="88" t="s">
+        <v>177</v>
+      </c>
+      <c r="K4" s="88"/>
+      <c r="L4" s="88"/>
     </row>
     <row r="5" spans="1:12" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="83" t="s">
+      <c r="A5" s="84" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="88" t="s">
+      <c r="B5" s="89" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="84" t="s">
+      <c r="C5" s="85" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="85"/>
-      <c r="E5" s="86"/>
-      <c r="F5" s="81" t="s">
+      <c r="D5" s="86"/>
+      <c r="E5" s="87"/>
+      <c r="F5" s="82" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="81"/>
-      <c r="H5" s="81" t="s">
+      <c r="G5" s="82"/>
+      <c r="H5" s="82" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="81"/>
-      <c r="J5" s="81" t="s">
+      <c r="I5" s="82"/>
+      <c r="J5" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="K5" s="81"/>
-      <c r="L5" s="81" t="s">
+      <c r="K5" s="82"/>
+      <c r="L5" s="82" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="83"/>
-      <c r="B6" s="89"/>
+      <c r="A6" s="84"/>
+      <c r="B6" s="90"/>
       <c r="C6" s="4" t="s">
         <v>7</v>
       </c>
@@ -1583,7 +1610,7 @@
       <c r="K6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="L6" s="81"/>
+      <c r="L6" s="82"/>
     </row>
     <row r="7" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
@@ -1605,7 +1632,7 @@
         <v>3</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H7" s="4">
         <v>2</v>
@@ -1614,9 +1641,9 @@
         <v>0</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="K7" s="52">
+        <v>176</v>
+      </c>
+      <c r="K7" s="51">
         <v>0</v>
       </c>
       <c r="L7" s="4">
@@ -1642,7 +1669,7 @@
       <c r="F8" s="4">
         <v>0</v>
       </c>
-      <c r="G8" s="29" t="s">
+      <c r="G8" s="28" t="s">
         <v>71</v>
       </c>
       <c r="H8" s="4">
@@ -1652,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K8" s="21">
         <v>0</v>
@@ -1680,7 +1707,7 @@
       <c r="F9" s="4">
         <v>1</v>
       </c>
-      <c r="G9" s="29" t="s">
+      <c r="G9" s="28" t="s">
         <v>37</v>
       </c>
       <c r="H9" s="4">
@@ -1690,7 +1717,7 @@
         <v>1</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K9" s="4">
         <v>3</v>
@@ -1716,9 +1743,9 @@
         <v>2</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="G10" s="29" t="s">
+        <v>167</v>
+      </c>
+      <c r="G10" s="28" t="s">
         <v>38</v>
       </c>
       <c r="H10" s="4">
@@ -1754,9 +1781,9 @@
         <v>0</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="G11" s="29" t="s">
+        <v>168</v>
+      </c>
+      <c r="G11" s="28" t="s">
         <v>36</v>
       </c>
       <c r="H11" s="4">
@@ -1794,7 +1821,7 @@
       <c r="F12" s="4">
         <v>1</v>
       </c>
-      <c r="G12" s="29" t="s">
+      <c r="G12" s="28" t="s">
         <v>36</v>
       </c>
       <c r="H12" s="4">
@@ -1807,7 +1834,7 @@
         <v>52</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="L12" s="3">
         <v>7</v>
@@ -1832,7 +1859,7 @@
       <c r="F13" s="4">
         <v>2</v>
       </c>
-      <c r="G13" s="29" t="s">
+      <c r="G13" s="28" t="s">
         <v>37</v>
       </c>
       <c r="H13" s="4">
@@ -1841,10 +1868,10 @@
       <c r="I13" s="4">
         <v>1</v>
       </c>
-      <c r="J13" s="28" t="s">
+      <c r="J13" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="K13" s="29" t="s">
+      <c r="K13" s="28" t="s">
         <v>75</v>
       </c>
       <c r="L13" s="3">
@@ -1870,8 +1897,8 @@
       <c r="F14" s="4">
         <v>1</v>
       </c>
-      <c r="G14" s="29" t="s">
-        <v>172</v>
+      <c r="G14" s="28" t="s">
+        <v>171</v>
       </c>
       <c r="H14" s="4">
         <v>4</v>
@@ -1880,7 +1907,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K14" s="4">
         <v>0</v>
@@ -1908,7 +1935,7 @@
       <c r="F15" s="4">
         <v>1</v>
       </c>
-      <c r="G15" s="29" t="s">
+      <c r="G15" s="28" t="s">
         <v>72</v>
       </c>
       <c r="H15" s="4">
@@ -1946,7 +1973,7 @@
       <c r="F16" s="4">
         <v>1</v>
       </c>
-      <c r="G16" s="29" t="s">
+      <c r="G16" s="28" t="s">
         <v>71</v>
       </c>
       <c r="H16" s="4">
@@ -1984,7 +2011,7 @@
       <c r="F17" s="4">
         <v>0</v>
       </c>
-      <c r="G17" s="29" t="s">
+      <c r="G17" s="28" t="s">
         <v>38</v>
       </c>
       <c r="H17" s="4">
@@ -1994,7 +2021,7 @@
         <v>0</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K17" s="4">
         <v>0</v>
@@ -2022,7 +2049,7 @@
       <c r="F18" s="4">
         <v>0</v>
       </c>
-      <c r="G18" s="29" t="s">
+      <c r="G18" s="28" t="s">
         <v>72</v>
       </c>
       <c r="H18" s="4">
@@ -2032,7 +2059,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K18" s="4">
         <v>0</v>
@@ -2060,7 +2087,7 @@
       <c r="F19" s="4">
         <v>1</v>
       </c>
-      <c r="G19" s="29" t="s">
+      <c r="G19" s="28" t="s">
         <v>73</v>
       </c>
       <c r="H19" s="4">
@@ -2070,7 +2097,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K19" s="4">
         <v>0</v>
@@ -2098,7 +2125,7 @@
       <c r="F20" s="4">
         <v>1</v>
       </c>
-      <c r="G20" s="29" t="s">
+      <c r="G20" s="28" t="s">
         <v>72</v>
       </c>
       <c r="H20" s="4">
@@ -2113,7 +2140,7 @@
       <c r="K20" s="4">
         <v>0</v>
       </c>
-      <c r="L20" s="36">
+      <c r="L20" s="35">
         <v>6</v>
       </c>
     </row>
@@ -2136,7 +2163,7 @@
       <c r="F21" s="4">
         <v>0</v>
       </c>
-      <c r="G21" s="29" t="s">
+      <c r="G21" s="28" t="s">
         <v>72</v>
       </c>
       <c r="H21" s="4">
@@ -2146,7 +2173,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K21" s="4">
         <v>0</v>
@@ -2163,13 +2190,13 @@
         <v>70</v>
       </c>
       <c r="C22" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D22" s="3">
         <v>3</v>
       </c>
       <c r="E22" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" s="4">
         <v>0</v>
@@ -2181,7 +2208,7 @@
         <v>3</v>
       </c>
       <c r="I22" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22" s="4">
         <v>0</v>
@@ -2189,7 +2216,7 @@
       <c r="K22" s="4">
         <v>0</v>
       </c>
-      <c r="L22" s="36">
+      <c r="L22" s="35">
         <v>3</v>
       </c>
     </row>
@@ -2198,7 +2225,7 @@
         <v>17</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C23" s="3">
         <v>14</v>
@@ -2222,10 +2249,10 @@
         <v>3</v>
       </c>
       <c r="J23" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="K23" s="4" t="s">
         <v>183</v>
-      </c>
-      <c r="K23" s="4" t="s">
-        <v>184</v>
       </c>
       <c r="L23" s="3">
         <v>14</v>
@@ -2260,7 +2287,7 @@
         <v>0</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K24" s="4">
         <v>0</v>
@@ -2270,10 +2297,10 @@
       </c>
     </row>
     <row r="27" spans="1:12" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J27" s="80" t="s">
+      <c r="J27" s="81" t="s">
         <v>76</v>
       </c>
-      <c r="K27" s="80"/>
+      <c r="K27" s="81"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -2297,12 +2324,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AC48"/>
+  <dimension ref="A1:AE48"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.33203125" style="54" customWidth="1"/>
-    <col min="2" max="2" width="27.21875" style="39" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5" style="31" customWidth="1"/>
+    <col min="1" max="1" width="21.33203125" style="53" customWidth="1"/>
+    <col min="2" max="2" width="21.33203125" style="38" customWidth="1"/>
+    <col min="3" max="3" width="4.88671875" style="30" customWidth="1"/>
     <col min="4" max="4" width="4.44140625" style="8" customWidth="1"/>
     <col min="5" max="5" width="5.6640625" style="8" customWidth="1"/>
     <col min="6" max="6" width="5.88671875" style="8" customWidth="1"/>
@@ -2310,1699 +2337,1712 @@
     <col min="8" max="8" width="6.44140625" style="8" customWidth="1"/>
     <col min="9" max="9" width="5" style="8" customWidth="1"/>
     <col min="10" max="10" width="5.109375" style="8" customWidth="1"/>
-    <col min="11" max="11" width="6.6640625" style="8" customWidth="1"/>
+    <col min="11" max="11" width="5.33203125" style="8" customWidth="1"/>
     <col min="12" max="12" width="6" style="8" customWidth="1"/>
     <col min="13" max="13" width="5.33203125" style="8" customWidth="1"/>
     <col min="14" max="14" width="6.44140625" style="8" customWidth="1"/>
-    <col min="15" max="15" width="6.21875" style="8" customWidth="1"/>
-    <col min="16" max="16" width="9.109375" style="8" customWidth="1"/>
+    <col min="15" max="15" width="3.5546875" style="8" customWidth="1"/>
+    <col min="16" max="16" width="5.6640625" style="8" customWidth="1"/>
     <col min="17" max="17" width="6.109375" style="8" customWidth="1"/>
-    <col min="18" max="19" width="6" style="8" customWidth="1"/>
-    <col min="20" max="20" width="5" style="8" customWidth="1"/>
-    <col min="21" max="21" width="6.109375" style="8" customWidth="1"/>
-    <col min="22" max="22" width="5.109375" style="8" customWidth="1"/>
-    <col min="23" max="23" width="5.6640625" style="8" customWidth="1"/>
-    <col min="24" max="24" width="4.5546875" style="8" customWidth="1"/>
-    <col min="25" max="25" width="4.88671875" style="8" customWidth="1"/>
-    <col min="26" max="26" width="6" style="8" customWidth="1"/>
-    <col min="27" max="27" width="5.88671875" style="8" customWidth="1"/>
-    <col min="28" max="28" width="6.109375" style="8" customWidth="1"/>
-    <col min="29" max="257" width="9.109375" style="39"/>
-    <col min="258" max="258" width="30.109375" style="39" customWidth="1"/>
-    <col min="259" max="259" width="33.33203125" style="39" customWidth="1"/>
-    <col min="260" max="260" width="11" style="39" customWidth="1"/>
-    <col min="261" max="261" width="12.5546875" style="39" customWidth="1"/>
-    <col min="262" max="262" width="11.5546875" style="39" customWidth="1"/>
-    <col min="263" max="263" width="10.6640625" style="39" customWidth="1"/>
-    <col min="264" max="264" width="11.33203125" style="39" customWidth="1"/>
-    <col min="265" max="265" width="11.109375" style="39" customWidth="1"/>
-    <col min="266" max="266" width="11.6640625" style="39" customWidth="1"/>
-    <col min="267" max="267" width="11.44140625" style="39" customWidth="1"/>
-    <col min="268" max="270" width="10.6640625" style="39" customWidth="1"/>
-    <col min="271" max="273" width="10.5546875" style="39" customWidth="1"/>
-    <col min="274" max="274" width="11" style="39" customWidth="1"/>
-    <col min="275" max="275" width="10.6640625" style="39" customWidth="1"/>
-    <col min="276" max="276" width="10.5546875" style="39" customWidth="1"/>
-    <col min="277" max="277" width="13.5546875" style="39" customWidth="1"/>
-    <col min="278" max="278" width="11.109375" style="39" customWidth="1"/>
-    <col min="279" max="279" width="11.88671875" style="39" customWidth="1"/>
-    <col min="280" max="280" width="10.5546875" style="39" customWidth="1"/>
-    <col min="281" max="281" width="10.6640625" style="39" customWidth="1"/>
-    <col min="282" max="282" width="10.5546875" style="39" customWidth="1"/>
-    <col min="283" max="283" width="13.5546875" style="39" customWidth="1"/>
-    <col min="284" max="284" width="12.44140625" style="39" customWidth="1"/>
-    <col min="285" max="513" width="9.109375" style="39"/>
-    <col min="514" max="514" width="30.109375" style="39" customWidth="1"/>
-    <col min="515" max="515" width="33.33203125" style="39" customWidth="1"/>
-    <col min="516" max="516" width="11" style="39" customWidth="1"/>
-    <col min="517" max="517" width="12.5546875" style="39" customWidth="1"/>
-    <col min="518" max="518" width="11.5546875" style="39" customWidth="1"/>
-    <col min="519" max="519" width="10.6640625" style="39" customWidth="1"/>
-    <col min="520" max="520" width="11.33203125" style="39" customWidth="1"/>
-    <col min="521" max="521" width="11.109375" style="39" customWidth="1"/>
-    <col min="522" max="522" width="11.6640625" style="39" customWidth="1"/>
-    <col min="523" max="523" width="11.44140625" style="39" customWidth="1"/>
-    <col min="524" max="526" width="10.6640625" style="39" customWidth="1"/>
-    <col min="527" max="529" width="10.5546875" style="39" customWidth="1"/>
-    <col min="530" max="530" width="11" style="39" customWidth="1"/>
-    <col min="531" max="531" width="10.6640625" style="39" customWidth="1"/>
-    <col min="532" max="532" width="10.5546875" style="39" customWidth="1"/>
-    <col min="533" max="533" width="13.5546875" style="39" customWidth="1"/>
-    <col min="534" max="534" width="11.109375" style="39" customWidth="1"/>
-    <col min="535" max="535" width="11.88671875" style="39" customWidth="1"/>
-    <col min="536" max="536" width="10.5546875" style="39" customWidth="1"/>
-    <col min="537" max="537" width="10.6640625" style="39" customWidth="1"/>
-    <col min="538" max="538" width="10.5546875" style="39" customWidth="1"/>
-    <col min="539" max="539" width="13.5546875" style="39" customWidth="1"/>
-    <col min="540" max="540" width="12.44140625" style="39" customWidth="1"/>
-    <col min="541" max="769" width="9.109375" style="39"/>
-    <col min="770" max="770" width="30.109375" style="39" customWidth="1"/>
-    <col min="771" max="771" width="33.33203125" style="39" customWidth="1"/>
-    <col min="772" max="772" width="11" style="39" customWidth="1"/>
-    <col min="773" max="773" width="12.5546875" style="39" customWidth="1"/>
-    <col min="774" max="774" width="11.5546875" style="39" customWidth="1"/>
-    <col min="775" max="775" width="10.6640625" style="39" customWidth="1"/>
-    <col min="776" max="776" width="11.33203125" style="39" customWidth="1"/>
-    <col min="777" max="777" width="11.109375" style="39" customWidth="1"/>
-    <col min="778" max="778" width="11.6640625" style="39" customWidth="1"/>
-    <col min="779" max="779" width="11.44140625" style="39" customWidth="1"/>
-    <col min="780" max="782" width="10.6640625" style="39" customWidth="1"/>
-    <col min="783" max="785" width="10.5546875" style="39" customWidth="1"/>
-    <col min="786" max="786" width="11" style="39" customWidth="1"/>
-    <col min="787" max="787" width="10.6640625" style="39" customWidth="1"/>
-    <col min="788" max="788" width="10.5546875" style="39" customWidth="1"/>
-    <col min="789" max="789" width="13.5546875" style="39" customWidth="1"/>
-    <col min="790" max="790" width="11.109375" style="39" customWidth="1"/>
-    <col min="791" max="791" width="11.88671875" style="39" customWidth="1"/>
-    <col min="792" max="792" width="10.5546875" style="39" customWidth="1"/>
-    <col min="793" max="793" width="10.6640625" style="39" customWidth="1"/>
-    <col min="794" max="794" width="10.5546875" style="39" customWidth="1"/>
-    <col min="795" max="795" width="13.5546875" style="39" customWidth="1"/>
-    <col min="796" max="796" width="12.44140625" style="39" customWidth="1"/>
-    <col min="797" max="1025" width="9.109375" style="39"/>
-    <col min="1026" max="1026" width="30.109375" style="39" customWidth="1"/>
-    <col min="1027" max="1027" width="33.33203125" style="39" customWidth="1"/>
-    <col min="1028" max="1028" width="11" style="39" customWidth="1"/>
-    <col min="1029" max="1029" width="12.5546875" style="39" customWidth="1"/>
-    <col min="1030" max="1030" width="11.5546875" style="39" customWidth="1"/>
-    <col min="1031" max="1031" width="10.6640625" style="39" customWidth="1"/>
-    <col min="1032" max="1032" width="11.33203125" style="39" customWidth="1"/>
-    <col min="1033" max="1033" width="11.109375" style="39" customWidth="1"/>
-    <col min="1034" max="1034" width="11.6640625" style="39" customWidth="1"/>
-    <col min="1035" max="1035" width="11.44140625" style="39" customWidth="1"/>
-    <col min="1036" max="1038" width="10.6640625" style="39" customWidth="1"/>
-    <col min="1039" max="1041" width="10.5546875" style="39" customWidth="1"/>
-    <col min="1042" max="1042" width="11" style="39" customWidth="1"/>
-    <col min="1043" max="1043" width="10.6640625" style="39" customWidth="1"/>
-    <col min="1044" max="1044" width="10.5546875" style="39" customWidth="1"/>
-    <col min="1045" max="1045" width="13.5546875" style="39" customWidth="1"/>
-    <col min="1046" max="1046" width="11.109375" style="39" customWidth="1"/>
-    <col min="1047" max="1047" width="11.88671875" style="39" customWidth="1"/>
-    <col min="1048" max="1048" width="10.5546875" style="39" customWidth="1"/>
-    <col min="1049" max="1049" width="10.6640625" style="39" customWidth="1"/>
-    <col min="1050" max="1050" width="10.5546875" style="39" customWidth="1"/>
-    <col min="1051" max="1051" width="13.5546875" style="39" customWidth="1"/>
-    <col min="1052" max="1052" width="12.44140625" style="39" customWidth="1"/>
-    <col min="1053" max="1281" width="9.109375" style="39"/>
-    <col min="1282" max="1282" width="30.109375" style="39" customWidth="1"/>
-    <col min="1283" max="1283" width="33.33203125" style="39" customWidth="1"/>
-    <col min="1284" max="1284" width="11" style="39" customWidth="1"/>
-    <col min="1285" max="1285" width="12.5546875" style="39" customWidth="1"/>
-    <col min="1286" max="1286" width="11.5546875" style="39" customWidth="1"/>
-    <col min="1287" max="1287" width="10.6640625" style="39" customWidth="1"/>
-    <col min="1288" max="1288" width="11.33203125" style="39" customWidth="1"/>
-    <col min="1289" max="1289" width="11.109375" style="39" customWidth="1"/>
-    <col min="1290" max="1290" width="11.6640625" style="39" customWidth="1"/>
-    <col min="1291" max="1291" width="11.44140625" style="39" customWidth="1"/>
-    <col min="1292" max="1294" width="10.6640625" style="39" customWidth="1"/>
-    <col min="1295" max="1297" width="10.5546875" style="39" customWidth="1"/>
-    <col min="1298" max="1298" width="11" style="39" customWidth="1"/>
-    <col min="1299" max="1299" width="10.6640625" style="39" customWidth="1"/>
-    <col min="1300" max="1300" width="10.5546875" style="39" customWidth="1"/>
-    <col min="1301" max="1301" width="13.5546875" style="39" customWidth="1"/>
-    <col min="1302" max="1302" width="11.109375" style="39" customWidth="1"/>
-    <col min="1303" max="1303" width="11.88671875" style="39" customWidth="1"/>
-    <col min="1304" max="1304" width="10.5546875" style="39" customWidth="1"/>
-    <col min="1305" max="1305" width="10.6640625" style="39" customWidth="1"/>
-    <col min="1306" max="1306" width="10.5546875" style="39" customWidth="1"/>
-    <col min="1307" max="1307" width="13.5546875" style="39" customWidth="1"/>
-    <col min="1308" max="1308" width="12.44140625" style="39" customWidth="1"/>
-    <col min="1309" max="1537" width="9.109375" style="39"/>
-    <col min="1538" max="1538" width="30.109375" style="39" customWidth="1"/>
-    <col min="1539" max="1539" width="33.33203125" style="39" customWidth="1"/>
-    <col min="1540" max="1540" width="11" style="39" customWidth="1"/>
-    <col min="1541" max="1541" width="12.5546875" style="39" customWidth="1"/>
-    <col min="1542" max="1542" width="11.5546875" style="39" customWidth="1"/>
-    <col min="1543" max="1543" width="10.6640625" style="39" customWidth="1"/>
-    <col min="1544" max="1544" width="11.33203125" style="39" customWidth="1"/>
-    <col min="1545" max="1545" width="11.109375" style="39" customWidth="1"/>
-    <col min="1546" max="1546" width="11.6640625" style="39" customWidth="1"/>
-    <col min="1547" max="1547" width="11.44140625" style="39" customWidth="1"/>
-    <col min="1548" max="1550" width="10.6640625" style="39" customWidth="1"/>
-    <col min="1551" max="1553" width="10.5546875" style="39" customWidth="1"/>
-    <col min="1554" max="1554" width="11" style="39" customWidth="1"/>
-    <col min="1555" max="1555" width="10.6640625" style="39" customWidth="1"/>
-    <col min="1556" max="1556" width="10.5546875" style="39" customWidth="1"/>
-    <col min="1557" max="1557" width="13.5546875" style="39" customWidth="1"/>
-    <col min="1558" max="1558" width="11.109375" style="39" customWidth="1"/>
-    <col min="1559" max="1559" width="11.88671875" style="39" customWidth="1"/>
-    <col min="1560" max="1560" width="10.5546875" style="39" customWidth="1"/>
-    <col min="1561" max="1561" width="10.6640625" style="39" customWidth="1"/>
-    <col min="1562" max="1562" width="10.5546875" style="39" customWidth="1"/>
-    <col min="1563" max="1563" width="13.5546875" style="39" customWidth="1"/>
-    <col min="1564" max="1564" width="12.44140625" style="39" customWidth="1"/>
-    <col min="1565" max="1793" width="9.109375" style="39"/>
-    <col min="1794" max="1794" width="30.109375" style="39" customWidth="1"/>
-    <col min="1795" max="1795" width="33.33203125" style="39" customWidth="1"/>
-    <col min="1796" max="1796" width="11" style="39" customWidth="1"/>
-    <col min="1797" max="1797" width="12.5546875" style="39" customWidth="1"/>
-    <col min="1798" max="1798" width="11.5546875" style="39" customWidth="1"/>
-    <col min="1799" max="1799" width="10.6640625" style="39" customWidth="1"/>
-    <col min="1800" max="1800" width="11.33203125" style="39" customWidth="1"/>
-    <col min="1801" max="1801" width="11.109375" style="39" customWidth="1"/>
-    <col min="1802" max="1802" width="11.6640625" style="39" customWidth="1"/>
-    <col min="1803" max="1803" width="11.44140625" style="39" customWidth="1"/>
-    <col min="1804" max="1806" width="10.6640625" style="39" customWidth="1"/>
-    <col min="1807" max="1809" width="10.5546875" style="39" customWidth="1"/>
-    <col min="1810" max="1810" width="11" style="39" customWidth="1"/>
-    <col min="1811" max="1811" width="10.6640625" style="39" customWidth="1"/>
-    <col min="1812" max="1812" width="10.5546875" style="39" customWidth="1"/>
-    <col min="1813" max="1813" width="13.5546875" style="39" customWidth="1"/>
-    <col min="1814" max="1814" width="11.109375" style="39" customWidth="1"/>
-    <col min="1815" max="1815" width="11.88671875" style="39" customWidth="1"/>
-    <col min="1816" max="1816" width="10.5546875" style="39" customWidth="1"/>
-    <col min="1817" max="1817" width="10.6640625" style="39" customWidth="1"/>
-    <col min="1818" max="1818" width="10.5546875" style="39" customWidth="1"/>
-    <col min="1819" max="1819" width="13.5546875" style="39" customWidth="1"/>
-    <col min="1820" max="1820" width="12.44140625" style="39" customWidth="1"/>
-    <col min="1821" max="2049" width="9.109375" style="39"/>
-    <col min="2050" max="2050" width="30.109375" style="39" customWidth="1"/>
-    <col min="2051" max="2051" width="33.33203125" style="39" customWidth="1"/>
-    <col min="2052" max="2052" width="11" style="39" customWidth="1"/>
-    <col min="2053" max="2053" width="12.5546875" style="39" customWidth="1"/>
-    <col min="2054" max="2054" width="11.5546875" style="39" customWidth="1"/>
-    <col min="2055" max="2055" width="10.6640625" style="39" customWidth="1"/>
-    <col min="2056" max="2056" width="11.33203125" style="39" customWidth="1"/>
-    <col min="2057" max="2057" width="11.109375" style="39" customWidth="1"/>
-    <col min="2058" max="2058" width="11.6640625" style="39" customWidth="1"/>
-    <col min="2059" max="2059" width="11.44140625" style="39" customWidth="1"/>
-    <col min="2060" max="2062" width="10.6640625" style="39" customWidth="1"/>
-    <col min="2063" max="2065" width="10.5546875" style="39" customWidth="1"/>
-    <col min="2066" max="2066" width="11" style="39" customWidth="1"/>
-    <col min="2067" max="2067" width="10.6640625" style="39" customWidth="1"/>
-    <col min="2068" max="2068" width="10.5546875" style="39" customWidth="1"/>
-    <col min="2069" max="2069" width="13.5546875" style="39" customWidth="1"/>
-    <col min="2070" max="2070" width="11.109375" style="39" customWidth="1"/>
-    <col min="2071" max="2071" width="11.88671875" style="39" customWidth="1"/>
-    <col min="2072" max="2072" width="10.5546875" style="39" customWidth="1"/>
-    <col min="2073" max="2073" width="10.6640625" style="39" customWidth="1"/>
-    <col min="2074" max="2074" width="10.5546875" style="39" customWidth="1"/>
-    <col min="2075" max="2075" width="13.5546875" style="39" customWidth="1"/>
-    <col min="2076" max="2076" width="12.44140625" style="39" customWidth="1"/>
-    <col min="2077" max="2305" width="9.109375" style="39"/>
-    <col min="2306" max="2306" width="30.109375" style="39" customWidth="1"/>
-    <col min="2307" max="2307" width="33.33203125" style="39" customWidth="1"/>
-    <col min="2308" max="2308" width="11" style="39" customWidth="1"/>
-    <col min="2309" max="2309" width="12.5546875" style="39" customWidth="1"/>
-    <col min="2310" max="2310" width="11.5546875" style="39" customWidth="1"/>
-    <col min="2311" max="2311" width="10.6640625" style="39" customWidth="1"/>
-    <col min="2312" max="2312" width="11.33203125" style="39" customWidth="1"/>
-    <col min="2313" max="2313" width="11.109375" style="39" customWidth="1"/>
-    <col min="2314" max="2314" width="11.6640625" style="39" customWidth="1"/>
-    <col min="2315" max="2315" width="11.44140625" style="39" customWidth="1"/>
-    <col min="2316" max="2318" width="10.6640625" style="39" customWidth="1"/>
-    <col min="2319" max="2321" width="10.5546875" style="39" customWidth="1"/>
-    <col min="2322" max="2322" width="11" style="39" customWidth="1"/>
-    <col min="2323" max="2323" width="10.6640625" style="39" customWidth="1"/>
-    <col min="2324" max="2324" width="10.5546875" style="39" customWidth="1"/>
-    <col min="2325" max="2325" width="13.5546875" style="39" customWidth="1"/>
-    <col min="2326" max="2326" width="11.109375" style="39" customWidth="1"/>
-    <col min="2327" max="2327" width="11.88671875" style="39" customWidth="1"/>
-    <col min="2328" max="2328" width="10.5546875" style="39" customWidth="1"/>
-    <col min="2329" max="2329" width="10.6640625" style="39" customWidth="1"/>
-    <col min="2330" max="2330" width="10.5546875" style="39" customWidth="1"/>
-    <col min="2331" max="2331" width="13.5546875" style="39" customWidth="1"/>
-    <col min="2332" max="2332" width="12.44140625" style="39" customWidth="1"/>
-    <col min="2333" max="2561" width="9.109375" style="39"/>
-    <col min="2562" max="2562" width="30.109375" style="39" customWidth="1"/>
-    <col min="2563" max="2563" width="33.33203125" style="39" customWidth="1"/>
-    <col min="2564" max="2564" width="11" style="39" customWidth="1"/>
-    <col min="2565" max="2565" width="12.5546875" style="39" customWidth="1"/>
-    <col min="2566" max="2566" width="11.5546875" style="39" customWidth="1"/>
-    <col min="2567" max="2567" width="10.6640625" style="39" customWidth="1"/>
-    <col min="2568" max="2568" width="11.33203125" style="39" customWidth="1"/>
-    <col min="2569" max="2569" width="11.109375" style="39" customWidth="1"/>
-    <col min="2570" max="2570" width="11.6640625" style="39" customWidth="1"/>
-    <col min="2571" max="2571" width="11.44140625" style="39" customWidth="1"/>
-    <col min="2572" max="2574" width="10.6640625" style="39" customWidth="1"/>
-    <col min="2575" max="2577" width="10.5546875" style="39" customWidth="1"/>
-    <col min="2578" max="2578" width="11" style="39" customWidth="1"/>
-    <col min="2579" max="2579" width="10.6640625" style="39" customWidth="1"/>
-    <col min="2580" max="2580" width="10.5546875" style="39" customWidth="1"/>
-    <col min="2581" max="2581" width="13.5546875" style="39" customWidth="1"/>
-    <col min="2582" max="2582" width="11.109375" style="39" customWidth="1"/>
-    <col min="2583" max="2583" width="11.88671875" style="39" customWidth="1"/>
-    <col min="2584" max="2584" width="10.5546875" style="39" customWidth="1"/>
-    <col min="2585" max="2585" width="10.6640625" style="39" customWidth="1"/>
-    <col min="2586" max="2586" width="10.5546875" style="39" customWidth="1"/>
-    <col min="2587" max="2587" width="13.5546875" style="39" customWidth="1"/>
-    <col min="2588" max="2588" width="12.44140625" style="39" customWidth="1"/>
-    <col min="2589" max="2817" width="9.109375" style="39"/>
-    <col min="2818" max="2818" width="30.109375" style="39" customWidth="1"/>
-    <col min="2819" max="2819" width="33.33203125" style="39" customWidth="1"/>
-    <col min="2820" max="2820" width="11" style="39" customWidth="1"/>
-    <col min="2821" max="2821" width="12.5546875" style="39" customWidth="1"/>
-    <col min="2822" max="2822" width="11.5546875" style="39" customWidth="1"/>
-    <col min="2823" max="2823" width="10.6640625" style="39" customWidth="1"/>
-    <col min="2824" max="2824" width="11.33203125" style="39" customWidth="1"/>
-    <col min="2825" max="2825" width="11.109375" style="39" customWidth="1"/>
-    <col min="2826" max="2826" width="11.6640625" style="39" customWidth="1"/>
-    <col min="2827" max="2827" width="11.44140625" style="39" customWidth="1"/>
-    <col min="2828" max="2830" width="10.6640625" style="39" customWidth="1"/>
-    <col min="2831" max="2833" width="10.5546875" style="39" customWidth="1"/>
-    <col min="2834" max="2834" width="11" style="39" customWidth="1"/>
-    <col min="2835" max="2835" width="10.6640625" style="39" customWidth="1"/>
-    <col min="2836" max="2836" width="10.5546875" style="39" customWidth="1"/>
-    <col min="2837" max="2837" width="13.5546875" style="39" customWidth="1"/>
-    <col min="2838" max="2838" width="11.109375" style="39" customWidth="1"/>
-    <col min="2839" max="2839" width="11.88671875" style="39" customWidth="1"/>
-    <col min="2840" max="2840" width="10.5546875" style="39" customWidth="1"/>
-    <col min="2841" max="2841" width="10.6640625" style="39" customWidth="1"/>
-    <col min="2842" max="2842" width="10.5546875" style="39" customWidth="1"/>
-    <col min="2843" max="2843" width="13.5546875" style="39" customWidth="1"/>
-    <col min="2844" max="2844" width="12.44140625" style="39" customWidth="1"/>
-    <col min="2845" max="3073" width="9.109375" style="39"/>
-    <col min="3074" max="3074" width="30.109375" style="39" customWidth="1"/>
-    <col min="3075" max="3075" width="33.33203125" style="39" customWidth="1"/>
-    <col min="3076" max="3076" width="11" style="39" customWidth="1"/>
-    <col min="3077" max="3077" width="12.5546875" style="39" customWidth="1"/>
-    <col min="3078" max="3078" width="11.5546875" style="39" customWidth="1"/>
-    <col min="3079" max="3079" width="10.6640625" style="39" customWidth="1"/>
-    <col min="3080" max="3080" width="11.33203125" style="39" customWidth="1"/>
-    <col min="3081" max="3081" width="11.109375" style="39" customWidth="1"/>
-    <col min="3082" max="3082" width="11.6640625" style="39" customWidth="1"/>
-    <col min="3083" max="3083" width="11.44140625" style="39" customWidth="1"/>
-    <col min="3084" max="3086" width="10.6640625" style="39" customWidth="1"/>
-    <col min="3087" max="3089" width="10.5546875" style="39" customWidth="1"/>
-    <col min="3090" max="3090" width="11" style="39" customWidth="1"/>
-    <col min="3091" max="3091" width="10.6640625" style="39" customWidth="1"/>
-    <col min="3092" max="3092" width="10.5546875" style="39" customWidth="1"/>
-    <col min="3093" max="3093" width="13.5546875" style="39" customWidth="1"/>
-    <col min="3094" max="3094" width="11.109375" style="39" customWidth="1"/>
-    <col min="3095" max="3095" width="11.88671875" style="39" customWidth="1"/>
-    <col min="3096" max="3096" width="10.5546875" style="39" customWidth="1"/>
-    <col min="3097" max="3097" width="10.6640625" style="39" customWidth="1"/>
-    <col min="3098" max="3098" width="10.5546875" style="39" customWidth="1"/>
-    <col min="3099" max="3099" width="13.5546875" style="39" customWidth="1"/>
-    <col min="3100" max="3100" width="12.44140625" style="39" customWidth="1"/>
-    <col min="3101" max="3329" width="9.109375" style="39"/>
-    <col min="3330" max="3330" width="30.109375" style="39" customWidth="1"/>
-    <col min="3331" max="3331" width="33.33203125" style="39" customWidth="1"/>
-    <col min="3332" max="3332" width="11" style="39" customWidth="1"/>
-    <col min="3333" max="3333" width="12.5546875" style="39" customWidth="1"/>
-    <col min="3334" max="3334" width="11.5546875" style="39" customWidth="1"/>
-    <col min="3335" max="3335" width="10.6640625" style="39" customWidth="1"/>
-    <col min="3336" max="3336" width="11.33203125" style="39" customWidth="1"/>
-    <col min="3337" max="3337" width="11.109375" style="39" customWidth="1"/>
-    <col min="3338" max="3338" width="11.6640625" style="39" customWidth="1"/>
-    <col min="3339" max="3339" width="11.44140625" style="39" customWidth="1"/>
-    <col min="3340" max="3342" width="10.6640625" style="39" customWidth="1"/>
-    <col min="3343" max="3345" width="10.5546875" style="39" customWidth="1"/>
-    <col min="3346" max="3346" width="11" style="39" customWidth="1"/>
-    <col min="3347" max="3347" width="10.6640625" style="39" customWidth="1"/>
-    <col min="3348" max="3348" width="10.5546875" style="39" customWidth="1"/>
-    <col min="3349" max="3349" width="13.5546875" style="39" customWidth="1"/>
-    <col min="3350" max="3350" width="11.109375" style="39" customWidth="1"/>
-    <col min="3351" max="3351" width="11.88671875" style="39" customWidth="1"/>
-    <col min="3352" max="3352" width="10.5546875" style="39" customWidth="1"/>
-    <col min="3353" max="3353" width="10.6640625" style="39" customWidth="1"/>
-    <col min="3354" max="3354" width="10.5546875" style="39" customWidth="1"/>
-    <col min="3355" max="3355" width="13.5546875" style="39" customWidth="1"/>
-    <col min="3356" max="3356" width="12.44140625" style="39" customWidth="1"/>
-    <col min="3357" max="3585" width="9.109375" style="39"/>
-    <col min="3586" max="3586" width="30.109375" style="39" customWidth="1"/>
-    <col min="3587" max="3587" width="33.33203125" style="39" customWidth="1"/>
-    <col min="3588" max="3588" width="11" style="39" customWidth="1"/>
-    <col min="3589" max="3589" width="12.5546875" style="39" customWidth="1"/>
-    <col min="3590" max="3590" width="11.5546875" style="39" customWidth="1"/>
-    <col min="3591" max="3591" width="10.6640625" style="39" customWidth="1"/>
-    <col min="3592" max="3592" width="11.33203125" style="39" customWidth="1"/>
-    <col min="3593" max="3593" width="11.109375" style="39" customWidth="1"/>
-    <col min="3594" max="3594" width="11.6640625" style="39" customWidth="1"/>
-    <col min="3595" max="3595" width="11.44140625" style="39" customWidth="1"/>
-    <col min="3596" max="3598" width="10.6640625" style="39" customWidth="1"/>
-    <col min="3599" max="3601" width="10.5546875" style="39" customWidth="1"/>
-    <col min="3602" max="3602" width="11" style="39" customWidth="1"/>
-    <col min="3603" max="3603" width="10.6640625" style="39" customWidth="1"/>
-    <col min="3604" max="3604" width="10.5546875" style="39" customWidth="1"/>
-    <col min="3605" max="3605" width="13.5546875" style="39" customWidth="1"/>
-    <col min="3606" max="3606" width="11.109375" style="39" customWidth="1"/>
-    <col min="3607" max="3607" width="11.88671875" style="39" customWidth="1"/>
-    <col min="3608" max="3608" width="10.5546875" style="39" customWidth="1"/>
-    <col min="3609" max="3609" width="10.6640625" style="39" customWidth="1"/>
-    <col min="3610" max="3610" width="10.5546875" style="39" customWidth="1"/>
-    <col min="3611" max="3611" width="13.5546875" style="39" customWidth="1"/>
-    <col min="3612" max="3612" width="12.44140625" style="39" customWidth="1"/>
-    <col min="3613" max="3841" width="9.109375" style="39"/>
-    <col min="3842" max="3842" width="30.109375" style="39" customWidth="1"/>
-    <col min="3843" max="3843" width="33.33203125" style="39" customWidth="1"/>
-    <col min="3844" max="3844" width="11" style="39" customWidth="1"/>
-    <col min="3845" max="3845" width="12.5546875" style="39" customWidth="1"/>
-    <col min="3846" max="3846" width="11.5546875" style="39" customWidth="1"/>
-    <col min="3847" max="3847" width="10.6640625" style="39" customWidth="1"/>
-    <col min="3848" max="3848" width="11.33203125" style="39" customWidth="1"/>
-    <col min="3849" max="3849" width="11.109375" style="39" customWidth="1"/>
-    <col min="3850" max="3850" width="11.6640625" style="39" customWidth="1"/>
-    <col min="3851" max="3851" width="11.44140625" style="39" customWidth="1"/>
-    <col min="3852" max="3854" width="10.6640625" style="39" customWidth="1"/>
-    <col min="3855" max="3857" width="10.5546875" style="39" customWidth="1"/>
-    <col min="3858" max="3858" width="11" style="39" customWidth="1"/>
-    <col min="3859" max="3859" width="10.6640625" style="39" customWidth="1"/>
-    <col min="3860" max="3860" width="10.5546875" style="39" customWidth="1"/>
-    <col min="3861" max="3861" width="13.5546875" style="39" customWidth="1"/>
-    <col min="3862" max="3862" width="11.109375" style="39" customWidth="1"/>
-    <col min="3863" max="3863" width="11.88671875" style="39" customWidth="1"/>
-    <col min="3864" max="3864" width="10.5546875" style="39" customWidth="1"/>
-    <col min="3865" max="3865" width="10.6640625" style="39" customWidth="1"/>
-    <col min="3866" max="3866" width="10.5546875" style="39" customWidth="1"/>
-    <col min="3867" max="3867" width="13.5546875" style="39" customWidth="1"/>
-    <col min="3868" max="3868" width="12.44140625" style="39" customWidth="1"/>
-    <col min="3869" max="4097" width="9.109375" style="39"/>
-    <col min="4098" max="4098" width="30.109375" style="39" customWidth="1"/>
-    <col min="4099" max="4099" width="33.33203125" style="39" customWidth="1"/>
-    <col min="4100" max="4100" width="11" style="39" customWidth="1"/>
-    <col min="4101" max="4101" width="12.5546875" style="39" customWidth="1"/>
-    <col min="4102" max="4102" width="11.5546875" style="39" customWidth="1"/>
-    <col min="4103" max="4103" width="10.6640625" style="39" customWidth="1"/>
-    <col min="4104" max="4104" width="11.33203125" style="39" customWidth="1"/>
-    <col min="4105" max="4105" width="11.109375" style="39" customWidth="1"/>
-    <col min="4106" max="4106" width="11.6640625" style="39" customWidth="1"/>
-    <col min="4107" max="4107" width="11.44140625" style="39" customWidth="1"/>
-    <col min="4108" max="4110" width="10.6640625" style="39" customWidth="1"/>
-    <col min="4111" max="4113" width="10.5546875" style="39" customWidth="1"/>
-    <col min="4114" max="4114" width="11" style="39" customWidth="1"/>
-    <col min="4115" max="4115" width="10.6640625" style="39" customWidth="1"/>
-    <col min="4116" max="4116" width="10.5546875" style="39" customWidth="1"/>
-    <col min="4117" max="4117" width="13.5546875" style="39" customWidth="1"/>
-    <col min="4118" max="4118" width="11.109375" style="39" customWidth="1"/>
-    <col min="4119" max="4119" width="11.88671875" style="39" customWidth="1"/>
-    <col min="4120" max="4120" width="10.5546875" style="39" customWidth="1"/>
-    <col min="4121" max="4121" width="10.6640625" style="39" customWidth="1"/>
-    <col min="4122" max="4122" width="10.5546875" style="39" customWidth="1"/>
-    <col min="4123" max="4123" width="13.5546875" style="39" customWidth="1"/>
-    <col min="4124" max="4124" width="12.44140625" style="39" customWidth="1"/>
-    <col min="4125" max="4353" width="9.109375" style="39"/>
-    <col min="4354" max="4354" width="30.109375" style="39" customWidth="1"/>
-    <col min="4355" max="4355" width="33.33203125" style="39" customWidth="1"/>
-    <col min="4356" max="4356" width="11" style="39" customWidth="1"/>
-    <col min="4357" max="4357" width="12.5546875" style="39" customWidth="1"/>
-    <col min="4358" max="4358" width="11.5546875" style="39" customWidth="1"/>
-    <col min="4359" max="4359" width="10.6640625" style="39" customWidth="1"/>
-    <col min="4360" max="4360" width="11.33203125" style="39" customWidth="1"/>
-    <col min="4361" max="4361" width="11.109375" style="39" customWidth="1"/>
-    <col min="4362" max="4362" width="11.6640625" style="39" customWidth="1"/>
-    <col min="4363" max="4363" width="11.44140625" style="39" customWidth="1"/>
-    <col min="4364" max="4366" width="10.6640625" style="39" customWidth="1"/>
-    <col min="4367" max="4369" width="10.5546875" style="39" customWidth="1"/>
-    <col min="4370" max="4370" width="11" style="39" customWidth="1"/>
-    <col min="4371" max="4371" width="10.6640625" style="39" customWidth="1"/>
-    <col min="4372" max="4372" width="10.5546875" style="39" customWidth="1"/>
-    <col min="4373" max="4373" width="13.5546875" style="39" customWidth="1"/>
-    <col min="4374" max="4374" width="11.109375" style="39" customWidth="1"/>
-    <col min="4375" max="4375" width="11.88671875" style="39" customWidth="1"/>
-    <col min="4376" max="4376" width="10.5546875" style="39" customWidth="1"/>
-    <col min="4377" max="4377" width="10.6640625" style="39" customWidth="1"/>
-    <col min="4378" max="4378" width="10.5546875" style="39" customWidth="1"/>
-    <col min="4379" max="4379" width="13.5546875" style="39" customWidth="1"/>
-    <col min="4380" max="4380" width="12.44140625" style="39" customWidth="1"/>
-    <col min="4381" max="4609" width="9.109375" style="39"/>
-    <col min="4610" max="4610" width="30.109375" style="39" customWidth="1"/>
-    <col min="4611" max="4611" width="33.33203125" style="39" customWidth="1"/>
-    <col min="4612" max="4612" width="11" style="39" customWidth="1"/>
-    <col min="4613" max="4613" width="12.5546875" style="39" customWidth="1"/>
-    <col min="4614" max="4614" width="11.5546875" style="39" customWidth="1"/>
-    <col min="4615" max="4615" width="10.6640625" style="39" customWidth="1"/>
-    <col min="4616" max="4616" width="11.33203125" style="39" customWidth="1"/>
-    <col min="4617" max="4617" width="11.109375" style="39" customWidth="1"/>
-    <col min="4618" max="4618" width="11.6640625" style="39" customWidth="1"/>
-    <col min="4619" max="4619" width="11.44140625" style="39" customWidth="1"/>
-    <col min="4620" max="4622" width="10.6640625" style="39" customWidth="1"/>
-    <col min="4623" max="4625" width="10.5546875" style="39" customWidth="1"/>
-    <col min="4626" max="4626" width="11" style="39" customWidth="1"/>
-    <col min="4627" max="4627" width="10.6640625" style="39" customWidth="1"/>
-    <col min="4628" max="4628" width="10.5546875" style="39" customWidth="1"/>
-    <col min="4629" max="4629" width="13.5546875" style="39" customWidth="1"/>
-    <col min="4630" max="4630" width="11.109375" style="39" customWidth="1"/>
-    <col min="4631" max="4631" width="11.88671875" style="39" customWidth="1"/>
-    <col min="4632" max="4632" width="10.5546875" style="39" customWidth="1"/>
-    <col min="4633" max="4633" width="10.6640625" style="39" customWidth="1"/>
-    <col min="4634" max="4634" width="10.5546875" style="39" customWidth="1"/>
-    <col min="4635" max="4635" width="13.5546875" style="39" customWidth="1"/>
-    <col min="4636" max="4636" width="12.44140625" style="39" customWidth="1"/>
-    <col min="4637" max="4865" width="9.109375" style="39"/>
-    <col min="4866" max="4866" width="30.109375" style="39" customWidth="1"/>
-    <col min="4867" max="4867" width="33.33203125" style="39" customWidth="1"/>
-    <col min="4868" max="4868" width="11" style="39" customWidth="1"/>
-    <col min="4869" max="4869" width="12.5546875" style="39" customWidth="1"/>
-    <col min="4870" max="4870" width="11.5546875" style="39" customWidth="1"/>
-    <col min="4871" max="4871" width="10.6640625" style="39" customWidth="1"/>
-    <col min="4872" max="4872" width="11.33203125" style="39" customWidth="1"/>
-    <col min="4873" max="4873" width="11.109375" style="39" customWidth="1"/>
-    <col min="4874" max="4874" width="11.6640625" style="39" customWidth="1"/>
-    <col min="4875" max="4875" width="11.44140625" style="39" customWidth="1"/>
-    <col min="4876" max="4878" width="10.6640625" style="39" customWidth="1"/>
-    <col min="4879" max="4881" width="10.5546875" style="39" customWidth="1"/>
-    <col min="4882" max="4882" width="11" style="39" customWidth="1"/>
-    <col min="4883" max="4883" width="10.6640625" style="39" customWidth="1"/>
-    <col min="4884" max="4884" width="10.5546875" style="39" customWidth="1"/>
-    <col min="4885" max="4885" width="13.5546875" style="39" customWidth="1"/>
-    <col min="4886" max="4886" width="11.109375" style="39" customWidth="1"/>
-    <col min="4887" max="4887" width="11.88671875" style="39" customWidth="1"/>
-    <col min="4888" max="4888" width="10.5546875" style="39" customWidth="1"/>
-    <col min="4889" max="4889" width="10.6640625" style="39" customWidth="1"/>
-    <col min="4890" max="4890" width="10.5546875" style="39" customWidth="1"/>
-    <col min="4891" max="4891" width="13.5546875" style="39" customWidth="1"/>
-    <col min="4892" max="4892" width="12.44140625" style="39" customWidth="1"/>
-    <col min="4893" max="5121" width="9.109375" style="39"/>
-    <col min="5122" max="5122" width="30.109375" style="39" customWidth="1"/>
-    <col min="5123" max="5123" width="33.33203125" style="39" customWidth="1"/>
-    <col min="5124" max="5124" width="11" style="39" customWidth="1"/>
-    <col min="5125" max="5125" width="12.5546875" style="39" customWidth="1"/>
-    <col min="5126" max="5126" width="11.5546875" style="39" customWidth="1"/>
-    <col min="5127" max="5127" width="10.6640625" style="39" customWidth="1"/>
-    <col min="5128" max="5128" width="11.33203125" style="39" customWidth="1"/>
-    <col min="5129" max="5129" width="11.109375" style="39" customWidth="1"/>
-    <col min="5130" max="5130" width="11.6640625" style="39" customWidth="1"/>
-    <col min="5131" max="5131" width="11.44140625" style="39" customWidth="1"/>
-    <col min="5132" max="5134" width="10.6640625" style="39" customWidth="1"/>
-    <col min="5135" max="5137" width="10.5546875" style="39" customWidth="1"/>
-    <col min="5138" max="5138" width="11" style="39" customWidth="1"/>
-    <col min="5139" max="5139" width="10.6640625" style="39" customWidth="1"/>
-    <col min="5140" max="5140" width="10.5546875" style="39" customWidth="1"/>
-    <col min="5141" max="5141" width="13.5546875" style="39" customWidth="1"/>
-    <col min="5142" max="5142" width="11.109375" style="39" customWidth="1"/>
-    <col min="5143" max="5143" width="11.88671875" style="39" customWidth="1"/>
-    <col min="5144" max="5144" width="10.5546875" style="39" customWidth="1"/>
-    <col min="5145" max="5145" width="10.6640625" style="39" customWidth="1"/>
-    <col min="5146" max="5146" width="10.5546875" style="39" customWidth="1"/>
-    <col min="5147" max="5147" width="13.5546875" style="39" customWidth="1"/>
-    <col min="5148" max="5148" width="12.44140625" style="39" customWidth="1"/>
-    <col min="5149" max="5377" width="9.109375" style="39"/>
-    <col min="5378" max="5378" width="30.109375" style="39" customWidth="1"/>
-    <col min="5379" max="5379" width="33.33203125" style="39" customWidth="1"/>
-    <col min="5380" max="5380" width="11" style="39" customWidth="1"/>
-    <col min="5381" max="5381" width="12.5546875" style="39" customWidth="1"/>
-    <col min="5382" max="5382" width="11.5546875" style="39" customWidth="1"/>
-    <col min="5383" max="5383" width="10.6640625" style="39" customWidth="1"/>
-    <col min="5384" max="5384" width="11.33203125" style="39" customWidth="1"/>
-    <col min="5385" max="5385" width="11.109375" style="39" customWidth="1"/>
-    <col min="5386" max="5386" width="11.6640625" style="39" customWidth="1"/>
-    <col min="5387" max="5387" width="11.44140625" style="39" customWidth="1"/>
-    <col min="5388" max="5390" width="10.6640625" style="39" customWidth="1"/>
-    <col min="5391" max="5393" width="10.5546875" style="39" customWidth="1"/>
-    <col min="5394" max="5394" width="11" style="39" customWidth="1"/>
-    <col min="5395" max="5395" width="10.6640625" style="39" customWidth="1"/>
-    <col min="5396" max="5396" width="10.5546875" style="39" customWidth="1"/>
-    <col min="5397" max="5397" width="13.5546875" style="39" customWidth="1"/>
-    <col min="5398" max="5398" width="11.109375" style="39" customWidth="1"/>
-    <col min="5399" max="5399" width="11.88671875" style="39" customWidth="1"/>
-    <col min="5400" max="5400" width="10.5546875" style="39" customWidth="1"/>
-    <col min="5401" max="5401" width="10.6640625" style="39" customWidth="1"/>
-    <col min="5402" max="5402" width="10.5546875" style="39" customWidth="1"/>
-    <col min="5403" max="5403" width="13.5546875" style="39" customWidth="1"/>
-    <col min="5404" max="5404" width="12.44140625" style="39" customWidth="1"/>
-    <col min="5405" max="5633" width="9.109375" style="39"/>
-    <col min="5634" max="5634" width="30.109375" style="39" customWidth="1"/>
-    <col min="5635" max="5635" width="33.33203125" style="39" customWidth="1"/>
-    <col min="5636" max="5636" width="11" style="39" customWidth="1"/>
-    <col min="5637" max="5637" width="12.5546875" style="39" customWidth="1"/>
-    <col min="5638" max="5638" width="11.5546875" style="39" customWidth="1"/>
-    <col min="5639" max="5639" width="10.6640625" style="39" customWidth="1"/>
-    <col min="5640" max="5640" width="11.33203125" style="39" customWidth="1"/>
-    <col min="5641" max="5641" width="11.109375" style="39" customWidth="1"/>
-    <col min="5642" max="5642" width="11.6640625" style="39" customWidth="1"/>
-    <col min="5643" max="5643" width="11.44140625" style="39" customWidth="1"/>
-    <col min="5644" max="5646" width="10.6640625" style="39" customWidth="1"/>
-    <col min="5647" max="5649" width="10.5546875" style="39" customWidth="1"/>
-    <col min="5650" max="5650" width="11" style="39" customWidth="1"/>
-    <col min="5651" max="5651" width="10.6640625" style="39" customWidth="1"/>
-    <col min="5652" max="5652" width="10.5546875" style="39" customWidth="1"/>
-    <col min="5653" max="5653" width="13.5546875" style="39" customWidth="1"/>
-    <col min="5654" max="5654" width="11.109375" style="39" customWidth="1"/>
-    <col min="5655" max="5655" width="11.88671875" style="39" customWidth="1"/>
-    <col min="5656" max="5656" width="10.5546875" style="39" customWidth="1"/>
-    <col min="5657" max="5657" width="10.6640625" style="39" customWidth="1"/>
-    <col min="5658" max="5658" width="10.5546875" style="39" customWidth="1"/>
-    <col min="5659" max="5659" width="13.5546875" style="39" customWidth="1"/>
-    <col min="5660" max="5660" width="12.44140625" style="39" customWidth="1"/>
-    <col min="5661" max="5889" width="9.109375" style="39"/>
-    <col min="5890" max="5890" width="30.109375" style="39" customWidth="1"/>
-    <col min="5891" max="5891" width="33.33203125" style="39" customWidth="1"/>
-    <col min="5892" max="5892" width="11" style="39" customWidth="1"/>
-    <col min="5893" max="5893" width="12.5546875" style="39" customWidth="1"/>
-    <col min="5894" max="5894" width="11.5546875" style="39" customWidth="1"/>
-    <col min="5895" max="5895" width="10.6640625" style="39" customWidth="1"/>
-    <col min="5896" max="5896" width="11.33203125" style="39" customWidth="1"/>
-    <col min="5897" max="5897" width="11.109375" style="39" customWidth="1"/>
-    <col min="5898" max="5898" width="11.6640625" style="39" customWidth="1"/>
-    <col min="5899" max="5899" width="11.44140625" style="39" customWidth="1"/>
-    <col min="5900" max="5902" width="10.6640625" style="39" customWidth="1"/>
-    <col min="5903" max="5905" width="10.5546875" style="39" customWidth="1"/>
-    <col min="5906" max="5906" width="11" style="39" customWidth="1"/>
-    <col min="5907" max="5907" width="10.6640625" style="39" customWidth="1"/>
-    <col min="5908" max="5908" width="10.5546875" style="39" customWidth="1"/>
-    <col min="5909" max="5909" width="13.5546875" style="39" customWidth="1"/>
-    <col min="5910" max="5910" width="11.109375" style="39" customWidth="1"/>
-    <col min="5911" max="5911" width="11.88671875" style="39" customWidth="1"/>
-    <col min="5912" max="5912" width="10.5546875" style="39" customWidth="1"/>
-    <col min="5913" max="5913" width="10.6640625" style="39" customWidth="1"/>
-    <col min="5914" max="5914" width="10.5546875" style="39" customWidth="1"/>
-    <col min="5915" max="5915" width="13.5546875" style="39" customWidth="1"/>
-    <col min="5916" max="5916" width="12.44140625" style="39" customWidth="1"/>
-    <col min="5917" max="6145" width="9.109375" style="39"/>
-    <col min="6146" max="6146" width="30.109375" style="39" customWidth="1"/>
-    <col min="6147" max="6147" width="33.33203125" style="39" customWidth="1"/>
-    <col min="6148" max="6148" width="11" style="39" customWidth="1"/>
-    <col min="6149" max="6149" width="12.5546875" style="39" customWidth="1"/>
-    <col min="6150" max="6150" width="11.5546875" style="39" customWidth="1"/>
-    <col min="6151" max="6151" width="10.6640625" style="39" customWidth="1"/>
-    <col min="6152" max="6152" width="11.33203125" style="39" customWidth="1"/>
-    <col min="6153" max="6153" width="11.109375" style="39" customWidth="1"/>
-    <col min="6154" max="6154" width="11.6640625" style="39" customWidth="1"/>
-    <col min="6155" max="6155" width="11.44140625" style="39" customWidth="1"/>
-    <col min="6156" max="6158" width="10.6640625" style="39" customWidth="1"/>
-    <col min="6159" max="6161" width="10.5546875" style="39" customWidth="1"/>
-    <col min="6162" max="6162" width="11" style="39" customWidth="1"/>
-    <col min="6163" max="6163" width="10.6640625" style="39" customWidth="1"/>
-    <col min="6164" max="6164" width="10.5546875" style="39" customWidth="1"/>
-    <col min="6165" max="6165" width="13.5546875" style="39" customWidth="1"/>
-    <col min="6166" max="6166" width="11.109375" style="39" customWidth="1"/>
-    <col min="6167" max="6167" width="11.88671875" style="39" customWidth="1"/>
-    <col min="6168" max="6168" width="10.5546875" style="39" customWidth="1"/>
-    <col min="6169" max="6169" width="10.6640625" style="39" customWidth="1"/>
-    <col min="6170" max="6170" width="10.5546875" style="39" customWidth="1"/>
-    <col min="6171" max="6171" width="13.5546875" style="39" customWidth="1"/>
-    <col min="6172" max="6172" width="12.44140625" style="39" customWidth="1"/>
-    <col min="6173" max="6401" width="9.109375" style="39"/>
-    <col min="6402" max="6402" width="30.109375" style="39" customWidth="1"/>
-    <col min="6403" max="6403" width="33.33203125" style="39" customWidth="1"/>
-    <col min="6404" max="6404" width="11" style="39" customWidth="1"/>
-    <col min="6405" max="6405" width="12.5546875" style="39" customWidth="1"/>
-    <col min="6406" max="6406" width="11.5546875" style="39" customWidth="1"/>
-    <col min="6407" max="6407" width="10.6640625" style="39" customWidth="1"/>
-    <col min="6408" max="6408" width="11.33203125" style="39" customWidth="1"/>
-    <col min="6409" max="6409" width="11.109375" style="39" customWidth="1"/>
-    <col min="6410" max="6410" width="11.6640625" style="39" customWidth="1"/>
-    <col min="6411" max="6411" width="11.44140625" style="39" customWidth="1"/>
-    <col min="6412" max="6414" width="10.6640625" style="39" customWidth="1"/>
-    <col min="6415" max="6417" width="10.5546875" style="39" customWidth="1"/>
-    <col min="6418" max="6418" width="11" style="39" customWidth="1"/>
-    <col min="6419" max="6419" width="10.6640625" style="39" customWidth="1"/>
-    <col min="6420" max="6420" width="10.5546875" style="39" customWidth="1"/>
-    <col min="6421" max="6421" width="13.5546875" style="39" customWidth="1"/>
-    <col min="6422" max="6422" width="11.109375" style="39" customWidth="1"/>
-    <col min="6423" max="6423" width="11.88671875" style="39" customWidth="1"/>
-    <col min="6424" max="6424" width="10.5546875" style="39" customWidth="1"/>
-    <col min="6425" max="6425" width="10.6640625" style="39" customWidth="1"/>
-    <col min="6426" max="6426" width="10.5546875" style="39" customWidth="1"/>
-    <col min="6427" max="6427" width="13.5546875" style="39" customWidth="1"/>
-    <col min="6428" max="6428" width="12.44140625" style="39" customWidth="1"/>
-    <col min="6429" max="6657" width="9.109375" style="39"/>
-    <col min="6658" max="6658" width="30.109375" style="39" customWidth="1"/>
-    <col min="6659" max="6659" width="33.33203125" style="39" customWidth="1"/>
-    <col min="6660" max="6660" width="11" style="39" customWidth="1"/>
-    <col min="6661" max="6661" width="12.5546875" style="39" customWidth="1"/>
-    <col min="6662" max="6662" width="11.5546875" style="39" customWidth="1"/>
-    <col min="6663" max="6663" width="10.6640625" style="39" customWidth="1"/>
-    <col min="6664" max="6664" width="11.33203125" style="39" customWidth="1"/>
-    <col min="6665" max="6665" width="11.109375" style="39" customWidth="1"/>
-    <col min="6666" max="6666" width="11.6640625" style="39" customWidth="1"/>
-    <col min="6667" max="6667" width="11.44140625" style="39" customWidth="1"/>
-    <col min="6668" max="6670" width="10.6640625" style="39" customWidth="1"/>
-    <col min="6671" max="6673" width="10.5546875" style="39" customWidth="1"/>
-    <col min="6674" max="6674" width="11" style="39" customWidth="1"/>
-    <col min="6675" max="6675" width="10.6640625" style="39" customWidth="1"/>
-    <col min="6676" max="6676" width="10.5546875" style="39" customWidth="1"/>
-    <col min="6677" max="6677" width="13.5546875" style="39" customWidth="1"/>
-    <col min="6678" max="6678" width="11.109375" style="39" customWidth="1"/>
-    <col min="6679" max="6679" width="11.88671875" style="39" customWidth="1"/>
-    <col min="6680" max="6680" width="10.5546875" style="39" customWidth="1"/>
-    <col min="6681" max="6681" width="10.6640625" style="39" customWidth="1"/>
-    <col min="6682" max="6682" width="10.5546875" style="39" customWidth="1"/>
-    <col min="6683" max="6683" width="13.5546875" style="39" customWidth="1"/>
-    <col min="6684" max="6684" width="12.44140625" style="39" customWidth="1"/>
-    <col min="6685" max="6913" width="9.109375" style="39"/>
-    <col min="6914" max="6914" width="30.109375" style="39" customWidth="1"/>
-    <col min="6915" max="6915" width="33.33203125" style="39" customWidth="1"/>
-    <col min="6916" max="6916" width="11" style="39" customWidth="1"/>
-    <col min="6917" max="6917" width="12.5546875" style="39" customWidth="1"/>
-    <col min="6918" max="6918" width="11.5546875" style="39" customWidth="1"/>
-    <col min="6919" max="6919" width="10.6640625" style="39" customWidth="1"/>
-    <col min="6920" max="6920" width="11.33203125" style="39" customWidth="1"/>
-    <col min="6921" max="6921" width="11.109375" style="39" customWidth="1"/>
-    <col min="6922" max="6922" width="11.6640625" style="39" customWidth="1"/>
-    <col min="6923" max="6923" width="11.44140625" style="39" customWidth="1"/>
-    <col min="6924" max="6926" width="10.6640625" style="39" customWidth="1"/>
-    <col min="6927" max="6929" width="10.5546875" style="39" customWidth="1"/>
-    <col min="6930" max="6930" width="11" style="39" customWidth="1"/>
-    <col min="6931" max="6931" width="10.6640625" style="39" customWidth="1"/>
-    <col min="6932" max="6932" width="10.5546875" style="39" customWidth="1"/>
-    <col min="6933" max="6933" width="13.5546875" style="39" customWidth="1"/>
-    <col min="6934" max="6934" width="11.109375" style="39" customWidth="1"/>
-    <col min="6935" max="6935" width="11.88671875" style="39" customWidth="1"/>
-    <col min="6936" max="6936" width="10.5546875" style="39" customWidth="1"/>
-    <col min="6937" max="6937" width="10.6640625" style="39" customWidth="1"/>
-    <col min="6938" max="6938" width="10.5546875" style="39" customWidth="1"/>
-    <col min="6939" max="6939" width="13.5546875" style="39" customWidth="1"/>
-    <col min="6940" max="6940" width="12.44140625" style="39" customWidth="1"/>
-    <col min="6941" max="7169" width="9.109375" style="39"/>
-    <col min="7170" max="7170" width="30.109375" style="39" customWidth="1"/>
-    <col min="7171" max="7171" width="33.33203125" style="39" customWidth="1"/>
-    <col min="7172" max="7172" width="11" style="39" customWidth="1"/>
-    <col min="7173" max="7173" width="12.5546875" style="39" customWidth="1"/>
-    <col min="7174" max="7174" width="11.5546875" style="39" customWidth="1"/>
-    <col min="7175" max="7175" width="10.6640625" style="39" customWidth="1"/>
-    <col min="7176" max="7176" width="11.33203125" style="39" customWidth="1"/>
-    <col min="7177" max="7177" width="11.109375" style="39" customWidth="1"/>
-    <col min="7178" max="7178" width="11.6640625" style="39" customWidth="1"/>
-    <col min="7179" max="7179" width="11.44140625" style="39" customWidth="1"/>
-    <col min="7180" max="7182" width="10.6640625" style="39" customWidth="1"/>
-    <col min="7183" max="7185" width="10.5546875" style="39" customWidth="1"/>
-    <col min="7186" max="7186" width="11" style="39" customWidth="1"/>
-    <col min="7187" max="7187" width="10.6640625" style="39" customWidth="1"/>
-    <col min="7188" max="7188" width="10.5546875" style="39" customWidth="1"/>
-    <col min="7189" max="7189" width="13.5546875" style="39" customWidth="1"/>
-    <col min="7190" max="7190" width="11.109375" style="39" customWidth="1"/>
-    <col min="7191" max="7191" width="11.88671875" style="39" customWidth="1"/>
-    <col min="7192" max="7192" width="10.5546875" style="39" customWidth="1"/>
-    <col min="7193" max="7193" width="10.6640625" style="39" customWidth="1"/>
-    <col min="7194" max="7194" width="10.5546875" style="39" customWidth="1"/>
-    <col min="7195" max="7195" width="13.5546875" style="39" customWidth="1"/>
-    <col min="7196" max="7196" width="12.44140625" style="39" customWidth="1"/>
-    <col min="7197" max="7425" width="9.109375" style="39"/>
-    <col min="7426" max="7426" width="30.109375" style="39" customWidth="1"/>
-    <col min="7427" max="7427" width="33.33203125" style="39" customWidth="1"/>
-    <col min="7428" max="7428" width="11" style="39" customWidth="1"/>
-    <col min="7429" max="7429" width="12.5546875" style="39" customWidth="1"/>
-    <col min="7430" max="7430" width="11.5546875" style="39" customWidth="1"/>
-    <col min="7431" max="7431" width="10.6640625" style="39" customWidth="1"/>
-    <col min="7432" max="7432" width="11.33203125" style="39" customWidth="1"/>
-    <col min="7433" max="7433" width="11.109375" style="39" customWidth="1"/>
-    <col min="7434" max="7434" width="11.6640625" style="39" customWidth="1"/>
-    <col min="7435" max="7435" width="11.44140625" style="39" customWidth="1"/>
-    <col min="7436" max="7438" width="10.6640625" style="39" customWidth="1"/>
-    <col min="7439" max="7441" width="10.5546875" style="39" customWidth="1"/>
-    <col min="7442" max="7442" width="11" style="39" customWidth="1"/>
-    <col min="7443" max="7443" width="10.6640625" style="39" customWidth="1"/>
-    <col min="7444" max="7444" width="10.5546875" style="39" customWidth="1"/>
-    <col min="7445" max="7445" width="13.5546875" style="39" customWidth="1"/>
-    <col min="7446" max="7446" width="11.109375" style="39" customWidth="1"/>
-    <col min="7447" max="7447" width="11.88671875" style="39" customWidth="1"/>
-    <col min="7448" max="7448" width="10.5546875" style="39" customWidth="1"/>
-    <col min="7449" max="7449" width="10.6640625" style="39" customWidth="1"/>
-    <col min="7450" max="7450" width="10.5546875" style="39" customWidth="1"/>
-    <col min="7451" max="7451" width="13.5546875" style="39" customWidth="1"/>
-    <col min="7452" max="7452" width="12.44140625" style="39" customWidth="1"/>
-    <col min="7453" max="7681" width="9.109375" style="39"/>
-    <col min="7682" max="7682" width="30.109375" style="39" customWidth="1"/>
-    <col min="7683" max="7683" width="33.33203125" style="39" customWidth="1"/>
-    <col min="7684" max="7684" width="11" style="39" customWidth="1"/>
-    <col min="7685" max="7685" width="12.5546875" style="39" customWidth="1"/>
-    <col min="7686" max="7686" width="11.5546875" style="39" customWidth="1"/>
-    <col min="7687" max="7687" width="10.6640625" style="39" customWidth="1"/>
-    <col min="7688" max="7688" width="11.33203125" style="39" customWidth="1"/>
-    <col min="7689" max="7689" width="11.109375" style="39" customWidth="1"/>
-    <col min="7690" max="7690" width="11.6640625" style="39" customWidth="1"/>
-    <col min="7691" max="7691" width="11.44140625" style="39" customWidth="1"/>
-    <col min="7692" max="7694" width="10.6640625" style="39" customWidth="1"/>
-    <col min="7695" max="7697" width="10.5546875" style="39" customWidth="1"/>
-    <col min="7698" max="7698" width="11" style="39" customWidth="1"/>
-    <col min="7699" max="7699" width="10.6640625" style="39" customWidth="1"/>
-    <col min="7700" max="7700" width="10.5546875" style="39" customWidth="1"/>
-    <col min="7701" max="7701" width="13.5546875" style="39" customWidth="1"/>
-    <col min="7702" max="7702" width="11.109375" style="39" customWidth="1"/>
-    <col min="7703" max="7703" width="11.88671875" style="39" customWidth="1"/>
-    <col min="7704" max="7704" width="10.5546875" style="39" customWidth="1"/>
-    <col min="7705" max="7705" width="10.6640625" style="39" customWidth="1"/>
-    <col min="7706" max="7706" width="10.5546875" style="39" customWidth="1"/>
-    <col min="7707" max="7707" width="13.5546875" style="39" customWidth="1"/>
-    <col min="7708" max="7708" width="12.44140625" style="39" customWidth="1"/>
-    <col min="7709" max="7937" width="9.109375" style="39"/>
-    <col min="7938" max="7938" width="30.109375" style="39" customWidth="1"/>
-    <col min="7939" max="7939" width="33.33203125" style="39" customWidth="1"/>
-    <col min="7940" max="7940" width="11" style="39" customWidth="1"/>
-    <col min="7941" max="7941" width="12.5546875" style="39" customWidth="1"/>
-    <col min="7942" max="7942" width="11.5546875" style="39" customWidth="1"/>
-    <col min="7943" max="7943" width="10.6640625" style="39" customWidth="1"/>
-    <col min="7944" max="7944" width="11.33203125" style="39" customWidth="1"/>
-    <col min="7945" max="7945" width="11.109375" style="39" customWidth="1"/>
-    <col min="7946" max="7946" width="11.6640625" style="39" customWidth="1"/>
-    <col min="7947" max="7947" width="11.44140625" style="39" customWidth="1"/>
-    <col min="7948" max="7950" width="10.6640625" style="39" customWidth="1"/>
-    <col min="7951" max="7953" width="10.5546875" style="39" customWidth="1"/>
-    <col min="7954" max="7954" width="11" style="39" customWidth="1"/>
-    <col min="7955" max="7955" width="10.6640625" style="39" customWidth="1"/>
-    <col min="7956" max="7956" width="10.5546875" style="39" customWidth="1"/>
-    <col min="7957" max="7957" width="13.5546875" style="39" customWidth="1"/>
-    <col min="7958" max="7958" width="11.109375" style="39" customWidth="1"/>
-    <col min="7959" max="7959" width="11.88671875" style="39" customWidth="1"/>
-    <col min="7960" max="7960" width="10.5546875" style="39" customWidth="1"/>
-    <col min="7961" max="7961" width="10.6640625" style="39" customWidth="1"/>
-    <col min="7962" max="7962" width="10.5546875" style="39" customWidth="1"/>
-    <col min="7963" max="7963" width="13.5546875" style="39" customWidth="1"/>
-    <col min="7964" max="7964" width="12.44140625" style="39" customWidth="1"/>
-    <col min="7965" max="8193" width="9.109375" style="39"/>
-    <col min="8194" max="8194" width="30.109375" style="39" customWidth="1"/>
-    <col min="8195" max="8195" width="33.33203125" style="39" customWidth="1"/>
-    <col min="8196" max="8196" width="11" style="39" customWidth="1"/>
-    <col min="8197" max="8197" width="12.5546875" style="39" customWidth="1"/>
-    <col min="8198" max="8198" width="11.5546875" style="39" customWidth="1"/>
-    <col min="8199" max="8199" width="10.6640625" style="39" customWidth="1"/>
-    <col min="8200" max="8200" width="11.33203125" style="39" customWidth="1"/>
-    <col min="8201" max="8201" width="11.109375" style="39" customWidth="1"/>
-    <col min="8202" max="8202" width="11.6640625" style="39" customWidth="1"/>
-    <col min="8203" max="8203" width="11.44140625" style="39" customWidth="1"/>
-    <col min="8204" max="8206" width="10.6640625" style="39" customWidth="1"/>
-    <col min="8207" max="8209" width="10.5546875" style="39" customWidth="1"/>
-    <col min="8210" max="8210" width="11" style="39" customWidth="1"/>
-    <col min="8211" max="8211" width="10.6640625" style="39" customWidth="1"/>
-    <col min="8212" max="8212" width="10.5546875" style="39" customWidth="1"/>
-    <col min="8213" max="8213" width="13.5546875" style="39" customWidth="1"/>
-    <col min="8214" max="8214" width="11.109375" style="39" customWidth="1"/>
-    <col min="8215" max="8215" width="11.88671875" style="39" customWidth="1"/>
-    <col min="8216" max="8216" width="10.5546875" style="39" customWidth="1"/>
-    <col min="8217" max="8217" width="10.6640625" style="39" customWidth="1"/>
-    <col min="8218" max="8218" width="10.5546875" style="39" customWidth="1"/>
-    <col min="8219" max="8219" width="13.5546875" style="39" customWidth="1"/>
-    <col min="8220" max="8220" width="12.44140625" style="39" customWidth="1"/>
-    <col min="8221" max="8449" width="9.109375" style="39"/>
-    <col min="8450" max="8450" width="30.109375" style="39" customWidth="1"/>
-    <col min="8451" max="8451" width="33.33203125" style="39" customWidth="1"/>
-    <col min="8452" max="8452" width="11" style="39" customWidth="1"/>
-    <col min="8453" max="8453" width="12.5546875" style="39" customWidth="1"/>
-    <col min="8454" max="8454" width="11.5546875" style="39" customWidth="1"/>
-    <col min="8455" max="8455" width="10.6640625" style="39" customWidth="1"/>
-    <col min="8456" max="8456" width="11.33203125" style="39" customWidth="1"/>
-    <col min="8457" max="8457" width="11.109375" style="39" customWidth="1"/>
-    <col min="8458" max="8458" width="11.6640625" style="39" customWidth="1"/>
-    <col min="8459" max="8459" width="11.44140625" style="39" customWidth="1"/>
-    <col min="8460" max="8462" width="10.6640625" style="39" customWidth="1"/>
-    <col min="8463" max="8465" width="10.5546875" style="39" customWidth="1"/>
-    <col min="8466" max="8466" width="11" style="39" customWidth="1"/>
-    <col min="8467" max="8467" width="10.6640625" style="39" customWidth="1"/>
-    <col min="8468" max="8468" width="10.5546875" style="39" customWidth="1"/>
-    <col min="8469" max="8469" width="13.5546875" style="39" customWidth="1"/>
-    <col min="8470" max="8470" width="11.109375" style="39" customWidth="1"/>
-    <col min="8471" max="8471" width="11.88671875" style="39" customWidth="1"/>
-    <col min="8472" max="8472" width="10.5546875" style="39" customWidth="1"/>
-    <col min="8473" max="8473" width="10.6640625" style="39" customWidth="1"/>
-    <col min="8474" max="8474" width="10.5546875" style="39" customWidth="1"/>
-    <col min="8475" max="8475" width="13.5546875" style="39" customWidth="1"/>
-    <col min="8476" max="8476" width="12.44140625" style="39" customWidth="1"/>
-    <col min="8477" max="8705" width="9.109375" style="39"/>
-    <col min="8706" max="8706" width="30.109375" style="39" customWidth="1"/>
-    <col min="8707" max="8707" width="33.33203125" style="39" customWidth="1"/>
-    <col min="8708" max="8708" width="11" style="39" customWidth="1"/>
-    <col min="8709" max="8709" width="12.5546875" style="39" customWidth="1"/>
-    <col min="8710" max="8710" width="11.5546875" style="39" customWidth="1"/>
-    <col min="8711" max="8711" width="10.6640625" style="39" customWidth="1"/>
-    <col min="8712" max="8712" width="11.33203125" style="39" customWidth="1"/>
-    <col min="8713" max="8713" width="11.109375" style="39" customWidth="1"/>
-    <col min="8714" max="8714" width="11.6640625" style="39" customWidth="1"/>
-    <col min="8715" max="8715" width="11.44140625" style="39" customWidth="1"/>
-    <col min="8716" max="8718" width="10.6640625" style="39" customWidth="1"/>
-    <col min="8719" max="8721" width="10.5546875" style="39" customWidth="1"/>
-    <col min="8722" max="8722" width="11" style="39" customWidth="1"/>
-    <col min="8723" max="8723" width="10.6640625" style="39" customWidth="1"/>
-    <col min="8724" max="8724" width="10.5546875" style="39" customWidth="1"/>
-    <col min="8725" max="8725" width="13.5546875" style="39" customWidth="1"/>
-    <col min="8726" max="8726" width="11.109375" style="39" customWidth="1"/>
-    <col min="8727" max="8727" width="11.88671875" style="39" customWidth="1"/>
-    <col min="8728" max="8728" width="10.5546875" style="39" customWidth="1"/>
-    <col min="8729" max="8729" width="10.6640625" style="39" customWidth="1"/>
-    <col min="8730" max="8730" width="10.5546875" style="39" customWidth="1"/>
-    <col min="8731" max="8731" width="13.5546875" style="39" customWidth="1"/>
-    <col min="8732" max="8732" width="12.44140625" style="39" customWidth="1"/>
-    <col min="8733" max="8961" width="9.109375" style="39"/>
-    <col min="8962" max="8962" width="30.109375" style="39" customWidth="1"/>
-    <col min="8963" max="8963" width="33.33203125" style="39" customWidth="1"/>
-    <col min="8964" max="8964" width="11" style="39" customWidth="1"/>
-    <col min="8965" max="8965" width="12.5546875" style="39" customWidth="1"/>
-    <col min="8966" max="8966" width="11.5546875" style="39" customWidth="1"/>
-    <col min="8967" max="8967" width="10.6640625" style="39" customWidth="1"/>
-    <col min="8968" max="8968" width="11.33203125" style="39" customWidth="1"/>
-    <col min="8969" max="8969" width="11.109375" style="39" customWidth="1"/>
-    <col min="8970" max="8970" width="11.6640625" style="39" customWidth="1"/>
-    <col min="8971" max="8971" width="11.44140625" style="39" customWidth="1"/>
-    <col min="8972" max="8974" width="10.6640625" style="39" customWidth="1"/>
-    <col min="8975" max="8977" width="10.5546875" style="39" customWidth="1"/>
-    <col min="8978" max="8978" width="11" style="39" customWidth="1"/>
-    <col min="8979" max="8979" width="10.6640625" style="39" customWidth="1"/>
-    <col min="8980" max="8980" width="10.5546875" style="39" customWidth="1"/>
-    <col min="8981" max="8981" width="13.5546875" style="39" customWidth="1"/>
-    <col min="8982" max="8982" width="11.109375" style="39" customWidth="1"/>
-    <col min="8983" max="8983" width="11.88671875" style="39" customWidth="1"/>
-    <col min="8984" max="8984" width="10.5546875" style="39" customWidth="1"/>
-    <col min="8985" max="8985" width="10.6640625" style="39" customWidth="1"/>
-    <col min="8986" max="8986" width="10.5546875" style="39" customWidth="1"/>
-    <col min="8987" max="8987" width="13.5546875" style="39" customWidth="1"/>
-    <col min="8988" max="8988" width="12.44140625" style="39" customWidth="1"/>
-    <col min="8989" max="9217" width="9.109375" style="39"/>
-    <col min="9218" max="9218" width="30.109375" style="39" customWidth="1"/>
-    <col min="9219" max="9219" width="33.33203125" style="39" customWidth="1"/>
-    <col min="9220" max="9220" width="11" style="39" customWidth="1"/>
-    <col min="9221" max="9221" width="12.5546875" style="39" customWidth="1"/>
-    <col min="9222" max="9222" width="11.5546875" style="39" customWidth="1"/>
-    <col min="9223" max="9223" width="10.6640625" style="39" customWidth="1"/>
-    <col min="9224" max="9224" width="11.33203125" style="39" customWidth="1"/>
-    <col min="9225" max="9225" width="11.109375" style="39" customWidth="1"/>
-    <col min="9226" max="9226" width="11.6640625" style="39" customWidth="1"/>
-    <col min="9227" max="9227" width="11.44140625" style="39" customWidth="1"/>
-    <col min="9228" max="9230" width="10.6640625" style="39" customWidth="1"/>
-    <col min="9231" max="9233" width="10.5546875" style="39" customWidth="1"/>
-    <col min="9234" max="9234" width="11" style="39" customWidth="1"/>
-    <col min="9235" max="9235" width="10.6640625" style="39" customWidth="1"/>
-    <col min="9236" max="9236" width="10.5546875" style="39" customWidth="1"/>
-    <col min="9237" max="9237" width="13.5546875" style="39" customWidth="1"/>
-    <col min="9238" max="9238" width="11.109375" style="39" customWidth="1"/>
-    <col min="9239" max="9239" width="11.88671875" style="39" customWidth="1"/>
-    <col min="9240" max="9240" width="10.5546875" style="39" customWidth="1"/>
-    <col min="9241" max="9241" width="10.6640625" style="39" customWidth="1"/>
-    <col min="9242" max="9242" width="10.5546875" style="39" customWidth="1"/>
-    <col min="9243" max="9243" width="13.5546875" style="39" customWidth="1"/>
-    <col min="9244" max="9244" width="12.44140625" style="39" customWidth="1"/>
-    <col min="9245" max="9473" width="9.109375" style="39"/>
-    <col min="9474" max="9474" width="30.109375" style="39" customWidth="1"/>
-    <col min="9475" max="9475" width="33.33203125" style="39" customWidth="1"/>
-    <col min="9476" max="9476" width="11" style="39" customWidth="1"/>
-    <col min="9477" max="9477" width="12.5546875" style="39" customWidth="1"/>
-    <col min="9478" max="9478" width="11.5546875" style="39" customWidth="1"/>
-    <col min="9479" max="9479" width="10.6640625" style="39" customWidth="1"/>
-    <col min="9480" max="9480" width="11.33203125" style="39" customWidth="1"/>
-    <col min="9481" max="9481" width="11.109375" style="39" customWidth="1"/>
-    <col min="9482" max="9482" width="11.6640625" style="39" customWidth="1"/>
-    <col min="9483" max="9483" width="11.44140625" style="39" customWidth="1"/>
-    <col min="9484" max="9486" width="10.6640625" style="39" customWidth="1"/>
-    <col min="9487" max="9489" width="10.5546875" style="39" customWidth="1"/>
-    <col min="9490" max="9490" width="11" style="39" customWidth="1"/>
-    <col min="9491" max="9491" width="10.6640625" style="39" customWidth="1"/>
-    <col min="9492" max="9492" width="10.5546875" style="39" customWidth="1"/>
-    <col min="9493" max="9493" width="13.5546875" style="39" customWidth="1"/>
-    <col min="9494" max="9494" width="11.109375" style="39" customWidth="1"/>
-    <col min="9495" max="9495" width="11.88671875" style="39" customWidth="1"/>
-    <col min="9496" max="9496" width="10.5546875" style="39" customWidth="1"/>
-    <col min="9497" max="9497" width="10.6640625" style="39" customWidth="1"/>
-    <col min="9498" max="9498" width="10.5546875" style="39" customWidth="1"/>
-    <col min="9499" max="9499" width="13.5546875" style="39" customWidth="1"/>
-    <col min="9500" max="9500" width="12.44140625" style="39" customWidth="1"/>
-    <col min="9501" max="9729" width="9.109375" style="39"/>
-    <col min="9730" max="9730" width="30.109375" style="39" customWidth="1"/>
-    <col min="9731" max="9731" width="33.33203125" style="39" customWidth="1"/>
-    <col min="9732" max="9732" width="11" style="39" customWidth="1"/>
-    <col min="9733" max="9733" width="12.5546875" style="39" customWidth="1"/>
-    <col min="9734" max="9734" width="11.5546875" style="39" customWidth="1"/>
-    <col min="9735" max="9735" width="10.6640625" style="39" customWidth="1"/>
-    <col min="9736" max="9736" width="11.33203125" style="39" customWidth="1"/>
-    <col min="9737" max="9737" width="11.109375" style="39" customWidth="1"/>
-    <col min="9738" max="9738" width="11.6640625" style="39" customWidth="1"/>
-    <col min="9739" max="9739" width="11.44140625" style="39" customWidth="1"/>
-    <col min="9740" max="9742" width="10.6640625" style="39" customWidth="1"/>
-    <col min="9743" max="9745" width="10.5546875" style="39" customWidth="1"/>
-    <col min="9746" max="9746" width="11" style="39" customWidth="1"/>
-    <col min="9747" max="9747" width="10.6640625" style="39" customWidth="1"/>
-    <col min="9748" max="9748" width="10.5546875" style="39" customWidth="1"/>
-    <col min="9749" max="9749" width="13.5546875" style="39" customWidth="1"/>
-    <col min="9750" max="9750" width="11.109375" style="39" customWidth="1"/>
-    <col min="9751" max="9751" width="11.88671875" style="39" customWidth="1"/>
-    <col min="9752" max="9752" width="10.5546875" style="39" customWidth="1"/>
-    <col min="9753" max="9753" width="10.6640625" style="39" customWidth="1"/>
-    <col min="9754" max="9754" width="10.5546875" style="39" customWidth="1"/>
-    <col min="9755" max="9755" width="13.5546875" style="39" customWidth="1"/>
-    <col min="9756" max="9756" width="12.44140625" style="39" customWidth="1"/>
-    <col min="9757" max="9985" width="9.109375" style="39"/>
-    <col min="9986" max="9986" width="30.109375" style="39" customWidth="1"/>
-    <col min="9987" max="9987" width="33.33203125" style="39" customWidth="1"/>
-    <col min="9988" max="9988" width="11" style="39" customWidth="1"/>
-    <col min="9989" max="9989" width="12.5546875" style="39" customWidth="1"/>
-    <col min="9990" max="9990" width="11.5546875" style="39" customWidth="1"/>
-    <col min="9991" max="9991" width="10.6640625" style="39" customWidth="1"/>
-    <col min="9992" max="9992" width="11.33203125" style="39" customWidth="1"/>
-    <col min="9993" max="9993" width="11.109375" style="39" customWidth="1"/>
-    <col min="9994" max="9994" width="11.6640625" style="39" customWidth="1"/>
-    <col min="9995" max="9995" width="11.44140625" style="39" customWidth="1"/>
-    <col min="9996" max="9998" width="10.6640625" style="39" customWidth="1"/>
-    <col min="9999" max="10001" width="10.5546875" style="39" customWidth="1"/>
-    <col min="10002" max="10002" width="11" style="39" customWidth="1"/>
-    <col min="10003" max="10003" width="10.6640625" style="39" customWidth="1"/>
-    <col min="10004" max="10004" width="10.5546875" style="39" customWidth="1"/>
-    <col min="10005" max="10005" width="13.5546875" style="39" customWidth="1"/>
-    <col min="10006" max="10006" width="11.109375" style="39" customWidth="1"/>
-    <col min="10007" max="10007" width="11.88671875" style="39" customWidth="1"/>
-    <col min="10008" max="10008" width="10.5546875" style="39" customWidth="1"/>
-    <col min="10009" max="10009" width="10.6640625" style="39" customWidth="1"/>
-    <col min="10010" max="10010" width="10.5546875" style="39" customWidth="1"/>
-    <col min="10011" max="10011" width="13.5546875" style="39" customWidth="1"/>
-    <col min="10012" max="10012" width="12.44140625" style="39" customWidth="1"/>
-    <col min="10013" max="10241" width="9.109375" style="39"/>
-    <col min="10242" max="10242" width="30.109375" style="39" customWidth="1"/>
-    <col min="10243" max="10243" width="33.33203125" style="39" customWidth="1"/>
-    <col min="10244" max="10244" width="11" style="39" customWidth="1"/>
-    <col min="10245" max="10245" width="12.5546875" style="39" customWidth="1"/>
-    <col min="10246" max="10246" width="11.5546875" style="39" customWidth="1"/>
-    <col min="10247" max="10247" width="10.6640625" style="39" customWidth="1"/>
-    <col min="10248" max="10248" width="11.33203125" style="39" customWidth="1"/>
-    <col min="10249" max="10249" width="11.109375" style="39" customWidth="1"/>
-    <col min="10250" max="10250" width="11.6640625" style="39" customWidth="1"/>
-    <col min="10251" max="10251" width="11.44140625" style="39" customWidth="1"/>
-    <col min="10252" max="10254" width="10.6640625" style="39" customWidth="1"/>
-    <col min="10255" max="10257" width="10.5546875" style="39" customWidth="1"/>
-    <col min="10258" max="10258" width="11" style="39" customWidth="1"/>
-    <col min="10259" max="10259" width="10.6640625" style="39" customWidth="1"/>
-    <col min="10260" max="10260" width="10.5546875" style="39" customWidth="1"/>
-    <col min="10261" max="10261" width="13.5546875" style="39" customWidth="1"/>
-    <col min="10262" max="10262" width="11.109375" style="39" customWidth="1"/>
-    <col min="10263" max="10263" width="11.88671875" style="39" customWidth="1"/>
-    <col min="10264" max="10264" width="10.5546875" style="39" customWidth="1"/>
-    <col min="10265" max="10265" width="10.6640625" style="39" customWidth="1"/>
-    <col min="10266" max="10266" width="10.5546875" style="39" customWidth="1"/>
-    <col min="10267" max="10267" width="13.5546875" style="39" customWidth="1"/>
-    <col min="10268" max="10268" width="12.44140625" style="39" customWidth="1"/>
-    <col min="10269" max="10497" width="9.109375" style="39"/>
-    <col min="10498" max="10498" width="30.109375" style="39" customWidth="1"/>
-    <col min="10499" max="10499" width="33.33203125" style="39" customWidth="1"/>
-    <col min="10500" max="10500" width="11" style="39" customWidth="1"/>
-    <col min="10501" max="10501" width="12.5546875" style="39" customWidth="1"/>
-    <col min="10502" max="10502" width="11.5546875" style="39" customWidth="1"/>
-    <col min="10503" max="10503" width="10.6640625" style="39" customWidth="1"/>
-    <col min="10504" max="10504" width="11.33203125" style="39" customWidth="1"/>
-    <col min="10505" max="10505" width="11.109375" style="39" customWidth="1"/>
-    <col min="10506" max="10506" width="11.6640625" style="39" customWidth="1"/>
-    <col min="10507" max="10507" width="11.44140625" style="39" customWidth="1"/>
-    <col min="10508" max="10510" width="10.6640625" style="39" customWidth="1"/>
-    <col min="10511" max="10513" width="10.5546875" style="39" customWidth="1"/>
-    <col min="10514" max="10514" width="11" style="39" customWidth="1"/>
-    <col min="10515" max="10515" width="10.6640625" style="39" customWidth="1"/>
-    <col min="10516" max="10516" width="10.5546875" style="39" customWidth="1"/>
-    <col min="10517" max="10517" width="13.5546875" style="39" customWidth="1"/>
-    <col min="10518" max="10518" width="11.109375" style="39" customWidth="1"/>
-    <col min="10519" max="10519" width="11.88671875" style="39" customWidth="1"/>
-    <col min="10520" max="10520" width="10.5546875" style="39" customWidth="1"/>
-    <col min="10521" max="10521" width="10.6640625" style="39" customWidth="1"/>
-    <col min="10522" max="10522" width="10.5546875" style="39" customWidth="1"/>
-    <col min="10523" max="10523" width="13.5546875" style="39" customWidth="1"/>
-    <col min="10524" max="10524" width="12.44140625" style="39" customWidth="1"/>
-    <col min="10525" max="10753" width="9.109375" style="39"/>
-    <col min="10754" max="10754" width="30.109375" style="39" customWidth="1"/>
-    <col min="10755" max="10755" width="33.33203125" style="39" customWidth="1"/>
-    <col min="10756" max="10756" width="11" style="39" customWidth="1"/>
-    <col min="10757" max="10757" width="12.5546875" style="39" customWidth="1"/>
-    <col min="10758" max="10758" width="11.5546875" style="39" customWidth="1"/>
-    <col min="10759" max="10759" width="10.6640625" style="39" customWidth="1"/>
-    <col min="10760" max="10760" width="11.33203125" style="39" customWidth="1"/>
-    <col min="10761" max="10761" width="11.109375" style="39" customWidth="1"/>
-    <col min="10762" max="10762" width="11.6640625" style="39" customWidth="1"/>
-    <col min="10763" max="10763" width="11.44140625" style="39" customWidth="1"/>
-    <col min="10764" max="10766" width="10.6640625" style="39" customWidth="1"/>
-    <col min="10767" max="10769" width="10.5546875" style="39" customWidth="1"/>
-    <col min="10770" max="10770" width="11" style="39" customWidth="1"/>
-    <col min="10771" max="10771" width="10.6640625" style="39" customWidth="1"/>
-    <col min="10772" max="10772" width="10.5546875" style="39" customWidth="1"/>
-    <col min="10773" max="10773" width="13.5546875" style="39" customWidth="1"/>
-    <col min="10774" max="10774" width="11.109375" style="39" customWidth="1"/>
-    <col min="10775" max="10775" width="11.88671875" style="39" customWidth="1"/>
-    <col min="10776" max="10776" width="10.5546875" style="39" customWidth="1"/>
-    <col min="10777" max="10777" width="10.6640625" style="39" customWidth="1"/>
-    <col min="10778" max="10778" width="10.5546875" style="39" customWidth="1"/>
-    <col min="10779" max="10779" width="13.5546875" style="39" customWidth="1"/>
-    <col min="10780" max="10780" width="12.44140625" style="39" customWidth="1"/>
-    <col min="10781" max="11009" width="9.109375" style="39"/>
-    <col min="11010" max="11010" width="30.109375" style="39" customWidth="1"/>
-    <col min="11011" max="11011" width="33.33203125" style="39" customWidth="1"/>
-    <col min="11012" max="11012" width="11" style="39" customWidth="1"/>
-    <col min="11013" max="11013" width="12.5546875" style="39" customWidth="1"/>
-    <col min="11014" max="11014" width="11.5546875" style="39" customWidth="1"/>
-    <col min="11015" max="11015" width="10.6640625" style="39" customWidth="1"/>
-    <col min="11016" max="11016" width="11.33203125" style="39" customWidth="1"/>
-    <col min="11017" max="11017" width="11.109375" style="39" customWidth="1"/>
-    <col min="11018" max="11018" width="11.6640625" style="39" customWidth="1"/>
-    <col min="11019" max="11019" width="11.44140625" style="39" customWidth="1"/>
-    <col min="11020" max="11022" width="10.6640625" style="39" customWidth="1"/>
-    <col min="11023" max="11025" width="10.5546875" style="39" customWidth="1"/>
-    <col min="11026" max="11026" width="11" style="39" customWidth="1"/>
-    <col min="11027" max="11027" width="10.6640625" style="39" customWidth="1"/>
-    <col min="11028" max="11028" width="10.5546875" style="39" customWidth="1"/>
-    <col min="11029" max="11029" width="13.5546875" style="39" customWidth="1"/>
-    <col min="11030" max="11030" width="11.109375" style="39" customWidth="1"/>
-    <col min="11031" max="11031" width="11.88671875" style="39" customWidth="1"/>
-    <col min="11032" max="11032" width="10.5546875" style="39" customWidth="1"/>
-    <col min="11033" max="11033" width="10.6640625" style="39" customWidth="1"/>
-    <col min="11034" max="11034" width="10.5546875" style="39" customWidth="1"/>
-    <col min="11035" max="11035" width="13.5546875" style="39" customWidth="1"/>
-    <col min="11036" max="11036" width="12.44140625" style="39" customWidth="1"/>
-    <col min="11037" max="11265" width="9.109375" style="39"/>
-    <col min="11266" max="11266" width="30.109375" style="39" customWidth="1"/>
-    <col min="11267" max="11267" width="33.33203125" style="39" customWidth="1"/>
-    <col min="11268" max="11268" width="11" style="39" customWidth="1"/>
-    <col min="11269" max="11269" width="12.5546875" style="39" customWidth="1"/>
-    <col min="11270" max="11270" width="11.5546875" style="39" customWidth="1"/>
-    <col min="11271" max="11271" width="10.6640625" style="39" customWidth="1"/>
-    <col min="11272" max="11272" width="11.33203125" style="39" customWidth="1"/>
-    <col min="11273" max="11273" width="11.109375" style="39" customWidth="1"/>
-    <col min="11274" max="11274" width="11.6640625" style="39" customWidth="1"/>
-    <col min="11275" max="11275" width="11.44140625" style="39" customWidth="1"/>
-    <col min="11276" max="11278" width="10.6640625" style="39" customWidth="1"/>
-    <col min="11279" max="11281" width="10.5546875" style="39" customWidth="1"/>
-    <col min="11282" max="11282" width="11" style="39" customWidth="1"/>
-    <col min="11283" max="11283" width="10.6640625" style="39" customWidth="1"/>
-    <col min="11284" max="11284" width="10.5546875" style="39" customWidth="1"/>
-    <col min="11285" max="11285" width="13.5546875" style="39" customWidth="1"/>
-    <col min="11286" max="11286" width="11.109375" style="39" customWidth="1"/>
-    <col min="11287" max="11287" width="11.88671875" style="39" customWidth="1"/>
-    <col min="11288" max="11288" width="10.5546875" style="39" customWidth="1"/>
-    <col min="11289" max="11289" width="10.6640625" style="39" customWidth="1"/>
-    <col min="11290" max="11290" width="10.5546875" style="39" customWidth="1"/>
-    <col min="11291" max="11291" width="13.5546875" style="39" customWidth="1"/>
-    <col min="11292" max="11292" width="12.44140625" style="39" customWidth="1"/>
-    <col min="11293" max="11521" width="9.109375" style="39"/>
-    <col min="11522" max="11522" width="30.109375" style="39" customWidth="1"/>
-    <col min="11523" max="11523" width="33.33203125" style="39" customWidth="1"/>
-    <col min="11524" max="11524" width="11" style="39" customWidth="1"/>
-    <col min="11525" max="11525" width="12.5546875" style="39" customWidth="1"/>
-    <col min="11526" max="11526" width="11.5546875" style="39" customWidth="1"/>
-    <col min="11527" max="11527" width="10.6640625" style="39" customWidth="1"/>
-    <col min="11528" max="11528" width="11.33203125" style="39" customWidth="1"/>
-    <col min="11529" max="11529" width="11.109375" style="39" customWidth="1"/>
-    <col min="11530" max="11530" width="11.6640625" style="39" customWidth="1"/>
-    <col min="11531" max="11531" width="11.44140625" style="39" customWidth="1"/>
-    <col min="11532" max="11534" width="10.6640625" style="39" customWidth="1"/>
-    <col min="11535" max="11537" width="10.5546875" style="39" customWidth="1"/>
-    <col min="11538" max="11538" width="11" style="39" customWidth="1"/>
-    <col min="11539" max="11539" width="10.6640625" style="39" customWidth="1"/>
-    <col min="11540" max="11540" width="10.5546875" style="39" customWidth="1"/>
-    <col min="11541" max="11541" width="13.5546875" style="39" customWidth="1"/>
-    <col min="11542" max="11542" width="11.109375" style="39" customWidth="1"/>
-    <col min="11543" max="11543" width="11.88671875" style="39" customWidth="1"/>
-    <col min="11544" max="11544" width="10.5546875" style="39" customWidth="1"/>
-    <col min="11545" max="11545" width="10.6640625" style="39" customWidth="1"/>
-    <col min="11546" max="11546" width="10.5546875" style="39" customWidth="1"/>
-    <col min="11547" max="11547" width="13.5546875" style="39" customWidth="1"/>
-    <col min="11548" max="11548" width="12.44140625" style="39" customWidth="1"/>
-    <col min="11549" max="11777" width="9.109375" style="39"/>
-    <col min="11778" max="11778" width="30.109375" style="39" customWidth="1"/>
-    <col min="11779" max="11779" width="33.33203125" style="39" customWidth="1"/>
-    <col min="11780" max="11780" width="11" style="39" customWidth="1"/>
-    <col min="11781" max="11781" width="12.5546875" style="39" customWidth="1"/>
-    <col min="11782" max="11782" width="11.5546875" style="39" customWidth="1"/>
-    <col min="11783" max="11783" width="10.6640625" style="39" customWidth="1"/>
-    <col min="11784" max="11784" width="11.33203125" style="39" customWidth="1"/>
-    <col min="11785" max="11785" width="11.109375" style="39" customWidth="1"/>
-    <col min="11786" max="11786" width="11.6640625" style="39" customWidth="1"/>
-    <col min="11787" max="11787" width="11.44140625" style="39" customWidth="1"/>
-    <col min="11788" max="11790" width="10.6640625" style="39" customWidth="1"/>
-    <col min="11791" max="11793" width="10.5546875" style="39" customWidth="1"/>
-    <col min="11794" max="11794" width="11" style="39" customWidth="1"/>
-    <col min="11795" max="11795" width="10.6640625" style="39" customWidth="1"/>
-    <col min="11796" max="11796" width="10.5546875" style="39" customWidth="1"/>
-    <col min="11797" max="11797" width="13.5546875" style="39" customWidth="1"/>
-    <col min="11798" max="11798" width="11.109375" style="39" customWidth="1"/>
-    <col min="11799" max="11799" width="11.88671875" style="39" customWidth="1"/>
-    <col min="11800" max="11800" width="10.5546875" style="39" customWidth="1"/>
-    <col min="11801" max="11801" width="10.6640625" style="39" customWidth="1"/>
-    <col min="11802" max="11802" width="10.5546875" style="39" customWidth="1"/>
-    <col min="11803" max="11803" width="13.5546875" style="39" customWidth="1"/>
-    <col min="11804" max="11804" width="12.44140625" style="39" customWidth="1"/>
-    <col min="11805" max="12033" width="9.109375" style="39"/>
-    <col min="12034" max="12034" width="30.109375" style="39" customWidth="1"/>
-    <col min="12035" max="12035" width="33.33203125" style="39" customWidth="1"/>
-    <col min="12036" max="12036" width="11" style="39" customWidth="1"/>
-    <col min="12037" max="12037" width="12.5546875" style="39" customWidth="1"/>
-    <col min="12038" max="12038" width="11.5546875" style="39" customWidth="1"/>
-    <col min="12039" max="12039" width="10.6640625" style="39" customWidth="1"/>
-    <col min="12040" max="12040" width="11.33203125" style="39" customWidth="1"/>
-    <col min="12041" max="12041" width="11.109375" style="39" customWidth="1"/>
-    <col min="12042" max="12042" width="11.6640625" style="39" customWidth="1"/>
-    <col min="12043" max="12043" width="11.44140625" style="39" customWidth="1"/>
-    <col min="12044" max="12046" width="10.6640625" style="39" customWidth="1"/>
-    <col min="12047" max="12049" width="10.5546875" style="39" customWidth="1"/>
-    <col min="12050" max="12050" width="11" style="39" customWidth="1"/>
-    <col min="12051" max="12051" width="10.6640625" style="39" customWidth="1"/>
-    <col min="12052" max="12052" width="10.5546875" style="39" customWidth="1"/>
-    <col min="12053" max="12053" width="13.5546875" style="39" customWidth="1"/>
-    <col min="12054" max="12054" width="11.109375" style="39" customWidth="1"/>
-    <col min="12055" max="12055" width="11.88671875" style="39" customWidth="1"/>
-    <col min="12056" max="12056" width="10.5546875" style="39" customWidth="1"/>
-    <col min="12057" max="12057" width="10.6640625" style="39" customWidth="1"/>
-    <col min="12058" max="12058" width="10.5546875" style="39" customWidth="1"/>
-    <col min="12059" max="12059" width="13.5546875" style="39" customWidth="1"/>
-    <col min="12060" max="12060" width="12.44140625" style="39" customWidth="1"/>
-    <col min="12061" max="12289" width="9.109375" style="39"/>
-    <col min="12290" max="12290" width="30.109375" style="39" customWidth="1"/>
-    <col min="12291" max="12291" width="33.33203125" style="39" customWidth="1"/>
-    <col min="12292" max="12292" width="11" style="39" customWidth="1"/>
-    <col min="12293" max="12293" width="12.5546875" style="39" customWidth="1"/>
-    <col min="12294" max="12294" width="11.5546875" style="39" customWidth="1"/>
-    <col min="12295" max="12295" width="10.6640625" style="39" customWidth="1"/>
-    <col min="12296" max="12296" width="11.33203125" style="39" customWidth="1"/>
-    <col min="12297" max="12297" width="11.109375" style="39" customWidth="1"/>
-    <col min="12298" max="12298" width="11.6640625" style="39" customWidth="1"/>
-    <col min="12299" max="12299" width="11.44140625" style="39" customWidth="1"/>
-    <col min="12300" max="12302" width="10.6640625" style="39" customWidth="1"/>
-    <col min="12303" max="12305" width="10.5546875" style="39" customWidth="1"/>
-    <col min="12306" max="12306" width="11" style="39" customWidth="1"/>
-    <col min="12307" max="12307" width="10.6640625" style="39" customWidth="1"/>
-    <col min="12308" max="12308" width="10.5546875" style="39" customWidth="1"/>
-    <col min="12309" max="12309" width="13.5546875" style="39" customWidth="1"/>
-    <col min="12310" max="12310" width="11.109375" style="39" customWidth="1"/>
-    <col min="12311" max="12311" width="11.88671875" style="39" customWidth="1"/>
-    <col min="12312" max="12312" width="10.5546875" style="39" customWidth="1"/>
-    <col min="12313" max="12313" width="10.6640625" style="39" customWidth="1"/>
-    <col min="12314" max="12314" width="10.5546875" style="39" customWidth="1"/>
-    <col min="12315" max="12315" width="13.5546875" style="39" customWidth="1"/>
-    <col min="12316" max="12316" width="12.44140625" style="39" customWidth="1"/>
-    <col min="12317" max="12545" width="9.109375" style="39"/>
-    <col min="12546" max="12546" width="30.109375" style="39" customWidth="1"/>
-    <col min="12547" max="12547" width="33.33203125" style="39" customWidth="1"/>
-    <col min="12548" max="12548" width="11" style="39" customWidth="1"/>
-    <col min="12549" max="12549" width="12.5546875" style="39" customWidth="1"/>
-    <col min="12550" max="12550" width="11.5546875" style="39" customWidth="1"/>
-    <col min="12551" max="12551" width="10.6640625" style="39" customWidth="1"/>
-    <col min="12552" max="12552" width="11.33203125" style="39" customWidth="1"/>
-    <col min="12553" max="12553" width="11.109375" style="39" customWidth="1"/>
-    <col min="12554" max="12554" width="11.6640625" style="39" customWidth="1"/>
-    <col min="12555" max="12555" width="11.44140625" style="39" customWidth="1"/>
-    <col min="12556" max="12558" width="10.6640625" style="39" customWidth="1"/>
-    <col min="12559" max="12561" width="10.5546875" style="39" customWidth="1"/>
-    <col min="12562" max="12562" width="11" style="39" customWidth="1"/>
-    <col min="12563" max="12563" width="10.6640625" style="39" customWidth="1"/>
-    <col min="12564" max="12564" width="10.5546875" style="39" customWidth="1"/>
-    <col min="12565" max="12565" width="13.5546875" style="39" customWidth="1"/>
-    <col min="12566" max="12566" width="11.109375" style="39" customWidth="1"/>
-    <col min="12567" max="12567" width="11.88671875" style="39" customWidth="1"/>
-    <col min="12568" max="12568" width="10.5546875" style="39" customWidth="1"/>
-    <col min="12569" max="12569" width="10.6640625" style="39" customWidth="1"/>
-    <col min="12570" max="12570" width="10.5546875" style="39" customWidth="1"/>
-    <col min="12571" max="12571" width="13.5546875" style="39" customWidth="1"/>
-    <col min="12572" max="12572" width="12.44140625" style="39" customWidth="1"/>
-    <col min="12573" max="12801" width="9.109375" style="39"/>
-    <col min="12802" max="12802" width="30.109375" style="39" customWidth="1"/>
-    <col min="12803" max="12803" width="33.33203125" style="39" customWidth="1"/>
-    <col min="12804" max="12804" width="11" style="39" customWidth="1"/>
-    <col min="12805" max="12805" width="12.5546875" style="39" customWidth="1"/>
-    <col min="12806" max="12806" width="11.5546875" style="39" customWidth="1"/>
-    <col min="12807" max="12807" width="10.6640625" style="39" customWidth="1"/>
-    <col min="12808" max="12808" width="11.33203125" style="39" customWidth="1"/>
-    <col min="12809" max="12809" width="11.109375" style="39" customWidth="1"/>
-    <col min="12810" max="12810" width="11.6640625" style="39" customWidth="1"/>
-    <col min="12811" max="12811" width="11.44140625" style="39" customWidth="1"/>
-    <col min="12812" max="12814" width="10.6640625" style="39" customWidth="1"/>
-    <col min="12815" max="12817" width="10.5546875" style="39" customWidth="1"/>
-    <col min="12818" max="12818" width="11" style="39" customWidth="1"/>
-    <col min="12819" max="12819" width="10.6640625" style="39" customWidth="1"/>
-    <col min="12820" max="12820" width="10.5546875" style="39" customWidth="1"/>
-    <col min="12821" max="12821" width="13.5546875" style="39" customWidth="1"/>
-    <col min="12822" max="12822" width="11.109375" style="39" customWidth="1"/>
-    <col min="12823" max="12823" width="11.88671875" style="39" customWidth="1"/>
-    <col min="12824" max="12824" width="10.5546875" style="39" customWidth="1"/>
-    <col min="12825" max="12825" width="10.6640625" style="39" customWidth="1"/>
-    <col min="12826" max="12826" width="10.5546875" style="39" customWidth="1"/>
-    <col min="12827" max="12827" width="13.5546875" style="39" customWidth="1"/>
-    <col min="12828" max="12828" width="12.44140625" style="39" customWidth="1"/>
-    <col min="12829" max="13057" width="9.109375" style="39"/>
-    <col min="13058" max="13058" width="30.109375" style="39" customWidth="1"/>
-    <col min="13059" max="13059" width="33.33203125" style="39" customWidth="1"/>
-    <col min="13060" max="13060" width="11" style="39" customWidth="1"/>
-    <col min="13061" max="13061" width="12.5546875" style="39" customWidth="1"/>
-    <col min="13062" max="13062" width="11.5546875" style="39" customWidth="1"/>
-    <col min="13063" max="13063" width="10.6640625" style="39" customWidth="1"/>
-    <col min="13064" max="13064" width="11.33203125" style="39" customWidth="1"/>
-    <col min="13065" max="13065" width="11.109375" style="39" customWidth="1"/>
-    <col min="13066" max="13066" width="11.6640625" style="39" customWidth="1"/>
-    <col min="13067" max="13067" width="11.44140625" style="39" customWidth="1"/>
-    <col min="13068" max="13070" width="10.6640625" style="39" customWidth="1"/>
-    <col min="13071" max="13073" width="10.5546875" style="39" customWidth="1"/>
-    <col min="13074" max="13074" width="11" style="39" customWidth="1"/>
-    <col min="13075" max="13075" width="10.6640625" style="39" customWidth="1"/>
-    <col min="13076" max="13076" width="10.5546875" style="39" customWidth="1"/>
-    <col min="13077" max="13077" width="13.5546875" style="39" customWidth="1"/>
-    <col min="13078" max="13078" width="11.109375" style="39" customWidth="1"/>
-    <col min="13079" max="13079" width="11.88671875" style="39" customWidth="1"/>
-    <col min="13080" max="13080" width="10.5546875" style="39" customWidth="1"/>
-    <col min="13081" max="13081" width="10.6640625" style="39" customWidth="1"/>
-    <col min="13082" max="13082" width="10.5546875" style="39" customWidth="1"/>
-    <col min="13083" max="13083" width="13.5546875" style="39" customWidth="1"/>
-    <col min="13084" max="13084" width="12.44140625" style="39" customWidth="1"/>
-    <col min="13085" max="13313" width="9.109375" style="39"/>
-    <col min="13314" max="13314" width="30.109375" style="39" customWidth="1"/>
-    <col min="13315" max="13315" width="33.33203125" style="39" customWidth="1"/>
-    <col min="13316" max="13316" width="11" style="39" customWidth="1"/>
-    <col min="13317" max="13317" width="12.5546875" style="39" customWidth="1"/>
-    <col min="13318" max="13318" width="11.5546875" style="39" customWidth="1"/>
-    <col min="13319" max="13319" width="10.6640625" style="39" customWidth="1"/>
-    <col min="13320" max="13320" width="11.33203125" style="39" customWidth="1"/>
-    <col min="13321" max="13321" width="11.109375" style="39" customWidth="1"/>
-    <col min="13322" max="13322" width="11.6640625" style="39" customWidth="1"/>
-    <col min="13323" max="13323" width="11.44140625" style="39" customWidth="1"/>
-    <col min="13324" max="13326" width="10.6640625" style="39" customWidth="1"/>
-    <col min="13327" max="13329" width="10.5546875" style="39" customWidth="1"/>
-    <col min="13330" max="13330" width="11" style="39" customWidth="1"/>
-    <col min="13331" max="13331" width="10.6640625" style="39" customWidth="1"/>
-    <col min="13332" max="13332" width="10.5546875" style="39" customWidth="1"/>
-    <col min="13333" max="13333" width="13.5546875" style="39" customWidth="1"/>
-    <col min="13334" max="13334" width="11.109375" style="39" customWidth="1"/>
-    <col min="13335" max="13335" width="11.88671875" style="39" customWidth="1"/>
-    <col min="13336" max="13336" width="10.5546875" style="39" customWidth="1"/>
-    <col min="13337" max="13337" width="10.6640625" style="39" customWidth="1"/>
-    <col min="13338" max="13338" width="10.5546875" style="39" customWidth="1"/>
-    <col min="13339" max="13339" width="13.5546875" style="39" customWidth="1"/>
-    <col min="13340" max="13340" width="12.44140625" style="39" customWidth="1"/>
-    <col min="13341" max="13569" width="9.109375" style="39"/>
-    <col min="13570" max="13570" width="30.109375" style="39" customWidth="1"/>
-    <col min="13571" max="13571" width="33.33203125" style="39" customWidth="1"/>
-    <col min="13572" max="13572" width="11" style="39" customWidth="1"/>
-    <col min="13573" max="13573" width="12.5546875" style="39" customWidth="1"/>
-    <col min="13574" max="13574" width="11.5546875" style="39" customWidth="1"/>
-    <col min="13575" max="13575" width="10.6640625" style="39" customWidth="1"/>
-    <col min="13576" max="13576" width="11.33203125" style="39" customWidth="1"/>
-    <col min="13577" max="13577" width="11.109375" style="39" customWidth="1"/>
-    <col min="13578" max="13578" width="11.6640625" style="39" customWidth="1"/>
-    <col min="13579" max="13579" width="11.44140625" style="39" customWidth="1"/>
-    <col min="13580" max="13582" width="10.6640625" style="39" customWidth="1"/>
-    <col min="13583" max="13585" width="10.5546875" style="39" customWidth="1"/>
-    <col min="13586" max="13586" width="11" style="39" customWidth="1"/>
-    <col min="13587" max="13587" width="10.6640625" style="39" customWidth="1"/>
-    <col min="13588" max="13588" width="10.5546875" style="39" customWidth="1"/>
-    <col min="13589" max="13589" width="13.5546875" style="39" customWidth="1"/>
-    <col min="13590" max="13590" width="11.109375" style="39" customWidth="1"/>
-    <col min="13591" max="13591" width="11.88671875" style="39" customWidth="1"/>
-    <col min="13592" max="13592" width="10.5546875" style="39" customWidth="1"/>
-    <col min="13593" max="13593" width="10.6640625" style="39" customWidth="1"/>
-    <col min="13594" max="13594" width="10.5546875" style="39" customWidth="1"/>
-    <col min="13595" max="13595" width="13.5546875" style="39" customWidth="1"/>
-    <col min="13596" max="13596" width="12.44140625" style="39" customWidth="1"/>
-    <col min="13597" max="13825" width="9.109375" style="39"/>
-    <col min="13826" max="13826" width="30.109375" style="39" customWidth="1"/>
-    <col min="13827" max="13827" width="33.33203125" style="39" customWidth="1"/>
-    <col min="13828" max="13828" width="11" style="39" customWidth="1"/>
-    <col min="13829" max="13829" width="12.5546875" style="39" customWidth="1"/>
-    <col min="13830" max="13830" width="11.5546875" style="39" customWidth="1"/>
-    <col min="13831" max="13831" width="10.6640625" style="39" customWidth="1"/>
-    <col min="13832" max="13832" width="11.33203125" style="39" customWidth="1"/>
-    <col min="13833" max="13833" width="11.109375" style="39" customWidth="1"/>
-    <col min="13834" max="13834" width="11.6640625" style="39" customWidth="1"/>
-    <col min="13835" max="13835" width="11.44140625" style="39" customWidth="1"/>
-    <col min="13836" max="13838" width="10.6640625" style="39" customWidth="1"/>
-    <col min="13839" max="13841" width="10.5546875" style="39" customWidth="1"/>
-    <col min="13842" max="13842" width="11" style="39" customWidth="1"/>
-    <col min="13843" max="13843" width="10.6640625" style="39" customWidth="1"/>
-    <col min="13844" max="13844" width="10.5546875" style="39" customWidth="1"/>
-    <col min="13845" max="13845" width="13.5546875" style="39" customWidth="1"/>
-    <col min="13846" max="13846" width="11.109375" style="39" customWidth="1"/>
-    <col min="13847" max="13847" width="11.88671875" style="39" customWidth="1"/>
-    <col min="13848" max="13848" width="10.5546875" style="39" customWidth="1"/>
-    <col min="13849" max="13849" width="10.6640625" style="39" customWidth="1"/>
-    <col min="13850" max="13850" width="10.5546875" style="39" customWidth="1"/>
-    <col min="13851" max="13851" width="13.5546875" style="39" customWidth="1"/>
-    <col min="13852" max="13852" width="12.44140625" style="39" customWidth="1"/>
-    <col min="13853" max="14081" width="9.109375" style="39"/>
-    <col min="14082" max="14082" width="30.109375" style="39" customWidth="1"/>
-    <col min="14083" max="14083" width="33.33203125" style="39" customWidth="1"/>
-    <col min="14084" max="14084" width="11" style="39" customWidth="1"/>
-    <col min="14085" max="14085" width="12.5546875" style="39" customWidth="1"/>
-    <col min="14086" max="14086" width="11.5546875" style="39" customWidth="1"/>
-    <col min="14087" max="14087" width="10.6640625" style="39" customWidth="1"/>
-    <col min="14088" max="14088" width="11.33203125" style="39" customWidth="1"/>
-    <col min="14089" max="14089" width="11.109375" style="39" customWidth="1"/>
-    <col min="14090" max="14090" width="11.6640625" style="39" customWidth="1"/>
-    <col min="14091" max="14091" width="11.44140625" style="39" customWidth="1"/>
-    <col min="14092" max="14094" width="10.6640625" style="39" customWidth="1"/>
-    <col min="14095" max="14097" width="10.5546875" style="39" customWidth="1"/>
-    <col min="14098" max="14098" width="11" style="39" customWidth="1"/>
-    <col min="14099" max="14099" width="10.6640625" style="39" customWidth="1"/>
-    <col min="14100" max="14100" width="10.5546875" style="39" customWidth="1"/>
-    <col min="14101" max="14101" width="13.5546875" style="39" customWidth="1"/>
-    <col min="14102" max="14102" width="11.109375" style="39" customWidth="1"/>
-    <col min="14103" max="14103" width="11.88671875" style="39" customWidth="1"/>
-    <col min="14104" max="14104" width="10.5546875" style="39" customWidth="1"/>
-    <col min="14105" max="14105" width="10.6640625" style="39" customWidth="1"/>
-    <col min="14106" max="14106" width="10.5546875" style="39" customWidth="1"/>
-    <col min="14107" max="14107" width="13.5546875" style="39" customWidth="1"/>
-    <col min="14108" max="14108" width="12.44140625" style="39" customWidth="1"/>
-    <col min="14109" max="14337" width="9.109375" style="39"/>
-    <col min="14338" max="14338" width="30.109375" style="39" customWidth="1"/>
-    <col min="14339" max="14339" width="33.33203125" style="39" customWidth="1"/>
-    <col min="14340" max="14340" width="11" style="39" customWidth="1"/>
-    <col min="14341" max="14341" width="12.5546875" style="39" customWidth="1"/>
-    <col min="14342" max="14342" width="11.5546875" style="39" customWidth="1"/>
-    <col min="14343" max="14343" width="10.6640625" style="39" customWidth="1"/>
-    <col min="14344" max="14344" width="11.33203125" style="39" customWidth="1"/>
-    <col min="14345" max="14345" width="11.109375" style="39" customWidth="1"/>
-    <col min="14346" max="14346" width="11.6640625" style="39" customWidth="1"/>
-    <col min="14347" max="14347" width="11.44140625" style="39" customWidth="1"/>
-    <col min="14348" max="14350" width="10.6640625" style="39" customWidth="1"/>
-    <col min="14351" max="14353" width="10.5546875" style="39" customWidth="1"/>
-    <col min="14354" max="14354" width="11" style="39" customWidth="1"/>
-    <col min="14355" max="14355" width="10.6640625" style="39" customWidth="1"/>
-    <col min="14356" max="14356" width="10.5546875" style="39" customWidth="1"/>
-    <col min="14357" max="14357" width="13.5546875" style="39" customWidth="1"/>
-    <col min="14358" max="14358" width="11.109375" style="39" customWidth="1"/>
-    <col min="14359" max="14359" width="11.88671875" style="39" customWidth="1"/>
-    <col min="14360" max="14360" width="10.5546875" style="39" customWidth="1"/>
-    <col min="14361" max="14361" width="10.6640625" style="39" customWidth="1"/>
-    <col min="14362" max="14362" width="10.5546875" style="39" customWidth="1"/>
-    <col min="14363" max="14363" width="13.5546875" style="39" customWidth="1"/>
-    <col min="14364" max="14364" width="12.44140625" style="39" customWidth="1"/>
-    <col min="14365" max="14593" width="9.109375" style="39"/>
-    <col min="14594" max="14594" width="30.109375" style="39" customWidth="1"/>
-    <col min="14595" max="14595" width="33.33203125" style="39" customWidth="1"/>
-    <col min="14596" max="14596" width="11" style="39" customWidth="1"/>
-    <col min="14597" max="14597" width="12.5546875" style="39" customWidth="1"/>
-    <col min="14598" max="14598" width="11.5546875" style="39" customWidth="1"/>
-    <col min="14599" max="14599" width="10.6640625" style="39" customWidth="1"/>
-    <col min="14600" max="14600" width="11.33203125" style="39" customWidth="1"/>
-    <col min="14601" max="14601" width="11.109375" style="39" customWidth="1"/>
-    <col min="14602" max="14602" width="11.6640625" style="39" customWidth="1"/>
-    <col min="14603" max="14603" width="11.44140625" style="39" customWidth="1"/>
-    <col min="14604" max="14606" width="10.6640625" style="39" customWidth="1"/>
-    <col min="14607" max="14609" width="10.5546875" style="39" customWidth="1"/>
-    <col min="14610" max="14610" width="11" style="39" customWidth="1"/>
-    <col min="14611" max="14611" width="10.6640625" style="39" customWidth="1"/>
-    <col min="14612" max="14612" width="10.5546875" style="39" customWidth="1"/>
-    <col min="14613" max="14613" width="13.5546875" style="39" customWidth="1"/>
-    <col min="14614" max="14614" width="11.109375" style="39" customWidth="1"/>
-    <col min="14615" max="14615" width="11.88671875" style="39" customWidth="1"/>
-    <col min="14616" max="14616" width="10.5546875" style="39" customWidth="1"/>
-    <col min="14617" max="14617" width="10.6640625" style="39" customWidth="1"/>
-    <col min="14618" max="14618" width="10.5546875" style="39" customWidth="1"/>
-    <col min="14619" max="14619" width="13.5546875" style="39" customWidth="1"/>
-    <col min="14620" max="14620" width="12.44140625" style="39" customWidth="1"/>
-    <col min="14621" max="14849" width="9.109375" style="39"/>
-    <col min="14850" max="14850" width="30.109375" style="39" customWidth="1"/>
-    <col min="14851" max="14851" width="33.33203125" style="39" customWidth="1"/>
-    <col min="14852" max="14852" width="11" style="39" customWidth="1"/>
-    <col min="14853" max="14853" width="12.5546875" style="39" customWidth="1"/>
-    <col min="14854" max="14854" width="11.5546875" style="39" customWidth="1"/>
-    <col min="14855" max="14855" width="10.6640625" style="39" customWidth="1"/>
-    <col min="14856" max="14856" width="11.33203125" style="39" customWidth="1"/>
-    <col min="14857" max="14857" width="11.109375" style="39" customWidth="1"/>
-    <col min="14858" max="14858" width="11.6640625" style="39" customWidth="1"/>
-    <col min="14859" max="14859" width="11.44140625" style="39" customWidth="1"/>
-    <col min="14860" max="14862" width="10.6640625" style="39" customWidth="1"/>
-    <col min="14863" max="14865" width="10.5546875" style="39" customWidth="1"/>
-    <col min="14866" max="14866" width="11" style="39" customWidth="1"/>
-    <col min="14867" max="14867" width="10.6640625" style="39" customWidth="1"/>
-    <col min="14868" max="14868" width="10.5546875" style="39" customWidth="1"/>
-    <col min="14869" max="14869" width="13.5546875" style="39" customWidth="1"/>
-    <col min="14870" max="14870" width="11.109375" style="39" customWidth="1"/>
-    <col min="14871" max="14871" width="11.88671875" style="39" customWidth="1"/>
-    <col min="14872" max="14872" width="10.5546875" style="39" customWidth="1"/>
-    <col min="14873" max="14873" width="10.6640625" style="39" customWidth="1"/>
-    <col min="14874" max="14874" width="10.5546875" style="39" customWidth="1"/>
-    <col min="14875" max="14875" width="13.5546875" style="39" customWidth="1"/>
-    <col min="14876" max="14876" width="12.44140625" style="39" customWidth="1"/>
-    <col min="14877" max="15105" width="9.109375" style="39"/>
-    <col min="15106" max="15106" width="30.109375" style="39" customWidth="1"/>
-    <col min="15107" max="15107" width="33.33203125" style="39" customWidth="1"/>
-    <col min="15108" max="15108" width="11" style="39" customWidth="1"/>
-    <col min="15109" max="15109" width="12.5546875" style="39" customWidth="1"/>
-    <col min="15110" max="15110" width="11.5546875" style="39" customWidth="1"/>
-    <col min="15111" max="15111" width="10.6640625" style="39" customWidth="1"/>
-    <col min="15112" max="15112" width="11.33203125" style="39" customWidth="1"/>
-    <col min="15113" max="15113" width="11.109375" style="39" customWidth="1"/>
-    <col min="15114" max="15114" width="11.6640625" style="39" customWidth="1"/>
-    <col min="15115" max="15115" width="11.44140625" style="39" customWidth="1"/>
-    <col min="15116" max="15118" width="10.6640625" style="39" customWidth="1"/>
-    <col min="15119" max="15121" width="10.5546875" style="39" customWidth="1"/>
-    <col min="15122" max="15122" width="11" style="39" customWidth="1"/>
-    <col min="15123" max="15123" width="10.6640625" style="39" customWidth="1"/>
-    <col min="15124" max="15124" width="10.5546875" style="39" customWidth="1"/>
-    <col min="15125" max="15125" width="13.5546875" style="39" customWidth="1"/>
-    <col min="15126" max="15126" width="11.109375" style="39" customWidth="1"/>
-    <col min="15127" max="15127" width="11.88671875" style="39" customWidth="1"/>
-    <col min="15128" max="15128" width="10.5546875" style="39" customWidth="1"/>
-    <col min="15129" max="15129" width="10.6640625" style="39" customWidth="1"/>
-    <col min="15130" max="15130" width="10.5546875" style="39" customWidth="1"/>
-    <col min="15131" max="15131" width="13.5546875" style="39" customWidth="1"/>
-    <col min="15132" max="15132" width="12.44140625" style="39" customWidth="1"/>
-    <col min="15133" max="15361" width="9.109375" style="39"/>
-    <col min="15362" max="15362" width="30.109375" style="39" customWidth="1"/>
-    <col min="15363" max="15363" width="33.33203125" style="39" customWidth="1"/>
-    <col min="15364" max="15364" width="11" style="39" customWidth="1"/>
-    <col min="15365" max="15365" width="12.5546875" style="39" customWidth="1"/>
-    <col min="15366" max="15366" width="11.5546875" style="39" customWidth="1"/>
-    <col min="15367" max="15367" width="10.6640625" style="39" customWidth="1"/>
-    <col min="15368" max="15368" width="11.33203125" style="39" customWidth="1"/>
-    <col min="15369" max="15369" width="11.109375" style="39" customWidth="1"/>
-    <col min="15370" max="15370" width="11.6640625" style="39" customWidth="1"/>
-    <col min="15371" max="15371" width="11.44140625" style="39" customWidth="1"/>
-    <col min="15372" max="15374" width="10.6640625" style="39" customWidth="1"/>
-    <col min="15375" max="15377" width="10.5546875" style="39" customWidth="1"/>
-    <col min="15378" max="15378" width="11" style="39" customWidth="1"/>
-    <col min="15379" max="15379" width="10.6640625" style="39" customWidth="1"/>
-    <col min="15380" max="15380" width="10.5546875" style="39" customWidth="1"/>
-    <col min="15381" max="15381" width="13.5546875" style="39" customWidth="1"/>
-    <col min="15382" max="15382" width="11.109375" style="39" customWidth="1"/>
-    <col min="15383" max="15383" width="11.88671875" style="39" customWidth="1"/>
-    <col min="15384" max="15384" width="10.5546875" style="39" customWidth="1"/>
-    <col min="15385" max="15385" width="10.6640625" style="39" customWidth="1"/>
-    <col min="15386" max="15386" width="10.5546875" style="39" customWidth="1"/>
-    <col min="15387" max="15387" width="13.5546875" style="39" customWidth="1"/>
-    <col min="15388" max="15388" width="12.44140625" style="39" customWidth="1"/>
-    <col min="15389" max="15617" width="9.109375" style="39"/>
-    <col min="15618" max="15618" width="30.109375" style="39" customWidth="1"/>
-    <col min="15619" max="15619" width="33.33203125" style="39" customWidth="1"/>
-    <col min="15620" max="15620" width="11" style="39" customWidth="1"/>
-    <col min="15621" max="15621" width="12.5546875" style="39" customWidth="1"/>
-    <col min="15622" max="15622" width="11.5546875" style="39" customWidth="1"/>
-    <col min="15623" max="15623" width="10.6640625" style="39" customWidth="1"/>
-    <col min="15624" max="15624" width="11.33203125" style="39" customWidth="1"/>
-    <col min="15625" max="15625" width="11.109375" style="39" customWidth="1"/>
-    <col min="15626" max="15626" width="11.6640625" style="39" customWidth="1"/>
-    <col min="15627" max="15627" width="11.44140625" style="39" customWidth="1"/>
-    <col min="15628" max="15630" width="10.6640625" style="39" customWidth="1"/>
-    <col min="15631" max="15633" width="10.5546875" style="39" customWidth="1"/>
-    <col min="15634" max="15634" width="11" style="39" customWidth="1"/>
-    <col min="15635" max="15635" width="10.6640625" style="39" customWidth="1"/>
-    <col min="15636" max="15636" width="10.5546875" style="39" customWidth="1"/>
-    <col min="15637" max="15637" width="13.5546875" style="39" customWidth="1"/>
-    <col min="15638" max="15638" width="11.109375" style="39" customWidth="1"/>
-    <col min="15639" max="15639" width="11.88671875" style="39" customWidth="1"/>
-    <col min="15640" max="15640" width="10.5546875" style="39" customWidth="1"/>
-    <col min="15641" max="15641" width="10.6640625" style="39" customWidth="1"/>
-    <col min="15642" max="15642" width="10.5546875" style="39" customWidth="1"/>
-    <col min="15643" max="15643" width="13.5546875" style="39" customWidth="1"/>
-    <col min="15644" max="15644" width="12.44140625" style="39" customWidth="1"/>
-    <col min="15645" max="15873" width="9.109375" style="39"/>
-    <col min="15874" max="15874" width="30.109375" style="39" customWidth="1"/>
-    <col min="15875" max="15875" width="33.33203125" style="39" customWidth="1"/>
-    <col min="15876" max="15876" width="11" style="39" customWidth="1"/>
-    <col min="15877" max="15877" width="12.5546875" style="39" customWidth="1"/>
-    <col min="15878" max="15878" width="11.5546875" style="39" customWidth="1"/>
-    <col min="15879" max="15879" width="10.6640625" style="39" customWidth="1"/>
-    <col min="15880" max="15880" width="11.33203125" style="39" customWidth="1"/>
-    <col min="15881" max="15881" width="11.109375" style="39" customWidth="1"/>
-    <col min="15882" max="15882" width="11.6640625" style="39" customWidth="1"/>
-    <col min="15883" max="15883" width="11.44140625" style="39" customWidth="1"/>
-    <col min="15884" max="15886" width="10.6640625" style="39" customWidth="1"/>
-    <col min="15887" max="15889" width="10.5546875" style="39" customWidth="1"/>
-    <col min="15890" max="15890" width="11" style="39" customWidth="1"/>
-    <col min="15891" max="15891" width="10.6640625" style="39" customWidth="1"/>
-    <col min="15892" max="15892" width="10.5546875" style="39" customWidth="1"/>
-    <col min="15893" max="15893" width="13.5546875" style="39" customWidth="1"/>
-    <col min="15894" max="15894" width="11.109375" style="39" customWidth="1"/>
-    <col min="15895" max="15895" width="11.88671875" style="39" customWidth="1"/>
-    <col min="15896" max="15896" width="10.5546875" style="39" customWidth="1"/>
-    <col min="15897" max="15897" width="10.6640625" style="39" customWidth="1"/>
-    <col min="15898" max="15898" width="10.5546875" style="39" customWidth="1"/>
-    <col min="15899" max="15899" width="13.5546875" style="39" customWidth="1"/>
-    <col min="15900" max="15900" width="12.44140625" style="39" customWidth="1"/>
-    <col min="15901" max="16129" width="9.109375" style="39"/>
-    <col min="16130" max="16130" width="30.109375" style="39" customWidth="1"/>
-    <col min="16131" max="16131" width="33.33203125" style="39" customWidth="1"/>
-    <col min="16132" max="16132" width="11" style="39" customWidth="1"/>
-    <col min="16133" max="16133" width="12.5546875" style="39" customWidth="1"/>
-    <col min="16134" max="16134" width="11.5546875" style="39" customWidth="1"/>
-    <col min="16135" max="16135" width="10.6640625" style="39" customWidth="1"/>
-    <col min="16136" max="16136" width="11.33203125" style="39" customWidth="1"/>
-    <col min="16137" max="16137" width="11.109375" style="39" customWidth="1"/>
-    <col min="16138" max="16138" width="11.6640625" style="39" customWidth="1"/>
-    <col min="16139" max="16139" width="11.44140625" style="39" customWidth="1"/>
-    <col min="16140" max="16142" width="10.6640625" style="39" customWidth="1"/>
-    <col min="16143" max="16145" width="10.5546875" style="39" customWidth="1"/>
-    <col min="16146" max="16146" width="11" style="39" customWidth="1"/>
-    <col min="16147" max="16147" width="10.6640625" style="39" customWidth="1"/>
-    <col min="16148" max="16148" width="10.5546875" style="39" customWidth="1"/>
-    <col min="16149" max="16149" width="13.5546875" style="39" customWidth="1"/>
-    <col min="16150" max="16150" width="11.109375" style="39" customWidth="1"/>
-    <col min="16151" max="16151" width="11.88671875" style="39" customWidth="1"/>
-    <col min="16152" max="16152" width="10.5546875" style="39" customWidth="1"/>
-    <col min="16153" max="16153" width="10.6640625" style="39" customWidth="1"/>
-    <col min="16154" max="16154" width="10.5546875" style="39" customWidth="1"/>
-    <col min="16155" max="16155" width="13.5546875" style="39" customWidth="1"/>
-    <col min="16156" max="16156" width="12.44140625" style="39" customWidth="1"/>
-    <col min="16157" max="16384" width="9.109375" style="39"/>
+    <col min="18" max="18" width="3" style="8" customWidth="1"/>
+    <col min="19" max="19" width="6" style="8" customWidth="1"/>
+    <col min="20" max="20" width="4.44140625" style="8" customWidth="1"/>
+    <col min="21" max="21" width="4.88671875" style="8" customWidth="1"/>
+    <col min="22" max="22" width="5" style="8" customWidth="1"/>
+    <col min="23" max="23" width="3.6640625" style="8" customWidth="1"/>
+    <col min="24" max="24" width="5.109375" style="8" customWidth="1"/>
+    <col min="25" max="25" width="5.6640625" style="8" customWidth="1"/>
+    <col min="26" max="26" width="4.5546875" style="8" customWidth="1"/>
+    <col min="27" max="27" width="4.88671875" style="8" customWidth="1"/>
+    <col min="28" max="28" width="4" style="8" customWidth="1"/>
+    <col min="29" max="29" width="5.88671875" style="8" customWidth="1"/>
+    <col min="30" max="30" width="6.109375" style="8" customWidth="1"/>
+    <col min="31" max="259" width="9.109375" style="38"/>
+    <col min="260" max="260" width="30.109375" style="38" customWidth="1"/>
+    <col min="261" max="261" width="33.33203125" style="38" customWidth="1"/>
+    <col min="262" max="262" width="11" style="38" customWidth="1"/>
+    <col min="263" max="263" width="12.5546875" style="38" customWidth="1"/>
+    <col min="264" max="264" width="11.5546875" style="38" customWidth="1"/>
+    <col min="265" max="265" width="10.6640625" style="38" customWidth="1"/>
+    <col min="266" max="266" width="11.33203125" style="38" customWidth="1"/>
+    <col min="267" max="267" width="11.109375" style="38" customWidth="1"/>
+    <col min="268" max="268" width="11.6640625" style="38" customWidth="1"/>
+    <col min="269" max="269" width="11.44140625" style="38" customWidth="1"/>
+    <col min="270" max="272" width="10.6640625" style="38" customWidth="1"/>
+    <col min="273" max="275" width="10.5546875" style="38" customWidth="1"/>
+    <col min="276" max="276" width="11" style="38" customWidth="1"/>
+    <col min="277" max="277" width="10.6640625" style="38" customWidth="1"/>
+    <col min="278" max="278" width="10.5546875" style="38" customWidth="1"/>
+    <col min="279" max="279" width="13.5546875" style="38" customWidth="1"/>
+    <col min="280" max="280" width="11.109375" style="38" customWidth="1"/>
+    <col min="281" max="281" width="11.88671875" style="38" customWidth="1"/>
+    <col min="282" max="282" width="10.5546875" style="38" customWidth="1"/>
+    <col min="283" max="283" width="10.6640625" style="38" customWidth="1"/>
+    <col min="284" max="284" width="10.5546875" style="38" customWidth="1"/>
+    <col min="285" max="285" width="13.5546875" style="38" customWidth="1"/>
+    <col min="286" max="286" width="12.44140625" style="38" customWidth="1"/>
+    <col min="287" max="515" width="9.109375" style="38"/>
+    <col min="516" max="516" width="30.109375" style="38" customWidth="1"/>
+    <col min="517" max="517" width="33.33203125" style="38" customWidth="1"/>
+    <col min="518" max="518" width="11" style="38" customWidth="1"/>
+    <col min="519" max="519" width="12.5546875" style="38" customWidth="1"/>
+    <col min="520" max="520" width="11.5546875" style="38" customWidth="1"/>
+    <col min="521" max="521" width="10.6640625" style="38" customWidth="1"/>
+    <col min="522" max="522" width="11.33203125" style="38" customWidth="1"/>
+    <col min="523" max="523" width="11.109375" style="38" customWidth="1"/>
+    <col min="524" max="524" width="11.6640625" style="38" customWidth="1"/>
+    <col min="525" max="525" width="11.44140625" style="38" customWidth="1"/>
+    <col min="526" max="528" width="10.6640625" style="38" customWidth="1"/>
+    <col min="529" max="531" width="10.5546875" style="38" customWidth="1"/>
+    <col min="532" max="532" width="11" style="38" customWidth="1"/>
+    <col min="533" max="533" width="10.6640625" style="38" customWidth="1"/>
+    <col min="534" max="534" width="10.5546875" style="38" customWidth="1"/>
+    <col min="535" max="535" width="13.5546875" style="38" customWidth="1"/>
+    <col min="536" max="536" width="11.109375" style="38" customWidth="1"/>
+    <col min="537" max="537" width="11.88671875" style="38" customWidth="1"/>
+    <col min="538" max="538" width="10.5546875" style="38" customWidth="1"/>
+    <col min="539" max="539" width="10.6640625" style="38" customWidth="1"/>
+    <col min="540" max="540" width="10.5546875" style="38" customWidth="1"/>
+    <col min="541" max="541" width="13.5546875" style="38" customWidth="1"/>
+    <col min="542" max="542" width="12.44140625" style="38" customWidth="1"/>
+    <col min="543" max="771" width="9.109375" style="38"/>
+    <col min="772" max="772" width="30.109375" style="38" customWidth="1"/>
+    <col min="773" max="773" width="33.33203125" style="38" customWidth="1"/>
+    <col min="774" max="774" width="11" style="38" customWidth="1"/>
+    <col min="775" max="775" width="12.5546875" style="38" customWidth="1"/>
+    <col min="776" max="776" width="11.5546875" style="38" customWidth="1"/>
+    <col min="777" max="777" width="10.6640625" style="38" customWidth="1"/>
+    <col min="778" max="778" width="11.33203125" style="38" customWidth="1"/>
+    <col min="779" max="779" width="11.109375" style="38" customWidth="1"/>
+    <col min="780" max="780" width="11.6640625" style="38" customWidth="1"/>
+    <col min="781" max="781" width="11.44140625" style="38" customWidth="1"/>
+    <col min="782" max="784" width="10.6640625" style="38" customWidth="1"/>
+    <col min="785" max="787" width="10.5546875" style="38" customWidth="1"/>
+    <col min="788" max="788" width="11" style="38" customWidth="1"/>
+    <col min="789" max="789" width="10.6640625" style="38" customWidth="1"/>
+    <col min="790" max="790" width="10.5546875" style="38" customWidth="1"/>
+    <col min="791" max="791" width="13.5546875" style="38" customWidth="1"/>
+    <col min="792" max="792" width="11.109375" style="38" customWidth="1"/>
+    <col min="793" max="793" width="11.88671875" style="38" customWidth="1"/>
+    <col min="794" max="794" width="10.5546875" style="38" customWidth="1"/>
+    <col min="795" max="795" width="10.6640625" style="38" customWidth="1"/>
+    <col min="796" max="796" width="10.5546875" style="38" customWidth="1"/>
+    <col min="797" max="797" width="13.5546875" style="38" customWidth="1"/>
+    <col min="798" max="798" width="12.44140625" style="38" customWidth="1"/>
+    <col min="799" max="1027" width="9.109375" style="38"/>
+    <col min="1028" max="1028" width="30.109375" style="38" customWidth="1"/>
+    <col min="1029" max="1029" width="33.33203125" style="38" customWidth="1"/>
+    <col min="1030" max="1030" width="11" style="38" customWidth="1"/>
+    <col min="1031" max="1031" width="12.5546875" style="38" customWidth="1"/>
+    <col min="1032" max="1032" width="11.5546875" style="38" customWidth="1"/>
+    <col min="1033" max="1033" width="10.6640625" style="38" customWidth="1"/>
+    <col min="1034" max="1034" width="11.33203125" style="38" customWidth="1"/>
+    <col min="1035" max="1035" width="11.109375" style="38" customWidth="1"/>
+    <col min="1036" max="1036" width="11.6640625" style="38" customWidth="1"/>
+    <col min="1037" max="1037" width="11.44140625" style="38" customWidth="1"/>
+    <col min="1038" max="1040" width="10.6640625" style="38" customWidth="1"/>
+    <col min="1041" max="1043" width="10.5546875" style="38" customWidth="1"/>
+    <col min="1044" max="1044" width="11" style="38" customWidth="1"/>
+    <col min="1045" max="1045" width="10.6640625" style="38" customWidth="1"/>
+    <col min="1046" max="1046" width="10.5546875" style="38" customWidth="1"/>
+    <col min="1047" max="1047" width="13.5546875" style="38" customWidth="1"/>
+    <col min="1048" max="1048" width="11.109375" style="38" customWidth="1"/>
+    <col min="1049" max="1049" width="11.88671875" style="38" customWidth="1"/>
+    <col min="1050" max="1050" width="10.5546875" style="38" customWidth="1"/>
+    <col min="1051" max="1051" width="10.6640625" style="38" customWidth="1"/>
+    <col min="1052" max="1052" width="10.5546875" style="38" customWidth="1"/>
+    <col min="1053" max="1053" width="13.5546875" style="38" customWidth="1"/>
+    <col min="1054" max="1054" width="12.44140625" style="38" customWidth="1"/>
+    <col min="1055" max="1283" width="9.109375" style="38"/>
+    <col min="1284" max="1284" width="30.109375" style="38" customWidth="1"/>
+    <col min="1285" max="1285" width="33.33203125" style="38" customWidth="1"/>
+    <col min="1286" max="1286" width="11" style="38" customWidth="1"/>
+    <col min="1287" max="1287" width="12.5546875" style="38" customWidth="1"/>
+    <col min="1288" max="1288" width="11.5546875" style="38" customWidth="1"/>
+    <col min="1289" max="1289" width="10.6640625" style="38" customWidth="1"/>
+    <col min="1290" max="1290" width="11.33203125" style="38" customWidth="1"/>
+    <col min="1291" max="1291" width="11.109375" style="38" customWidth="1"/>
+    <col min="1292" max="1292" width="11.6640625" style="38" customWidth="1"/>
+    <col min="1293" max="1293" width="11.44140625" style="38" customWidth="1"/>
+    <col min="1294" max="1296" width="10.6640625" style="38" customWidth="1"/>
+    <col min="1297" max="1299" width="10.5546875" style="38" customWidth="1"/>
+    <col min="1300" max="1300" width="11" style="38" customWidth="1"/>
+    <col min="1301" max="1301" width="10.6640625" style="38" customWidth="1"/>
+    <col min="1302" max="1302" width="10.5546875" style="38" customWidth="1"/>
+    <col min="1303" max="1303" width="13.5546875" style="38" customWidth="1"/>
+    <col min="1304" max="1304" width="11.109375" style="38" customWidth="1"/>
+    <col min="1305" max="1305" width="11.88671875" style="38" customWidth="1"/>
+    <col min="1306" max="1306" width="10.5546875" style="38" customWidth="1"/>
+    <col min="1307" max="1307" width="10.6640625" style="38" customWidth="1"/>
+    <col min="1308" max="1308" width="10.5546875" style="38" customWidth="1"/>
+    <col min="1309" max="1309" width="13.5546875" style="38" customWidth="1"/>
+    <col min="1310" max="1310" width="12.44140625" style="38" customWidth="1"/>
+    <col min="1311" max="1539" width="9.109375" style="38"/>
+    <col min="1540" max="1540" width="30.109375" style="38" customWidth="1"/>
+    <col min="1541" max="1541" width="33.33203125" style="38" customWidth="1"/>
+    <col min="1542" max="1542" width="11" style="38" customWidth="1"/>
+    <col min="1543" max="1543" width="12.5546875" style="38" customWidth="1"/>
+    <col min="1544" max="1544" width="11.5546875" style="38" customWidth="1"/>
+    <col min="1545" max="1545" width="10.6640625" style="38" customWidth="1"/>
+    <col min="1546" max="1546" width="11.33203125" style="38" customWidth="1"/>
+    <col min="1547" max="1547" width="11.109375" style="38" customWidth="1"/>
+    <col min="1548" max="1548" width="11.6640625" style="38" customWidth="1"/>
+    <col min="1549" max="1549" width="11.44140625" style="38" customWidth="1"/>
+    <col min="1550" max="1552" width="10.6640625" style="38" customWidth="1"/>
+    <col min="1553" max="1555" width="10.5546875" style="38" customWidth="1"/>
+    <col min="1556" max="1556" width="11" style="38" customWidth="1"/>
+    <col min="1557" max="1557" width="10.6640625" style="38" customWidth="1"/>
+    <col min="1558" max="1558" width="10.5546875" style="38" customWidth="1"/>
+    <col min="1559" max="1559" width="13.5546875" style="38" customWidth="1"/>
+    <col min="1560" max="1560" width="11.109375" style="38" customWidth="1"/>
+    <col min="1561" max="1561" width="11.88671875" style="38" customWidth="1"/>
+    <col min="1562" max="1562" width="10.5546875" style="38" customWidth="1"/>
+    <col min="1563" max="1563" width="10.6640625" style="38" customWidth="1"/>
+    <col min="1564" max="1564" width="10.5546875" style="38" customWidth="1"/>
+    <col min="1565" max="1565" width="13.5546875" style="38" customWidth="1"/>
+    <col min="1566" max="1566" width="12.44140625" style="38" customWidth="1"/>
+    <col min="1567" max="1795" width="9.109375" style="38"/>
+    <col min="1796" max="1796" width="30.109375" style="38" customWidth="1"/>
+    <col min="1797" max="1797" width="33.33203125" style="38" customWidth="1"/>
+    <col min="1798" max="1798" width="11" style="38" customWidth="1"/>
+    <col min="1799" max="1799" width="12.5546875" style="38" customWidth="1"/>
+    <col min="1800" max="1800" width="11.5546875" style="38" customWidth="1"/>
+    <col min="1801" max="1801" width="10.6640625" style="38" customWidth="1"/>
+    <col min="1802" max="1802" width="11.33203125" style="38" customWidth="1"/>
+    <col min="1803" max="1803" width="11.109375" style="38" customWidth="1"/>
+    <col min="1804" max="1804" width="11.6640625" style="38" customWidth="1"/>
+    <col min="1805" max="1805" width="11.44140625" style="38" customWidth="1"/>
+    <col min="1806" max="1808" width="10.6640625" style="38" customWidth="1"/>
+    <col min="1809" max="1811" width="10.5546875" style="38" customWidth="1"/>
+    <col min="1812" max="1812" width="11" style="38" customWidth="1"/>
+    <col min="1813" max="1813" width="10.6640625" style="38" customWidth="1"/>
+    <col min="1814" max="1814" width="10.5546875" style="38" customWidth="1"/>
+    <col min="1815" max="1815" width="13.5546875" style="38" customWidth="1"/>
+    <col min="1816" max="1816" width="11.109375" style="38" customWidth="1"/>
+    <col min="1817" max="1817" width="11.88671875" style="38" customWidth="1"/>
+    <col min="1818" max="1818" width="10.5546875" style="38" customWidth="1"/>
+    <col min="1819" max="1819" width="10.6640625" style="38" customWidth="1"/>
+    <col min="1820" max="1820" width="10.5546875" style="38" customWidth="1"/>
+    <col min="1821" max="1821" width="13.5546875" style="38" customWidth="1"/>
+    <col min="1822" max="1822" width="12.44140625" style="38" customWidth="1"/>
+    <col min="1823" max="2051" width="9.109375" style="38"/>
+    <col min="2052" max="2052" width="30.109375" style="38" customWidth="1"/>
+    <col min="2053" max="2053" width="33.33203125" style="38" customWidth="1"/>
+    <col min="2054" max="2054" width="11" style="38" customWidth="1"/>
+    <col min="2055" max="2055" width="12.5546875" style="38" customWidth="1"/>
+    <col min="2056" max="2056" width="11.5546875" style="38" customWidth="1"/>
+    <col min="2057" max="2057" width="10.6640625" style="38" customWidth="1"/>
+    <col min="2058" max="2058" width="11.33203125" style="38" customWidth="1"/>
+    <col min="2059" max="2059" width="11.109375" style="38" customWidth="1"/>
+    <col min="2060" max="2060" width="11.6640625" style="38" customWidth="1"/>
+    <col min="2061" max="2061" width="11.44140625" style="38" customWidth="1"/>
+    <col min="2062" max="2064" width="10.6640625" style="38" customWidth="1"/>
+    <col min="2065" max="2067" width="10.5546875" style="38" customWidth="1"/>
+    <col min="2068" max="2068" width="11" style="38" customWidth="1"/>
+    <col min="2069" max="2069" width="10.6640625" style="38" customWidth="1"/>
+    <col min="2070" max="2070" width="10.5546875" style="38" customWidth="1"/>
+    <col min="2071" max="2071" width="13.5546875" style="38" customWidth="1"/>
+    <col min="2072" max="2072" width="11.109375" style="38" customWidth="1"/>
+    <col min="2073" max="2073" width="11.88671875" style="38" customWidth="1"/>
+    <col min="2074" max="2074" width="10.5546875" style="38" customWidth="1"/>
+    <col min="2075" max="2075" width="10.6640625" style="38" customWidth="1"/>
+    <col min="2076" max="2076" width="10.5546875" style="38" customWidth="1"/>
+    <col min="2077" max="2077" width="13.5546875" style="38" customWidth="1"/>
+    <col min="2078" max="2078" width="12.44140625" style="38" customWidth="1"/>
+    <col min="2079" max="2307" width="9.109375" style="38"/>
+    <col min="2308" max="2308" width="30.109375" style="38" customWidth="1"/>
+    <col min="2309" max="2309" width="33.33203125" style="38" customWidth="1"/>
+    <col min="2310" max="2310" width="11" style="38" customWidth="1"/>
+    <col min="2311" max="2311" width="12.5546875" style="38" customWidth="1"/>
+    <col min="2312" max="2312" width="11.5546875" style="38" customWidth="1"/>
+    <col min="2313" max="2313" width="10.6640625" style="38" customWidth="1"/>
+    <col min="2314" max="2314" width="11.33203125" style="38" customWidth="1"/>
+    <col min="2315" max="2315" width="11.109375" style="38" customWidth="1"/>
+    <col min="2316" max="2316" width="11.6640625" style="38" customWidth="1"/>
+    <col min="2317" max="2317" width="11.44140625" style="38" customWidth="1"/>
+    <col min="2318" max="2320" width="10.6640625" style="38" customWidth="1"/>
+    <col min="2321" max="2323" width="10.5546875" style="38" customWidth="1"/>
+    <col min="2324" max="2324" width="11" style="38" customWidth="1"/>
+    <col min="2325" max="2325" width="10.6640625" style="38" customWidth="1"/>
+    <col min="2326" max="2326" width="10.5546875" style="38" customWidth="1"/>
+    <col min="2327" max="2327" width="13.5546875" style="38" customWidth="1"/>
+    <col min="2328" max="2328" width="11.109375" style="38" customWidth="1"/>
+    <col min="2329" max="2329" width="11.88671875" style="38" customWidth="1"/>
+    <col min="2330" max="2330" width="10.5546875" style="38" customWidth="1"/>
+    <col min="2331" max="2331" width="10.6640625" style="38" customWidth="1"/>
+    <col min="2332" max="2332" width="10.5546875" style="38" customWidth="1"/>
+    <col min="2333" max="2333" width="13.5546875" style="38" customWidth="1"/>
+    <col min="2334" max="2334" width="12.44140625" style="38" customWidth="1"/>
+    <col min="2335" max="2563" width="9.109375" style="38"/>
+    <col min="2564" max="2564" width="30.109375" style="38" customWidth="1"/>
+    <col min="2565" max="2565" width="33.33203125" style="38" customWidth="1"/>
+    <col min="2566" max="2566" width="11" style="38" customWidth="1"/>
+    <col min="2567" max="2567" width="12.5546875" style="38" customWidth="1"/>
+    <col min="2568" max="2568" width="11.5546875" style="38" customWidth="1"/>
+    <col min="2569" max="2569" width="10.6640625" style="38" customWidth="1"/>
+    <col min="2570" max="2570" width="11.33203125" style="38" customWidth="1"/>
+    <col min="2571" max="2571" width="11.109375" style="38" customWidth="1"/>
+    <col min="2572" max="2572" width="11.6640625" style="38" customWidth="1"/>
+    <col min="2573" max="2573" width="11.44140625" style="38" customWidth="1"/>
+    <col min="2574" max="2576" width="10.6640625" style="38" customWidth="1"/>
+    <col min="2577" max="2579" width="10.5546875" style="38" customWidth="1"/>
+    <col min="2580" max="2580" width="11" style="38" customWidth="1"/>
+    <col min="2581" max="2581" width="10.6640625" style="38" customWidth="1"/>
+    <col min="2582" max="2582" width="10.5546875" style="38" customWidth="1"/>
+    <col min="2583" max="2583" width="13.5546875" style="38" customWidth="1"/>
+    <col min="2584" max="2584" width="11.109375" style="38" customWidth="1"/>
+    <col min="2585" max="2585" width="11.88671875" style="38" customWidth="1"/>
+    <col min="2586" max="2586" width="10.5546875" style="38" customWidth="1"/>
+    <col min="2587" max="2587" width="10.6640625" style="38" customWidth="1"/>
+    <col min="2588" max="2588" width="10.5546875" style="38" customWidth="1"/>
+    <col min="2589" max="2589" width="13.5546875" style="38" customWidth="1"/>
+    <col min="2590" max="2590" width="12.44140625" style="38" customWidth="1"/>
+    <col min="2591" max="2819" width="9.109375" style="38"/>
+    <col min="2820" max="2820" width="30.109375" style="38" customWidth="1"/>
+    <col min="2821" max="2821" width="33.33203125" style="38" customWidth="1"/>
+    <col min="2822" max="2822" width="11" style="38" customWidth="1"/>
+    <col min="2823" max="2823" width="12.5546875" style="38" customWidth="1"/>
+    <col min="2824" max="2824" width="11.5546875" style="38" customWidth="1"/>
+    <col min="2825" max="2825" width="10.6640625" style="38" customWidth="1"/>
+    <col min="2826" max="2826" width="11.33203125" style="38" customWidth="1"/>
+    <col min="2827" max="2827" width="11.109375" style="38" customWidth="1"/>
+    <col min="2828" max="2828" width="11.6640625" style="38" customWidth="1"/>
+    <col min="2829" max="2829" width="11.44140625" style="38" customWidth="1"/>
+    <col min="2830" max="2832" width="10.6640625" style="38" customWidth="1"/>
+    <col min="2833" max="2835" width="10.5546875" style="38" customWidth="1"/>
+    <col min="2836" max="2836" width="11" style="38" customWidth="1"/>
+    <col min="2837" max="2837" width="10.6640625" style="38" customWidth="1"/>
+    <col min="2838" max="2838" width="10.5546875" style="38" customWidth="1"/>
+    <col min="2839" max="2839" width="13.5546875" style="38" customWidth="1"/>
+    <col min="2840" max="2840" width="11.109375" style="38" customWidth="1"/>
+    <col min="2841" max="2841" width="11.88671875" style="38" customWidth="1"/>
+    <col min="2842" max="2842" width="10.5546875" style="38" customWidth="1"/>
+    <col min="2843" max="2843" width="10.6640625" style="38" customWidth="1"/>
+    <col min="2844" max="2844" width="10.5546875" style="38" customWidth="1"/>
+    <col min="2845" max="2845" width="13.5546875" style="38" customWidth="1"/>
+    <col min="2846" max="2846" width="12.44140625" style="38" customWidth="1"/>
+    <col min="2847" max="3075" width="9.109375" style="38"/>
+    <col min="3076" max="3076" width="30.109375" style="38" customWidth="1"/>
+    <col min="3077" max="3077" width="33.33203125" style="38" customWidth="1"/>
+    <col min="3078" max="3078" width="11" style="38" customWidth="1"/>
+    <col min="3079" max="3079" width="12.5546875" style="38" customWidth="1"/>
+    <col min="3080" max="3080" width="11.5546875" style="38" customWidth="1"/>
+    <col min="3081" max="3081" width="10.6640625" style="38" customWidth="1"/>
+    <col min="3082" max="3082" width="11.33203125" style="38" customWidth="1"/>
+    <col min="3083" max="3083" width="11.109375" style="38" customWidth="1"/>
+    <col min="3084" max="3084" width="11.6640625" style="38" customWidth="1"/>
+    <col min="3085" max="3085" width="11.44140625" style="38" customWidth="1"/>
+    <col min="3086" max="3088" width="10.6640625" style="38" customWidth="1"/>
+    <col min="3089" max="3091" width="10.5546875" style="38" customWidth="1"/>
+    <col min="3092" max="3092" width="11" style="38" customWidth="1"/>
+    <col min="3093" max="3093" width="10.6640625" style="38" customWidth="1"/>
+    <col min="3094" max="3094" width="10.5546875" style="38" customWidth="1"/>
+    <col min="3095" max="3095" width="13.5546875" style="38" customWidth="1"/>
+    <col min="3096" max="3096" width="11.109375" style="38" customWidth="1"/>
+    <col min="3097" max="3097" width="11.88671875" style="38" customWidth="1"/>
+    <col min="3098" max="3098" width="10.5546875" style="38" customWidth="1"/>
+    <col min="3099" max="3099" width="10.6640625" style="38" customWidth="1"/>
+    <col min="3100" max="3100" width="10.5546875" style="38" customWidth="1"/>
+    <col min="3101" max="3101" width="13.5546875" style="38" customWidth="1"/>
+    <col min="3102" max="3102" width="12.44140625" style="38" customWidth="1"/>
+    <col min="3103" max="3331" width="9.109375" style="38"/>
+    <col min="3332" max="3332" width="30.109375" style="38" customWidth="1"/>
+    <col min="3333" max="3333" width="33.33203125" style="38" customWidth="1"/>
+    <col min="3334" max="3334" width="11" style="38" customWidth="1"/>
+    <col min="3335" max="3335" width="12.5546875" style="38" customWidth="1"/>
+    <col min="3336" max="3336" width="11.5546875" style="38" customWidth="1"/>
+    <col min="3337" max="3337" width="10.6640625" style="38" customWidth="1"/>
+    <col min="3338" max="3338" width="11.33203125" style="38" customWidth="1"/>
+    <col min="3339" max="3339" width="11.109375" style="38" customWidth="1"/>
+    <col min="3340" max="3340" width="11.6640625" style="38" customWidth="1"/>
+    <col min="3341" max="3341" width="11.44140625" style="38" customWidth="1"/>
+    <col min="3342" max="3344" width="10.6640625" style="38" customWidth="1"/>
+    <col min="3345" max="3347" width="10.5546875" style="38" customWidth="1"/>
+    <col min="3348" max="3348" width="11" style="38" customWidth="1"/>
+    <col min="3349" max="3349" width="10.6640625" style="38" customWidth="1"/>
+    <col min="3350" max="3350" width="10.5546875" style="38" customWidth="1"/>
+    <col min="3351" max="3351" width="13.5546875" style="38" customWidth="1"/>
+    <col min="3352" max="3352" width="11.109375" style="38" customWidth="1"/>
+    <col min="3353" max="3353" width="11.88671875" style="38" customWidth="1"/>
+    <col min="3354" max="3354" width="10.5546875" style="38" customWidth="1"/>
+    <col min="3355" max="3355" width="10.6640625" style="38" customWidth="1"/>
+    <col min="3356" max="3356" width="10.5546875" style="38" customWidth="1"/>
+    <col min="3357" max="3357" width="13.5546875" style="38" customWidth="1"/>
+    <col min="3358" max="3358" width="12.44140625" style="38" customWidth="1"/>
+    <col min="3359" max="3587" width="9.109375" style="38"/>
+    <col min="3588" max="3588" width="30.109375" style="38" customWidth="1"/>
+    <col min="3589" max="3589" width="33.33203125" style="38" customWidth="1"/>
+    <col min="3590" max="3590" width="11" style="38" customWidth="1"/>
+    <col min="3591" max="3591" width="12.5546875" style="38" customWidth="1"/>
+    <col min="3592" max="3592" width="11.5546875" style="38" customWidth="1"/>
+    <col min="3593" max="3593" width="10.6640625" style="38" customWidth="1"/>
+    <col min="3594" max="3594" width="11.33203125" style="38" customWidth="1"/>
+    <col min="3595" max="3595" width="11.109375" style="38" customWidth="1"/>
+    <col min="3596" max="3596" width="11.6640625" style="38" customWidth="1"/>
+    <col min="3597" max="3597" width="11.44140625" style="38" customWidth="1"/>
+    <col min="3598" max="3600" width="10.6640625" style="38" customWidth="1"/>
+    <col min="3601" max="3603" width="10.5546875" style="38" customWidth="1"/>
+    <col min="3604" max="3604" width="11" style="38" customWidth="1"/>
+    <col min="3605" max="3605" width="10.6640625" style="38" customWidth="1"/>
+    <col min="3606" max="3606" width="10.5546875" style="38" customWidth="1"/>
+    <col min="3607" max="3607" width="13.5546875" style="38" customWidth="1"/>
+    <col min="3608" max="3608" width="11.109375" style="38" customWidth="1"/>
+    <col min="3609" max="3609" width="11.88671875" style="38" customWidth="1"/>
+    <col min="3610" max="3610" width="10.5546875" style="38" customWidth="1"/>
+    <col min="3611" max="3611" width="10.6640625" style="38" customWidth="1"/>
+    <col min="3612" max="3612" width="10.5546875" style="38" customWidth="1"/>
+    <col min="3613" max="3613" width="13.5546875" style="38" customWidth="1"/>
+    <col min="3614" max="3614" width="12.44140625" style="38" customWidth="1"/>
+    <col min="3615" max="3843" width="9.109375" style="38"/>
+    <col min="3844" max="3844" width="30.109375" style="38" customWidth="1"/>
+    <col min="3845" max="3845" width="33.33203125" style="38" customWidth="1"/>
+    <col min="3846" max="3846" width="11" style="38" customWidth="1"/>
+    <col min="3847" max="3847" width="12.5546875" style="38" customWidth="1"/>
+    <col min="3848" max="3848" width="11.5546875" style="38" customWidth="1"/>
+    <col min="3849" max="3849" width="10.6640625" style="38" customWidth="1"/>
+    <col min="3850" max="3850" width="11.33203125" style="38" customWidth="1"/>
+    <col min="3851" max="3851" width="11.109375" style="38" customWidth="1"/>
+    <col min="3852" max="3852" width="11.6640625" style="38" customWidth="1"/>
+    <col min="3853" max="3853" width="11.44140625" style="38" customWidth="1"/>
+    <col min="3854" max="3856" width="10.6640625" style="38" customWidth="1"/>
+    <col min="3857" max="3859" width="10.5546875" style="38" customWidth="1"/>
+    <col min="3860" max="3860" width="11" style="38" customWidth="1"/>
+    <col min="3861" max="3861" width="10.6640625" style="38" customWidth="1"/>
+    <col min="3862" max="3862" width="10.5546875" style="38" customWidth="1"/>
+    <col min="3863" max="3863" width="13.5546875" style="38" customWidth="1"/>
+    <col min="3864" max="3864" width="11.109375" style="38" customWidth="1"/>
+    <col min="3865" max="3865" width="11.88671875" style="38" customWidth="1"/>
+    <col min="3866" max="3866" width="10.5546875" style="38" customWidth="1"/>
+    <col min="3867" max="3867" width="10.6640625" style="38" customWidth="1"/>
+    <col min="3868" max="3868" width="10.5546875" style="38" customWidth="1"/>
+    <col min="3869" max="3869" width="13.5546875" style="38" customWidth="1"/>
+    <col min="3870" max="3870" width="12.44140625" style="38" customWidth="1"/>
+    <col min="3871" max="4099" width="9.109375" style="38"/>
+    <col min="4100" max="4100" width="30.109375" style="38" customWidth="1"/>
+    <col min="4101" max="4101" width="33.33203125" style="38" customWidth="1"/>
+    <col min="4102" max="4102" width="11" style="38" customWidth="1"/>
+    <col min="4103" max="4103" width="12.5546875" style="38" customWidth="1"/>
+    <col min="4104" max="4104" width="11.5546875" style="38" customWidth="1"/>
+    <col min="4105" max="4105" width="10.6640625" style="38" customWidth="1"/>
+    <col min="4106" max="4106" width="11.33203125" style="38" customWidth="1"/>
+    <col min="4107" max="4107" width="11.109375" style="38" customWidth="1"/>
+    <col min="4108" max="4108" width="11.6640625" style="38" customWidth="1"/>
+    <col min="4109" max="4109" width="11.44140625" style="38" customWidth="1"/>
+    <col min="4110" max="4112" width="10.6640625" style="38" customWidth="1"/>
+    <col min="4113" max="4115" width="10.5546875" style="38" customWidth="1"/>
+    <col min="4116" max="4116" width="11" style="38" customWidth="1"/>
+    <col min="4117" max="4117" width="10.6640625" style="38" customWidth="1"/>
+    <col min="4118" max="4118" width="10.5546875" style="38" customWidth="1"/>
+    <col min="4119" max="4119" width="13.5546875" style="38" customWidth="1"/>
+    <col min="4120" max="4120" width="11.109375" style="38" customWidth="1"/>
+    <col min="4121" max="4121" width="11.88671875" style="38" customWidth="1"/>
+    <col min="4122" max="4122" width="10.5546875" style="38" customWidth="1"/>
+    <col min="4123" max="4123" width="10.6640625" style="38" customWidth="1"/>
+    <col min="4124" max="4124" width="10.5546875" style="38" customWidth="1"/>
+    <col min="4125" max="4125" width="13.5546875" style="38" customWidth="1"/>
+    <col min="4126" max="4126" width="12.44140625" style="38" customWidth="1"/>
+    <col min="4127" max="4355" width="9.109375" style="38"/>
+    <col min="4356" max="4356" width="30.109375" style="38" customWidth="1"/>
+    <col min="4357" max="4357" width="33.33203125" style="38" customWidth="1"/>
+    <col min="4358" max="4358" width="11" style="38" customWidth="1"/>
+    <col min="4359" max="4359" width="12.5546875" style="38" customWidth="1"/>
+    <col min="4360" max="4360" width="11.5546875" style="38" customWidth="1"/>
+    <col min="4361" max="4361" width="10.6640625" style="38" customWidth="1"/>
+    <col min="4362" max="4362" width="11.33203125" style="38" customWidth="1"/>
+    <col min="4363" max="4363" width="11.109375" style="38" customWidth="1"/>
+    <col min="4364" max="4364" width="11.6640625" style="38" customWidth="1"/>
+    <col min="4365" max="4365" width="11.44140625" style="38" customWidth="1"/>
+    <col min="4366" max="4368" width="10.6640625" style="38" customWidth="1"/>
+    <col min="4369" max="4371" width="10.5546875" style="38" customWidth="1"/>
+    <col min="4372" max="4372" width="11" style="38" customWidth="1"/>
+    <col min="4373" max="4373" width="10.6640625" style="38" customWidth="1"/>
+    <col min="4374" max="4374" width="10.5546875" style="38" customWidth="1"/>
+    <col min="4375" max="4375" width="13.5546875" style="38" customWidth="1"/>
+    <col min="4376" max="4376" width="11.109375" style="38" customWidth="1"/>
+    <col min="4377" max="4377" width="11.88671875" style="38" customWidth="1"/>
+    <col min="4378" max="4378" width="10.5546875" style="38" customWidth="1"/>
+    <col min="4379" max="4379" width="10.6640625" style="38" customWidth="1"/>
+    <col min="4380" max="4380" width="10.5546875" style="38" customWidth="1"/>
+    <col min="4381" max="4381" width="13.5546875" style="38" customWidth="1"/>
+    <col min="4382" max="4382" width="12.44140625" style="38" customWidth="1"/>
+    <col min="4383" max="4611" width="9.109375" style="38"/>
+    <col min="4612" max="4612" width="30.109375" style="38" customWidth="1"/>
+    <col min="4613" max="4613" width="33.33203125" style="38" customWidth="1"/>
+    <col min="4614" max="4614" width="11" style="38" customWidth="1"/>
+    <col min="4615" max="4615" width="12.5546875" style="38" customWidth="1"/>
+    <col min="4616" max="4616" width="11.5546875" style="38" customWidth="1"/>
+    <col min="4617" max="4617" width="10.6640625" style="38" customWidth="1"/>
+    <col min="4618" max="4618" width="11.33203125" style="38" customWidth="1"/>
+    <col min="4619" max="4619" width="11.109375" style="38" customWidth="1"/>
+    <col min="4620" max="4620" width="11.6640625" style="38" customWidth="1"/>
+    <col min="4621" max="4621" width="11.44140625" style="38" customWidth="1"/>
+    <col min="4622" max="4624" width="10.6640625" style="38" customWidth="1"/>
+    <col min="4625" max="4627" width="10.5546875" style="38" customWidth="1"/>
+    <col min="4628" max="4628" width="11" style="38" customWidth="1"/>
+    <col min="4629" max="4629" width="10.6640625" style="38" customWidth="1"/>
+    <col min="4630" max="4630" width="10.5546875" style="38" customWidth="1"/>
+    <col min="4631" max="4631" width="13.5546875" style="38" customWidth="1"/>
+    <col min="4632" max="4632" width="11.109375" style="38" customWidth="1"/>
+    <col min="4633" max="4633" width="11.88671875" style="38" customWidth="1"/>
+    <col min="4634" max="4634" width="10.5546875" style="38" customWidth="1"/>
+    <col min="4635" max="4635" width="10.6640625" style="38" customWidth="1"/>
+    <col min="4636" max="4636" width="10.5546875" style="38" customWidth="1"/>
+    <col min="4637" max="4637" width="13.5546875" style="38" customWidth="1"/>
+    <col min="4638" max="4638" width="12.44140625" style="38" customWidth="1"/>
+    <col min="4639" max="4867" width="9.109375" style="38"/>
+    <col min="4868" max="4868" width="30.109375" style="38" customWidth="1"/>
+    <col min="4869" max="4869" width="33.33203125" style="38" customWidth="1"/>
+    <col min="4870" max="4870" width="11" style="38" customWidth="1"/>
+    <col min="4871" max="4871" width="12.5546875" style="38" customWidth="1"/>
+    <col min="4872" max="4872" width="11.5546875" style="38" customWidth="1"/>
+    <col min="4873" max="4873" width="10.6640625" style="38" customWidth="1"/>
+    <col min="4874" max="4874" width="11.33203125" style="38" customWidth="1"/>
+    <col min="4875" max="4875" width="11.109375" style="38" customWidth="1"/>
+    <col min="4876" max="4876" width="11.6640625" style="38" customWidth="1"/>
+    <col min="4877" max="4877" width="11.44140625" style="38" customWidth="1"/>
+    <col min="4878" max="4880" width="10.6640625" style="38" customWidth="1"/>
+    <col min="4881" max="4883" width="10.5546875" style="38" customWidth="1"/>
+    <col min="4884" max="4884" width="11" style="38" customWidth="1"/>
+    <col min="4885" max="4885" width="10.6640625" style="38" customWidth="1"/>
+    <col min="4886" max="4886" width="10.5546875" style="38" customWidth="1"/>
+    <col min="4887" max="4887" width="13.5546875" style="38" customWidth="1"/>
+    <col min="4888" max="4888" width="11.109375" style="38" customWidth="1"/>
+    <col min="4889" max="4889" width="11.88671875" style="38" customWidth="1"/>
+    <col min="4890" max="4890" width="10.5546875" style="38" customWidth="1"/>
+    <col min="4891" max="4891" width="10.6640625" style="38" customWidth="1"/>
+    <col min="4892" max="4892" width="10.5546875" style="38" customWidth="1"/>
+    <col min="4893" max="4893" width="13.5546875" style="38" customWidth="1"/>
+    <col min="4894" max="4894" width="12.44140625" style="38" customWidth="1"/>
+    <col min="4895" max="5123" width="9.109375" style="38"/>
+    <col min="5124" max="5124" width="30.109375" style="38" customWidth="1"/>
+    <col min="5125" max="5125" width="33.33203125" style="38" customWidth="1"/>
+    <col min="5126" max="5126" width="11" style="38" customWidth="1"/>
+    <col min="5127" max="5127" width="12.5546875" style="38" customWidth="1"/>
+    <col min="5128" max="5128" width="11.5546875" style="38" customWidth="1"/>
+    <col min="5129" max="5129" width="10.6640625" style="38" customWidth="1"/>
+    <col min="5130" max="5130" width="11.33203125" style="38" customWidth="1"/>
+    <col min="5131" max="5131" width="11.109375" style="38" customWidth="1"/>
+    <col min="5132" max="5132" width="11.6640625" style="38" customWidth="1"/>
+    <col min="5133" max="5133" width="11.44140625" style="38" customWidth="1"/>
+    <col min="5134" max="5136" width="10.6640625" style="38" customWidth="1"/>
+    <col min="5137" max="5139" width="10.5546875" style="38" customWidth="1"/>
+    <col min="5140" max="5140" width="11" style="38" customWidth="1"/>
+    <col min="5141" max="5141" width="10.6640625" style="38" customWidth="1"/>
+    <col min="5142" max="5142" width="10.5546875" style="38" customWidth="1"/>
+    <col min="5143" max="5143" width="13.5546875" style="38" customWidth="1"/>
+    <col min="5144" max="5144" width="11.109375" style="38" customWidth="1"/>
+    <col min="5145" max="5145" width="11.88671875" style="38" customWidth="1"/>
+    <col min="5146" max="5146" width="10.5546875" style="38" customWidth="1"/>
+    <col min="5147" max="5147" width="10.6640625" style="38" customWidth="1"/>
+    <col min="5148" max="5148" width="10.5546875" style="38" customWidth="1"/>
+    <col min="5149" max="5149" width="13.5546875" style="38" customWidth="1"/>
+    <col min="5150" max="5150" width="12.44140625" style="38" customWidth="1"/>
+    <col min="5151" max="5379" width="9.109375" style="38"/>
+    <col min="5380" max="5380" width="30.109375" style="38" customWidth="1"/>
+    <col min="5381" max="5381" width="33.33203125" style="38" customWidth="1"/>
+    <col min="5382" max="5382" width="11" style="38" customWidth="1"/>
+    <col min="5383" max="5383" width="12.5546875" style="38" customWidth="1"/>
+    <col min="5384" max="5384" width="11.5546875" style="38" customWidth="1"/>
+    <col min="5385" max="5385" width="10.6640625" style="38" customWidth="1"/>
+    <col min="5386" max="5386" width="11.33203125" style="38" customWidth="1"/>
+    <col min="5387" max="5387" width="11.109375" style="38" customWidth="1"/>
+    <col min="5388" max="5388" width="11.6640625" style="38" customWidth="1"/>
+    <col min="5389" max="5389" width="11.44140625" style="38" customWidth="1"/>
+    <col min="5390" max="5392" width="10.6640625" style="38" customWidth="1"/>
+    <col min="5393" max="5395" width="10.5546875" style="38" customWidth="1"/>
+    <col min="5396" max="5396" width="11" style="38" customWidth="1"/>
+    <col min="5397" max="5397" width="10.6640625" style="38" customWidth="1"/>
+    <col min="5398" max="5398" width="10.5546875" style="38" customWidth="1"/>
+    <col min="5399" max="5399" width="13.5546875" style="38" customWidth="1"/>
+    <col min="5400" max="5400" width="11.109375" style="38" customWidth="1"/>
+    <col min="5401" max="5401" width="11.88671875" style="38" customWidth="1"/>
+    <col min="5402" max="5402" width="10.5546875" style="38" customWidth="1"/>
+    <col min="5403" max="5403" width="10.6640625" style="38" customWidth="1"/>
+    <col min="5404" max="5404" width="10.5546875" style="38" customWidth="1"/>
+    <col min="5405" max="5405" width="13.5546875" style="38" customWidth="1"/>
+    <col min="5406" max="5406" width="12.44140625" style="38" customWidth="1"/>
+    <col min="5407" max="5635" width="9.109375" style="38"/>
+    <col min="5636" max="5636" width="30.109375" style="38" customWidth="1"/>
+    <col min="5637" max="5637" width="33.33203125" style="38" customWidth="1"/>
+    <col min="5638" max="5638" width="11" style="38" customWidth="1"/>
+    <col min="5639" max="5639" width="12.5546875" style="38" customWidth="1"/>
+    <col min="5640" max="5640" width="11.5546875" style="38" customWidth="1"/>
+    <col min="5641" max="5641" width="10.6640625" style="38" customWidth="1"/>
+    <col min="5642" max="5642" width="11.33203125" style="38" customWidth="1"/>
+    <col min="5643" max="5643" width="11.109375" style="38" customWidth="1"/>
+    <col min="5644" max="5644" width="11.6640625" style="38" customWidth="1"/>
+    <col min="5645" max="5645" width="11.44140625" style="38" customWidth="1"/>
+    <col min="5646" max="5648" width="10.6640625" style="38" customWidth="1"/>
+    <col min="5649" max="5651" width="10.5546875" style="38" customWidth="1"/>
+    <col min="5652" max="5652" width="11" style="38" customWidth="1"/>
+    <col min="5653" max="5653" width="10.6640625" style="38" customWidth="1"/>
+    <col min="5654" max="5654" width="10.5546875" style="38" customWidth="1"/>
+    <col min="5655" max="5655" width="13.5546875" style="38" customWidth="1"/>
+    <col min="5656" max="5656" width="11.109375" style="38" customWidth="1"/>
+    <col min="5657" max="5657" width="11.88671875" style="38" customWidth="1"/>
+    <col min="5658" max="5658" width="10.5546875" style="38" customWidth="1"/>
+    <col min="5659" max="5659" width="10.6640625" style="38" customWidth="1"/>
+    <col min="5660" max="5660" width="10.5546875" style="38" customWidth="1"/>
+    <col min="5661" max="5661" width="13.5546875" style="38" customWidth="1"/>
+    <col min="5662" max="5662" width="12.44140625" style="38" customWidth="1"/>
+    <col min="5663" max="5891" width="9.109375" style="38"/>
+    <col min="5892" max="5892" width="30.109375" style="38" customWidth="1"/>
+    <col min="5893" max="5893" width="33.33203125" style="38" customWidth="1"/>
+    <col min="5894" max="5894" width="11" style="38" customWidth="1"/>
+    <col min="5895" max="5895" width="12.5546875" style="38" customWidth="1"/>
+    <col min="5896" max="5896" width="11.5546875" style="38" customWidth="1"/>
+    <col min="5897" max="5897" width="10.6640625" style="38" customWidth="1"/>
+    <col min="5898" max="5898" width="11.33203125" style="38" customWidth="1"/>
+    <col min="5899" max="5899" width="11.109375" style="38" customWidth="1"/>
+    <col min="5900" max="5900" width="11.6640625" style="38" customWidth="1"/>
+    <col min="5901" max="5901" width="11.44140625" style="38" customWidth="1"/>
+    <col min="5902" max="5904" width="10.6640625" style="38" customWidth="1"/>
+    <col min="5905" max="5907" width="10.5546875" style="38" customWidth="1"/>
+    <col min="5908" max="5908" width="11" style="38" customWidth="1"/>
+    <col min="5909" max="5909" width="10.6640625" style="38" customWidth="1"/>
+    <col min="5910" max="5910" width="10.5546875" style="38" customWidth="1"/>
+    <col min="5911" max="5911" width="13.5546875" style="38" customWidth="1"/>
+    <col min="5912" max="5912" width="11.109375" style="38" customWidth="1"/>
+    <col min="5913" max="5913" width="11.88671875" style="38" customWidth="1"/>
+    <col min="5914" max="5914" width="10.5546875" style="38" customWidth="1"/>
+    <col min="5915" max="5915" width="10.6640625" style="38" customWidth="1"/>
+    <col min="5916" max="5916" width="10.5546875" style="38" customWidth="1"/>
+    <col min="5917" max="5917" width="13.5546875" style="38" customWidth="1"/>
+    <col min="5918" max="5918" width="12.44140625" style="38" customWidth="1"/>
+    <col min="5919" max="6147" width="9.109375" style="38"/>
+    <col min="6148" max="6148" width="30.109375" style="38" customWidth="1"/>
+    <col min="6149" max="6149" width="33.33203125" style="38" customWidth="1"/>
+    <col min="6150" max="6150" width="11" style="38" customWidth="1"/>
+    <col min="6151" max="6151" width="12.5546875" style="38" customWidth="1"/>
+    <col min="6152" max="6152" width="11.5546875" style="38" customWidth="1"/>
+    <col min="6153" max="6153" width="10.6640625" style="38" customWidth="1"/>
+    <col min="6154" max="6154" width="11.33203125" style="38" customWidth="1"/>
+    <col min="6155" max="6155" width="11.109375" style="38" customWidth="1"/>
+    <col min="6156" max="6156" width="11.6640625" style="38" customWidth="1"/>
+    <col min="6157" max="6157" width="11.44140625" style="38" customWidth="1"/>
+    <col min="6158" max="6160" width="10.6640625" style="38" customWidth="1"/>
+    <col min="6161" max="6163" width="10.5546875" style="38" customWidth="1"/>
+    <col min="6164" max="6164" width="11" style="38" customWidth="1"/>
+    <col min="6165" max="6165" width="10.6640625" style="38" customWidth="1"/>
+    <col min="6166" max="6166" width="10.5546875" style="38" customWidth="1"/>
+    <col min="6167" max="6167" width="13.5546875" style="38" customWidth="1"/>
+    <col min="6168" max="6168" width="11.109375" style="38" customWidth="1"/>
+    <col min="6169" max="6169" width="11.88671875" style="38" customWidth="1"/>
+    <col min="6170" max="6170" width="10.5546875" style="38" customWidth="1"/>
+    <col min="6171" max="6171" width="10.6640625" style="38" customWidth="1"/>
+    <col min="6172" max="6172" width="10.5546875" style="38" customWidth="1"/>
+    <col min="6173" max="6173" width="13.5546875" style="38" customWidth="1"/>
+    <col min="6174" max="6174" width="12.44140625" style="38" customWidth="1"/>
+    <col min="6175" max="6403" width="9.109375" style="38"/>
+    <col min="6404" max="6404" width="30.109375" style="38" customWidth="1"/>
+    <col min="6405" max="6405" width="33.33203125" style="38" customWidth="1"/>
+    <col min="6406" max="6406" width="11" style="38" customWidth="1"/>
+    <col min="6407" max="6407" width="12.5546875" style="38" customWidth="1"/>
+    <col min="6408" max="6408" width="11.5546875" style="38" customWidth="1"/>
+    <col min="6409" max="6409" width="10.6640625" style="38" customWidth="1"/>
+    <col min="6410" max="6410" width="11.33203125" style="38" customWidth="1"/>
+    <col min="6411" max="6411" width="11.109375" style="38" customWidth="1"/>
+    <col min="6412" max="6412" width="11.6640625" style="38" customWidth="1"/>
+    <col min="6413" max="6413" width="11.44140625" style="38" customWidth="1"/>
+    <col min="6414" max="6416" width="10.6640625" style="38" customWidth="1"/>
+    <col min="6417" max="6419" width="10.5546875" style="38" customWidth="1"/>
+    <col min="6420" max="6420" width="11" style="38" customWidth="1"/>
+    <col min="6421" max="6421" width="10.6640625" style="38" customWidth="1"/>
+    <col min="6422" max="6422" width="10.5546875" style="38" customWidth="1"/>
+    <col min="6423" max="6423" width="13.5546875" style="38" customWidth="1"/>
+    <col min="6424" max="6424" width="11.109375" style="38" customWidth="1"/>
+    <col min="6425" max="6425" width="11.88671875" style="38" customWidth="1"/>
+    <col min="6426" max="6426" width="10.5546875" style="38" customWidth="1"/>
+    <col min="6427" max="6427" width="10.6640625" style="38" customWidth="1"/>
+    <col min="6428" max="6428" width="10.5546875" style="38" customWidth="1"/>
+    <col min="6429" max="6429" width="13.5546875" style="38" customWidth="1"/>
+    <col min="6430" max="6430" width="12.44140625" style="38" customWidth="1"/>
+    <col min="6431" max="6659" width="9.109375" style="38"/>
+    <col min="6660" max="6660" width="30.109375" style="38" customWidth="1"/>
+    <col min="6661" max="6661" width="33.33203125" style="38" customWidth="1"/>
+    <col min="6662" max="6662" width="11" style="38" customWidth="1"/>
+    <col min="6663" max="6663" width="12.5546875" style="38" customWidth="1"/>
+    <col min="6664" max="6664" width="11.5546875" style="38" customWidth="1"/>
+    <col min="6665" max="6665" width="10.6640625" style="38" customWidth="1"/>
+    <col min="6666" max="6666" width="11.33203125" style="38" customWidth="1"/>
+    <col min="6667" max="6667" width="11.109375" style="38" customWidth="1"/>
+    <col min="6668" max="6668" width="11.6640625" style="38" customWidth="1"/>
+    <col min="6669" max="6669" width="11.44140625" style="38" customWidth="1"/>
+    <col min="6670" max="6672" width="10.6640625" style="38" customWidth="1"/>
+    <col min="6673" max="6675" width="10.5546875" style="38" customWidth="1"/>
+    <col min="6676" max="6676" width="11" style="38" customWidth="1"/>
+    <col min="6677" max="6677" width="10.6640625" style="38" customWidth="1"/>
+    <col min="6678" max="6678" width="10.5546875" style="38" customWidth="1"/>
+    <col min="6679" max="6679" width="13.5546875" style="38" customWidth="1"/>
+    <col min="6680" max="6680" width="11.109375" style="38" customWidth="1"/>
+    <col min="6681" max="6681" width="11.88671875" style="38" customWidth="1"/>
+    <col min="6682" max="6682" width="10.5546875" style="38" customWidth="1"/>
+    <col min="6683" max="6683" width="10.6640625" style="38" customWidth="1"/>
+    <col min="6684" max="6684" width="10.5546875" style="38" customWidth="1"/>
+    <col min="6685" max="6685" width="13.5546875" style="38" customWidth="1"/>
+    <col min="6686" max="6686" width="12.44140625" style="38" customWidth="1"/>
+    <col min="6687" max="6915" width="9.109375" style="38"/>
+    <col min="6916" max="6916" width="30.109375" style="38" customWidth="1"/>
+    <col min="6917" max="6917" width="33.33203125" style="38" customWidth="1"/>
+    <col min="6918" max="6918" width="11" style="38" customWidth="1"/>
+    <col min="6919" max="6919" width="12.5546875" style="38" customWidth="1"/>
+    <col min="6920" max="6920" width="11.5546875" style="38" customWidth="1"/>
+    <col min="6921" max="6921" width="10.6640625" style="38" customWidth="1"/>
+    <col min="6922" max="6922" width="11.33203125" style="38" customWidth="1"/>
+    <col min="6923" max="6923" width="11.109375" style="38" customWidth="1"/>
+    <col min="6924" max="6924" width="11.6640625" style="38" customWidth="1"/>
+    <col min="6925" max="6925" width="11.44140625" style="38" customWidth="1"/>
+    <col min="6926" max="6928" width="10.6640625" style="38" customWidth="1"/>
+    <col min="6929" max="6931" width="10.5546875" style="38" customWidth="1"/>
+    <col min="6932" max="6932" width="11" style="38" customWidth="1"/>
+    <col min="6933" max="6933" width="10.6640625" style="38" customWidth="1"/>
+    <col min="6934" max="6934" width="10.5546875" style="38" customWidth="1"/>
+    <col min="6935" max="6935" width="13.5546875" style="38" customWidth="1"/>
+    <col min="6936" max="6936" width="11.109375" style="38" customWidth="1"/>
+    <col min="6937" max="6937" width="11.88671875" style="38" customWidth="1"/>
+    <col min="6938" max="6938" width="10.5546875" style="38" customWidth="1"/>
+    <col min="6939" max="6939" width="10.6640625" style="38" customWidth="1"/>
+    <col min="6940" max="6940" width="10.5546875" style="38" customWidth="1"/>
+    <col min="6941" max="6941" width="13.5546875" style="38" customWidth="1"/>
+    <col min="6942" max="6942" width="12.44140625" style="38" customWidth="1"/>
+    <col min="6943" max="7171" width="9.109375" style="38"/>
+    <col min="7172" max="7172" width="30.109375" style="38" customWidth="1"/>
+    <col min="7173" max="7173" width="33.33203125" style="38" customWidth="1"/>
+    <col min="7174" max="7174" width="11" style="38" customWidth="1"/>
+    <col min="7175" max="7175" width="12.5546875" style="38" customWidth="1"/>
+    <col min="7176" max="7176" width="11.5546875" style="38" customWidth="1"/>
+    <col min="7177" max="7177" width="10.6640625" style="38" customWidth="1"/>
+    <col min="7178" max="7178" width="11.33203125" style="38" customWidth="1"/>
+    <col min="7179" max="7179" width="11.109375" style="38" customWidth="1"/>
+    <col min="7180" max="7180" width="11.6640625" style="38" customWidth="1"/>
+    <col min="7181" max="7181" width="11.44140625" style="38" customWidth="1"/>
+    <col min="7182" max="7184" width="10.6640625" style="38" customWidth="1"/>
+    <col min="7185" max="7187" width="10.5546875" style="38" customWidth="1"/>
+    <col min="7188" max="7188" width="11" style="38" customWidth="1"/>
+    <col min="7189" max="7189" width="10.6640625" style="38" customWidth="1"/>
+    <col min="7190" max="7190" width="10.5546875" style="38" customWidth="1"/>
+    <col min="7191" max="7191" width="13.5546875" style="38" customWidth="1"/>
+    <col min="7192" max="7192" width="11.109375" style="38" customWidth="1"/>
+    <col min="7193" max="7193" width="11.88671875" style="38" customWidth="1"/>
+    <col min="7194" max="7194" width="10.5546875" style="38" customWidth="1"/>
+    <col min="7195" max="7195" width="10.6640625" style="38" customWidth="1"/>
+    <col min="7196" max="7196" width="10.5546875" style="38" customWidth="1"/>
+    <col min="7197" max="7197" width="13.5546875" style="38" customWidth="1"/>
+    <col min="7198" max="7198" width="12.44140625" style="38" customWidth="1"/>
+    <col min="7199" max="7427" width="9.109375" style="38"/>
+    <col min="7428" max="7428" width="30.109375" style="38" customWidth="1"/>
+    <col min="7429" max="7429" width="33.33203125" style="38" customWidth="1"/>
+    <col min="7430" max="7430" width="11" style="38" customWidth="1"/>
+    <col min="7431" max="7431" width="12.5546875" style="38" customWidth="1"/>
+    <col min="7432" max="7432" width="11.5546875" style="38" customWidth="1"/>
+    <col min="7433" max="7433" width="10.6640625" style="38" customWidth="1"/>
+    <col min="7434" max="7434" width="11.33203125" style="38" customWidth="1"/>
+    <col min="7435" max="7435" width="11.109375" style="38" customWidth="1"/>
+    <col min="7436" max="7436" width="11.6640625" style="38" customWidth="1"/>
+    <col min="7437" max="7437" width="11.44140625" style="38" customWidth="1"/>
+    <col min="7438" max="7440" width="10.6640625" style="38" customWidth="1"/>
+    <col min="7441" max="7443" width="10.5546875" style="38" customWidth="1"/>
+    <col min="7444" max="7444" width="11" style="38" customWidth="1"/>
+    <col min="7445" max="7445" width="10.6640625" style="38" customWidth="1"/>
+    <col min="7446" max="7446" width="10.5546875" style="38" customWidth="1"/>
+    <col min="7447" max="7447" width="13.5546875" style="38" customWidth="1"/>
+    <col min="7448" max="7448" width="11.109375" style="38" customWidth="1"/>
+    <col min="7449" max="7449" width="11.88671875" style="38" customWidth="1"/>
+    <col min="7450" max="7450" width="10.5546875" style="38" customWidth="1"/>
+    <col min="7451" max="7451" width="10.6640625" style="38" customWidth="1"/>
+    <col min="7452" max="7452" width="10.5546875" style="38" customWidth="1"/>
+    <col min="7453" max="7453" width="13.5546875" style="38" customWidth="1"/>
+    <col min="7454" max="7454" width="12.44140625" style="38" customWidth="1"/>
+    <col min="7455" max="7683" width="9.109375" style="38"/>
+    <col min="7684" max="7684" width="30.109375" style="38" customWidth="1"/>
+    <col min="7685" max="7685" width="33.33203125" style="38" customWidth="1"/>
+    <col min="7686" max="7686" width="11" style="38" customWidth="1"/>
+    <col min="7687" max="7687" width="12.5546875" style="38" customWidth="1"/>
+    <col min="7688" max="7688" width="11.5546875" style="38" customWidth="1"/>
+    <col min="7689" max="7689" width="10.6640625" style="38" customWidth="1"/>
+    <col min="7690" max="7690" width="11.33203125" style="38" customWidth="1"/>
+    <col min="7691" max="7691" width="11.109375" style="38" customWidth="1"/>
+    <col min="7692" max="7692" width="11.6640625" style="38" customWidth="1"/>
+    <col min="7693" max="7693" width="11.44140625" style="38" customWidth="1"/>
+    <col min="7694" max="7696" width="10.6640625" style="38" customWidth="1"/>
+    <col min="7697" max="7699" width="10.5546875" style="38" customWidth="1"/>
+    <col min="7700" max="7700" width="11" style="38" customWidth="1"/>
+    <col min="7701" max="7701" width="10.6640625" style="38" customWidth="1"/>
+    <col min="7702" max="7702" width="10.5546875" style="38" customWidth="1"/>
+    <col min="7703" max="7703" width="13.5546875" style="38" customWidth="1"/>
+    <col min="7704" max="7704" width="11.109375" style="38" customWidth="1"/>
+    <col min="7705" max="7705" width="11.88671875" style="38" customWidth="1"/>
+    <col min="7706" max="7706" width="10.5546875" style="38" customWidth="1"/>
+    <col min="7707" max="7707" width="10.6640625" style="38" customWidth="1"/>
+    <col min="7708" max="7708" width="10.5546875" style="38" customWidth="1"/>
+    <col min="7709" max="7709" width="13.5546875" style="38" customWidth="1"/>
+    <col min="7710" max="7710" width="12.44140625" style="38" customWidth="1"/>
+    <col min="7711" max="7939" width="9.109375" style="38"/>
+    <col min="7940" max="7940" width="30.109375" style="38" customWidth="1"/>
+    <col min="7941" max="7941" width="33.33203125" style="38" customWidth="1"/>
+    <col min="7942" max="7942" width="11" style="38" customWidth="1"/>
+    <col min="7943" max="7943" width="12.5546875" style="38" customWidth="1"/>
+    <col min="7944" max="7944" width="11.5546875" style="38" customWidth="1"/>
+    <col min="7945" max="7945" width="10.6640625" style="38" customWidth="1"/>
+    <col min="7946" max="7946" width="11.33203125" style="38" customWidth="1"/>
+    <col min="7947" max="7947" width="11.109375" style="38" customWidth="1"/>
+    <col min="7948" max="7948" width="11.6640625" style="38" customWidth="1"/>
+    <col min="7949" max="7949" width="11.44140625" style="38" customWidth="1"/>
+    <col min="7950" max="7952" width="10.6640625" style="38" customWidth="1"/>
+    <col min="7953" max="7955" width="10.5546875" style="38" customWidth="1"/>
+    <col min="7956" max="7956" width="11" style="38" customWidth="1"/>
+    <col min="7957" max="7957" width="10.6640625" style="38" customWidth="1"/>
+    <col min="7958" max="7958" width="10.5546875" style="38" customWidth="1"/>
+    <col min="7959" max="7959" width="13.5546875" style="38" customWidth="1"/>
+    <col min="7960" max="7960" width="11.109375" style="38" customWidth="1"/>
+    <col min="7961" max="7961" width="11.88671875" style="38" customWidth="1"/>
+    <col min="7962" max="7962" width="10.5546875" style="38" customWidth="1"/>
+    <col min="7963" max="7963" width="10.6640625" style="38" customWidth="1"/>
+    <col min="7964" max="7964" width="10.5546875" style="38" customWidth="1"/>
+    <col min="7965" max="7965" width="13.5546875" style="38" customWidth="1"/>
+    <col min="7966" max="7966" width="12.44140625" style="38" customWidth="1"/>
+    <col min="7967" max="8195" width="9.109375" style="38"/>
+    <col min="8196" max="8196" width="30.109375" style="38" customWidth="1"/>
+    <col min="8197" max="8197" width="33.33203125" style="38" customWidth="1"/>
+    <col min="8198" max="8198" width="11" style="38" customWidth="1"/>
+    <col min="8199" max="8199" width="12.5546875" style="38" customWidth="1"/>
+    <col min="8200" max="8200" width="11.5546875" style="38" customWidth="1"/>
+    <col min="8201" max="8201" width="10.6640625" style="38" customWidth="1"/>
+    <col min="8202" max="8202" width="11.33203125" style="38" customWidth="1"/>
+    <col min="8203" max="8203" width="11.109375" style="38" customWidth="1"/>
+    <col min="8204" max="8204" width="11.6640625" style="38" customWidth="1"/>
+    <col min="8205" max="8205" width="11.44140625" style="38" customWidth="1"/>
+    <col min="8206" max="8208" width="10.6640625" style="38" customWidth="1"/>
+    <col min="8209" max="8211" width="10.5546875" style="38" customWidth="1"/>
+    <col min="8212" max="8212" width="11" style="38" customWidth="1"/>
+    <col min="8213" max="8213" width="10.6640625" style="38" customWidth="1"/>
+    <col min="8214" max="8214" width="10.5546875" style="38" customWidth="1"/>
+    <col min="8215" max="8215" width="13.5546875" style="38" customWidth="1"/>
+    <col min="8216" max="8216" width="11.109375" style="38" customWidth="1"/>
+    <col min="8217" max="8217" width="11.88671875" style="38" customWidth="1"/>
+    <col min="8218" max="8218" width="10.5546875" style="38" customWidth="1"/>
+    <col min="8219" max="8219" width="10.6640625" style="38" customWidth="1"/>
+    <col min="8220" max="8220" width="10.5546875" style="38" customWidth="1"/>
+    <col min="8221" max="8221" width="13.5546875" style="38" customWidth="1"/>
+    <col min="8222" max="8222" width="12.44140625" style="38" customWidth="1"/>
+    <col min="8223" max="8451" width="9.109375" style="38"/>
+    <col min="8452" max="8452" width="30.109375" style="38" customWidth="1"/>
+    <col min="8453" max="8453" width="33.33203125" style="38" customWidth="1"/>
+    <col min="8454" max="8454" width="11" style="38" customWidth="1"/>
+    <col min="8455" max="8455" width="12.5546875" style="38" customWidth="1"/>
+    <col min="8456" max="8456" width="11.5546875" style="38" customWidth="1"/>
+    <col min="8457" max="8457" width="10.6640625" style="38" customWidth="1"/>
+    <col min="8458" max="8458" width="11.33203125" style="38" customWidth="1"/>
+    <col min="8459" max="8459" width="11.109375" style="38" customWidth="1"/>
+    <col min="8460" max="8460" width="11.6640625" style="38" customWidth="1"/>
+    <col min="8461" max="8461" width="11.44140625" style="38" customWidth="1"/>
+    <col min="8462" max="8464" width="10.6640625" style="38" customWidth="1"/>
+    <col min="8465" max="8467" width="10.5546875" style="38" customWidth="1"/>
+    <col min="8468" max="8468" width="11" style="38" customWidth="1"/>
+    <col min="8469" max="8469" width="10.6640625" style="38" customWidth="1"/>
+    <col min="8470" max="8470" width="10.5546875" style="38" customWidth="1"/>
+    <col min="8471" max="8471" width="13.5546875" style="38" customWidth="1"/>
+    <col min="8472" max="8472" width="11.109375" style="38" customWidth="1"/>
+    <col min="8473" max="8473" width="11.88671875" style="38" customWidth="1"/>
+    <col min="8474" max="8474" width="10.5546875" style="38" customWidth="1"/>
+    <col min="8475" max="8475" width="10.6640625" style="38" customWidth="1"/>
+    <col min="8476" max="8476" width="10.5546875" style="38" customWidth="1"/>
+    <col min="8477" max="8477" width="13.5546875" style="38" customWidth="1"/>
+    <col min="8478" max="8478" width="12.44140625" style="38" customWidth="1"/>
+    <col min="8479" max="8707" width="9.109375" style="38"/>
+    <col min="8708" max="8708" width="30.109375" style="38" customWidth="1"/>
+    <col min="8709" max="8709" width="33.33203125" style="38" customWidth="1"/>
+    <col min="8710" max="8710" width="11" style="38" customWidth="1"/>
+    <col min="8711" max="8711" width="12.5546875" style="38" customWidth="1"/>
+    <col min="8712" max="8712" width="11.5546875" style="38" customWidth="1"/>
+    <col min="8713" max="8713" width="10.6640625" style="38" customWidth="1"/>
+    <col min="8714" max="8714" width="11.33203125" style="38" customWidth="1"/>
+    <col min="8715" max="8715" width="11.109375" style="38" customWidth="1"/>
+    <col min="8716" max="8716" width="11.6640625" style="38" customWidth="1"/>
+    <col min="8717" max="8717" width="11.44140625" style="38" customWidth="1"/>
+    <col min="8718" max="8720" width="10.6640625" style="38" customWidth="1"/>
+    <col min="8721" max="8723" width="10.5546875" style="38" customWidth="1"/>
+    <col min="8724" max="8724" width="11" style="38" customWidth="1"/>
+    <col min="8725" max="8725" width="10.6640625" style="38" customWidth="1"/>
+    <col min="8726" max="8726" width="10.5546875" style="38" customWidth="1"/>
+    <col min="8727" max="8727" width="13.5546875" style="38" customWidth="1"/>
+    <col min="8728" max="8728" width="11.109375" style="38" customWidth="1"/>
+    <col min="8729" max="8729" width="11.88671875" style="38" customWidth="1"/>
+    <col min="8730" max="8730" width="10.5546875" style="38" customWidth="1"/>
+    <col min="8731" max="8731" width="10.6640625" style="38" customWidth="1"/>
+    <col min="8732" max="8732" width="10.5546875" style="38" customWidth="1"/>
+    <col min="8733" max="8733" width="13.5546875" style="38" customWidth="1"/>
+    <col min="8734" max="8734" width="12.44140625" style="38" customWidth="1"/>
+    <col min="8735" max="8963" width="9.109375" style="38"/>
+    <col min="8964" max="8964" width="30.109375" style="38" customWidth="1"/>
+    <col min="8965" max="8965" width="33.33203125" style="38" customWidth="1"/>
+    <col min="8966" max="8966" width="11" style="38" customWidth="1"/>
+    <col min="8967" max="8967" width="12.5546875" style="38" customWidth="1"/>
+    <col min="8968" max="8968" width="11.5546875" style="38" customWidth="1"/>
+    <col min="8969" max="8969" width="10.6640625" style="38" customWidth="1"/>
+    <col min="8970" max="8970" width="11.33203125" style="38" customWidth="1"/>
+    <col min="8971" max="8971" width="11.109375" style="38" customWidth="1"/>
+    <col min="8972" max="8972" width="11.6640625" style="38" customWidth="1"/>
+    <col min="8973" max="8973" width="11.44140625" style="38" customWidth="1"/>
+    <col min="8974" max="8976" width="10.6640625" style="38" customWidth="1"/>
+    <col min="8977" max="8979" width="10.5546875" style="38" customWidth="1"/>
+    <col min="8980" max="8980" width="11" style="38" customWidth="1"/>
+    <col min="8981" max="8981" width="10.6640625" style="38" customWidth="1"/>
+    <col min="8982" max="8982" width="10.5546875" style="38" customWidth="1"/>
+    <col min="8983" max="8983" width="13.5546875" style="38" customWidth="1"/>
+    <col min="8984" max="8984" width="11.109375" style="38" customWidth="1"/>
+    <col min="8985" max="8985" width="11.88671875" style="38" customWidth="1"/>
+    <col min="8986" max="8986" width="10.5546875" style="38" customWidth="1"/>
+    <col min="8987" max="8987" width="10.6640625" style="38" customWidth="1"/>
+    <col min="8988" max="8988" width="10.5546875" style="38" customWidth="1"/>
+    <col min="8989" max="8989" width="13.5546875" style="38" customWidth="1"/>
+    <col min="8990" max="8990" width="12.44140625" style="38" customWidth="1"/>
+    <col min="8991" max="9219" width="9.109375" style="38"/>
+    <col min="9220" max="9220" width="30.109375" style="38" customWidth="1"/>
+    <col min="9221" max="9221" width="33.33203125" style="38" customWidth="1"/>
+    <col min="9222" max="9222" width="11" style="38" customWidth="1"/>
+    <col min="9223" max="9223" width="12.5546875" style="38" customWidth="1"/>
+    <col min="9224" max="9224" width="11.5546875" style="38" customWidth="1"/>
+    <col min="9225" max="9225" width="10.6640625" style="38" customWidth="1"/>
+    <col min="9226" max="9226" width="11.33203125" style="38" customWidth="1"/>
+    <col min="9227" max="9227" width="11.109375" style="38" customWidth="1"/>
+    <col min="9228" max="9228" width="11.6640625" style="38" customWidth="1"/>
+    <col min="9229" max="9229" width="11.44140625" style="38" customWidth="1"/>
+    <col min="9230" max="9232" width="10.6640625" style="38" customWidth="1"/>
+    <col min="9233" max="9235" width="10.5546875" style="38" customWidth="1"/>
+    <col min="9236" max="9236" width="11" style="38" customWidth="1"/>
+    <col min="9237" max="9237" width="10.6640625" style="38" customWidth="1"/>
+    <col min="9238" max="9238" width="10.5546875" style="38" customWidth="1"/>
+    <col min="9239" max="9239" width="13.5546875" style="38" customWidth="1"/>
+    <col min="9240" max="9240" width="11.109375" style="38" customWidth="1"/>
+    <col min="9241" max="9241" width="11.88671875" style="38" customWidth="1"/>
+    <col min="9242" max="9242" width="10.5546875" style="38" customWidth="1"/>
+    <col min="9243" max="9243" width="10.6640625" style="38" customWidth="1"/>
+    <col min="9244" max="9244" width="10.5546875" style="38" customWidth="1"/>
+    <col min="9245" max="9245" width="13.5546875" style="38" customWidth="1"/>
+    <col min="9246" max="9246" width="12.44140625" style="38" customWidth="1"/>
+    <col min="9247" max="9475" width="9.109375" style="38"/>
+    <col min="9476" max="9476" width="30.109375" style="38" customWidth="1"/>
+    <col min="9477" max="9477" width="33.33203125" style="38" customWidth="1"/>
+    <col min="9478" max="9478" width="11" style="38" customWidth="1"/>
+    <col min="9479" max="9479" width="12.5546875" style="38" customWidth="1"/>
+    <col min="9480" max="9480" width="11.5546875" style="38" customWidth="1"/>
+    <col min="9481" max="9481" width="10.6640625" style="38" customWidth="1"/>
+    <col min="9482" max="9482" width="11.33203125" style="38" customWidth="1"/>
+    <col min="9483" max="9483" width="11.109375" style="38" customWidth="1"/>
+    <col min="9484" max="9484" width="11.6640625" style="38" customWidth="1"/>
+    <col min="9485" max="9485" width="11.44140625" style="38" customWidth="1"/>
+    <col min="9486" max="9488" width="10.6640625" style="38" customWidth="1"/>
+    <col min="9489" max="9491" width="10.5546875" style="38" customWidth="1"/>
+    <col min="9492" max="9492" width="11" style="38" customWidth="1"/>
+    <col min="9493" max="9493" width="10.6640625" style="38" customWidth="1"/>
+    <col min="9494" max="9494" width="10.5546875" style="38" customWidth="1"/>
+    <col min="9495" max="9495" width="13.5546875" style="38" customWidth="1"/>
+    <col min="9496" max="9496" width="11.109375" style="38" customWidth="1"/>
+    <col min="9497" max="9497" width="11.88671875" style="38" customWidth="1"/>
+    <col min="9498" max="9498" width="10.5546875" style="38" customWidth="1"/>
+    <col min="9499" max="9499" width="10.6640625" style="38" customWidth="1"/>
+    <col min="9500" max="9500" width="10.5546875" style="38" customWidth="1"/>
+    <col min="9501" max="9501" width="13.5546875" style="38" customWidth="1"/>
+    <col min="9502" max="9502" width="12.44140625" style="38" customWidth="1"/>
+    <col min="9503" max="9731" width="9.109375" style="38"/>
+    <col min="9732" max="9732" width="30.109375" style="38" customWidth="1"/>
+    <col min="9733" max="9733" width="33.33203125" style="38" customWidth="1"/>
+    <col min="9734" max="9734" width="11" style="38" customWidth="1"/>
+    <col min="9735" max="9735" width="12.5546875" style="38" customWidth="1"/>
+    <col min="9736" max="9736" width="11.5546875" style="38" customWidth="1"/>
+    <col min="9737" max="9737" width="10.6640625" style="38" customWidth="1"/>
+    <col min="9738" max="9738" width="11.33203125" style="38" customWidth="1"/>
+    <col min="9739" max="9739" width="11.109375" style="38" customWidth="1"/>
+    <col min="9740" max="9740" width="11.6640625" style="38" customWidth="1"/>
+    <col min="9741" max="9741" width="11.44140625" style="38" customWidth="1"/>
+    <col min="9742" max="9744" width="10.6640625" style="38" customWidth="1"/>
+    <col min="9745" max="9747" width="10.5546875" style="38" customWidth="1"/>
+    <col min="9748" max="9748" width="11" style="38" customWidth="1"/>
+    <col min="9749" max="9749" width="10.6640625" style="38" customWidth="1"/>
+    <col min="9750" max="9750" width="10.5546875" style="38" customWidth="1"/>
+    <col min="9751" max="9751" width="13.5546875" style="38" customWidth="1"/>
+    <col min="9752" max="9752" width="11.109375" style="38" customWidth="1"/>
+    <col min="9753" max="9753" width="11.88671875" style="38" customWidth="1"/>
+    <col min="9754" max="9754" width="10.5546875" style="38" customWidth="1"/>
+    <col min="9755" max="9755" width="10.6640625" style="38" customWidth="1"/>
+    <col min="9756" max="9756" width="10.5546875" style="38" customWidth="1"/>
+    <col min="9757" max="9757" width="13.5546875" style="38" customWidth="1"/>
+    <col min="9758" max="9758" width="12.44140625" style="38" customWidth="1"/>
+    <col min="9759" max="9987" width="9.109375" style="38"/>
+    <col min="9988" max="9988" width="30.109375" style="38" customWidth="1"/>
+    <col min="9989" max="9989" width="33.33203125" style="38" customWidth="1"/>
+    <col min="9990" max="9990" width="11" style="38" customWidth="1"/>
+    <col min="9991" max="9991" width="12.5546875" style="38" customWidth="1"/>
+    <col min="9992" max="9992" width="11.5546875" style="38" customWidth="1"/>
+    <col min="9993" max="9993" width="10.6640625" style="38" customWidth="1"/>
+    <col min="9994" max="9994" width="11.33203125" style="38" customWidth="1"/>
+    <col min="9995" max="9995" width="11.109375" style="38" customWidth="1"/>
+    <col min="9996" max="9996" width="11.6640625" style="38" customWidth="1"/>
+    <col min="9997" max="9997" width="11.44140625" style="38" customWidth="1"/>
+    <col min="9998" max="10000" width="10.6640625" style="38" customWidth="1"/>
+    <col min="10001" max="10003" width="10.5546875" style="38" customWidth="1"/>
+    <col min="10004" max="10004" width="11" style="38" customWidth="1"/>
+    <col min="10005" max="10005" width="10.6640625" style="38" customWidth="1"/>
+    <col min="10006" max="10006" width="10.5546875" style="38" customWidth="1"/>
+    <col min="10007" max="10007" width="13.5546875" style="38" customWidth="1"/>
+    <col min="10008" max="10008" width="11.109375" style="38" customWidth="1"/>
+    <col min="10009" max="10009" width="11.88671875" style="38" customWidth="1"/>
+    <col min="10010" max="10010" width="10.5546875" style="38" customWidth="1"/>
+    <col min="10011" max="10011" width="10.6640625" style="38" customWidth="1"/>
+    <col min="10012" max="10012" width="10.5546875" style="38" customWidth="1"/>
+    <col min="10013" max="10013" width="13.5546875" style="38" customWidth="1"/>
+    <col min="10014" max="10014" width="12.44140625" style="38" customWidth="1"/>
+    <col min="10015" max="10243" width="9.109375" style="38"/>
+    <col min="10244" max="10244" width="30.109375" style="38" customWidth="1"/>
+    <col min="10245" max="10245" width="33.33203125" style="38" customWidth="1"/>
+    <col min="10246" max="10246" width="11" style="38" customWidth="1"/>
+    <col min="10247" max="10247" width="12.5546875" style="38" customWidth="1"/>
+    <col min="10248" max="10248" width="11.5546875" style="38" customWidth="1"/>
+    <col min="10249" max="10249" width="10.6640625" style="38" customWidth="1"/>
+    <col min="10250" max="10250" width="11.33203125" style="38" customWidth="1"/>
+    <col min="10251" max="10251" width="11.109375" style="38" customWidth="1"/>
+    <col min="10252" max="10252" width="11.6640625" style="38" customWidth="1"/>
+    <col min="10253" max="10253" width="11.44140625" style="38" customWidth="1"/>
+    <col min="10254" max="10256" width="10.6640625" style="38" customWidth="1"/>
+    <col min="10257" max="10259" width="10.5546875" style="38" customWidth="1"/>
+    <col min="10260" max="10260" width="11" style="38" customWidth="1"/>
+    <col min="10261" max="10261" width="10.6640625" style="38" customWidth="1"/>
+    <col min="10262" max="10262" width="10.5546875" style="38" customWidth="1"/>
+    <col min="10263" max="10263" width="13.5546875" style="38" customWidth="1"/>
+    <col min="10264" max="10264" width="11.109375" style="38" customWidth="1"/>
+    <col min="10265" max="10265" width="11.88671875" style="38" customWidth="1"/>
+    <col min="10266" max="10266" width="10.5546875" style="38" customWidth="1"/>
+    <col min="10267" max="10267" width="10.6640625" style="38" customWidth="1"/>
+    <col min="10268" max="10268" width="10.5546875" style="38" customWidth="1"/>
+    <col min="10269" max="10269" width="13.5546875" style="38" customWidth="1"/>
+    <col min="10270" max="10270" width="12.44140625" style="38" customWidth="1"/>
+    <col min="10271" max="10499" width="9.109375" style="38"/>
+    <col min="10500" max="10500" width="30.109375" style="38" customWidth="1"/>
+    <col min="10501" max="10501" width="33.33203125" style="38" customWidth="1"/>
+    <col min="10502" max="10502" width="11" style="38" customWidth="1"/>
+    <col min="10503" max="10503" width="12.5546875" style="38" customWidth="1"/>
+    <col min="10504" max="10504" width="11.5546875" style="38" customWidth="1"/>
+    <col min="10505" max="10505" width="10.6640625" style="38" customWidth="1"/>
+    <col min="10506" max="10506" width="11.33203125" style="38" customWidth="1"/>
+    <col min="10507" max="10507" width="11.109375" style="38" customWidth="1"/>
+    <col min="10508" max="10508" width="11.6640625" style="38" customWidth="1"/>
+    <col min="10509" max="10509" width="11.44140625" style="38" customWidth="1"/>
+    <col min="10510" max="10512" width="10.6640625" style="38" customWidth="1"/>
+    <col min="10513" max="10515" width="10.5546875" style="38" customWidth="1"/>
+    <col min="10516" max="10516" width="11" style="38" customWidth="1"/>
+    <col min="10517" max="10517" width="10.6640625" style="38" customWidth="1"/>
+    <col min="10518" max="10518" width="10.5546875" style="38" customWidth="1"/>
+    <col min="10519" max="10519" width="13.5546875" style="38" customWidth="1"/>
+    <col min="10520" max="10520" width="11.109375" style="38" customWidth="1"/>
+    <col min="10521" max="10521" width="11.88671875" style="38" customWidth="1"/>
+    <col min="10522" max="10522" width="10.5546875" style="38" customWidth="1"/>
+    <col min="10523" max="10523" width="10.6640625" style="38" customWidth="1"/>
+    <col min="10524" max="10524" width="10.5546875" style="38" customWidth="1"/>
+    <col min="10525" max="10525" width="13.5546875" style="38" customWidth="1"/>
+    <col min="10526" max="10526" width="12.44140625" style="38" customWidth="1"/>
+    <col min="10527" max="10755" width="9.109375" style="38"/>
+    <col min="10756" max="10756" width="30.109375" style="38" customWidth="1"/>
+    <col min="10757" max="10757" width="33.33203125" style="38" customWidth="1"/>
+    <col min="10758" max="10758" width="11" style="38" customWidth="1"/>
+    <col min="10759" max="10759" width="12.5546875" style="38" customWidth="1"/>
+    <col min="10760" max="10760" width="11.5546875" style="38" customWidth="1"/>
+    <col min="10761" max="10761" width="10.6640625" style="38" customWidth="1"/>
+    <col min="10762" max="10762" width="11.33203125" style="38" customWidth="1"/>
+    <col min="10763" max="10763" width="11.109375" style="38" customWidth="1"/>
+    <col min="10764" max="10764" width="11.6640625" style="38" customWidth="1"/>
+    <col min="10765" max="10765" width="11.44140625" style="38" customWidth="1"/>
+    <col min="10766" max="10768" width="10.6640625" style="38" customWidth="1"/>
+    <col min="10769" max="10771" width="10.5546875" style="38" customWidth="1"/>
+    <col min="10772" max="10772" width="11" style="38" customWidth="1"/>
+    <col min="10773" max="10773" width="10.6640625" style="38" customWidth="1"/>
+    <col min="10774" max="10774" width="10.5546875" style="38" customWidth="1"/>
+    <col min="10775" max="10775" width="13.5546875" style="38" customWidth="1"/>
+    <col min="10776" max="10776" width="11.109375" style="38" customWidth="1"/>
+    <col min="10777" max="10777" width="11.88671875" style="38" customWidth="1"/>
+    <col min="10778" max="10778" width="10.5546875" style="38" customWidth="1"/>
+    <col min="10779" max="10779" width="10.6640625" style="38" customWidth="1"/>
+    <col min="10780" max="10780" width="10.5546875" style="38" customWidth="1"/>
+    <col min="10781" max="10781" width="13.5546875" style="38" customWidth="1"/>
+    <col min="10782" max="10782" width="12.44140625" style="38" customWidth="1"/>
+    <col min="10783" max="11011" width="9.109375" style="38"/>
+    <col min="11012" max="11012" width="30.109375" style="38" customWidth="1"/>
+    <col min="11013" max="11013" width="33.33203125" style="38" customWidth="1"/>
+    <col min="11014" max="11014" width="11" style="38" customWidth="1"/>
+    <col min="11015" max="11015" width="12.5546875" style="38" customWidth="1"/>
+    <col min="11016" max="11016" width="11.5546875" style="38" customWidth="1"/>
+    <col min="11017" max="11017" width="10.6640625" style="38" customWidth="1"/>
+    <col min="11018" max="11018" width="11.33203125" style="38" customWidth="1"/>
+    <col min="11019" max="11019" width="11.109375" style="38" customWidth="1"/>
+    <col min="11020" max="11020" width="11.6640625" style="38" customWidth="1"/>
+    <col min="11021" max="11021" width="11.44140625" style="38" customWidth="1"/>
+    <col min="11022" max="11024" width="10.6640625" style="38" customWidth="1"/>
+    <col min="11025" max="11027" width="10.5546875" style="38" customWidth="1"/>
+    <col min="11028" max="11028" width="11" style="38" customWidth="1"/>
+    <col min="11029" max="11029" width="10.6640625" style="38" customWidth="1"/>
+    <col min="11030" max="11030" width="10.5546875" style="38" customWidth="1"/>
+    <col min="11031" max="11031" width="13.5546875" style="38" customWidth="1"/>
+    <col min="11032" max="11032" width="11.109375" style="38" customWidth="1"/>
+    <col min="11033" max="11033" width="11.88671875" style="38" customWidth="1"/>
+    <col min="11034" max="11034" width="10.5546875" style="38" customWidth="1"/>
+    <col min="11035" max="11035" width="10.6640625" style="38" customWidth="1"/>
+    <col min="11036" max="11036" width="10.5546875" style="38" customWidth="1"/>
+    <col min="11037" max="11037" width="13.5546875" style="38" customWidth="1"/>
+    <col min="11038" max="11038" width="12.44140625" style="38" customWidth="1"/>
+    <col min="11039" max="11267" width="9.109375" style="38"/>
+    <col min="11268" max="11268" width="30.109375" style="38" customWidth="1"/>
+    <col min="11269" max="11269" width="33.33203125" style="38" customWidth="1"/>
+    <col min="11270" max="11270" width="11" style="38" customWidth="1"/>
+    <col min="11271" max="11271" width="12.5546875" style="38" customWidth="1"/>
+    <col min="11272" max="11272" width="11.5546875" style="38" customWidth="1"/>
+    <col min="11273" max="11273" width="10.6640625" style="38" customWidth="1"/>
+    <col min="11274" max="11274" width="11.33203125" style="38" customWidth="1"/>
+    <col min="11275" max="11275" width="11.109375" style="38" customWidth="1"/>
+    <col min="11276" max="11276" width="11.6640625" style="38" customWidth="1"/>
+    <col min="11277" max="11277" width="11.44140625" style="38" customWidth="1"/>
+    <col min="11278" max="11280" width="10.6640625" style="38" customWidth="1"/>
+    <col min="11281" max="11283" width="10.5546875" style="38" customWidth="1"/>
+    <col min="11284" max="11284" width="11" style="38" customWidth="1"/>
+    <col min="11285" max="11285" width="10.6640625" style="38" customWidth="1"/>
+    <col min="11286" max="11286" width="10.5546875" style="38" customWidth="1"/>
+    <col min="11287" max="11287" width="13.5546875" style="38" customWidth="1"/>
+    <col min="11288" max="11288" width="11.109375" style="38" customWidth="1"/>
+    <col min="11289" max="11289" width="11.88671875" style="38" customWidth="1"/>
+    <col min="11290" max="11290" width="10.5546875" style="38" customWidth="1"/>
+    <col min="11291" max="11291" width="10.6640625" style="38" customWidth="1"/>
+    <col min="11292" max="11292" width="10.5546875" style="38" customWidth="1"/>
+    <col min="11293" max="11293" width="13.5546875" style="38" customWidth="1"/>
+    <col min="11294" max="11294" width="12.44140625" style="38" customWidth="1"/>
+    <col min="11295" max="11523" width="9.109375" style="38"/>
+    <col min="11524" max="11524" width="30.109375" style="38" customWidth="1"/>
+    <col min="11525" max="11525" width="33.33203125" style="38" customWidth="1"/>
+    <col min="11526" max="11526" width="11" style="38" customWidth="1"/>
+    <col min="11527" max="11527" width="12.5546875" style="38" customWidth="1"/>
+    <col min="11528" max="11528" width="11.5546875" style="38" customWidth="1"/>
+    <col min="11529" max="11529" width="10.6640625" style="38" customWidth="1"/>
+    <col min="11530" max="11530" width="11.33203125" style="38" customWidth="1"/>
+    <col min="11531" max="11531" width="11.109375" style="38" customWidth="1"/>
+    <col min="11532" max="11532" width="11.6640625" style="38" customWidth="1"/>
+    <col min="11533" max="11533" width="11.44140625" style="38" customWidth="1"/>
+    <col min="11534" max="11536" width="10.6640625" style="38" customWidth="1"/>
+    <col min="11537" max="11539" width="10.5546875" style="38" customWidth="1"/>
+    <col min="11540" max="11540" width="11" style="38" customWidth="1"/>
+    <col min="11541" max="11541" width="10.6640625" style="38" customWidth="1"/>
+    <col min="11542" max="11542" width="10.5546875" style="38" customWidth="1"/>
+    <col min="11543" max="11543" width="13.5546875" style="38" customWidth="1"/>
+    <col min="11544" max="11544" width="11.109375" style="38" customWidth="1"/>
+    <col min="11545" max="11545" width="11.88671875" style="38" customWidth="1"/>
+    <col min="11546" max="11546" width="10.5546875" style="38" customWidth="1"/>
+    <col min="11547" max="11547" width="10.6640625" style="38" customWidth="1"/>
+    <col min="11548" max="11548" width="10.5546875" style="38" customWidth="1"/>
+    <col min="11549" max="11549" width="13.5546875" style="38" customWidth="1"/>
+    <col min="11550" max="11550" width="12.44140625" style="38" customWidth="1"/>
+    <col min="11551" max="11779" width="9.109375" style="38"/>
+    <col min="11780" max="11780" width="30.109375" style="38" customWidth="1"/>
+    <col min="11781" max="11781" width="33.33203125" style="38" customWidth="1"/>
+    <col min="11782" max="11782" width="11" style="38" customWidth="1"/>
+    <col min="11783" max="11783" width="12.5546875" style="38" customWidth="1"/>
+    <col min="11784" max="11784" width="11.5546875" style="38" customWidth="1"/>
+    <col min="11785" max="11785" width="10.6640625" style="38" customWidth="1"/>
+    <col min="11786" max="11786" width="11.33203125" style="38" customWidth="1"/>
+    <col min="11787" max="11787" width="11.109375" style="38" customWidth="1"/>
+    <col min="11788" max="11788" width="11.6640625" style="38" customWidth="1"/>
+    <col min="11789" max="11789" width="11.44140625" style="38" customWidth="1"/>
+    <col min="11790" max="11792" width="10.6640625" style="38" customWidth="1"/>
+    <col min="11793" max="11795" width="10.5546875" style="38" customWidth="1"/>
+    <col min="11796" max="11796" width="11" style="38" customWidth="1"/>
+    <col min="11797" max="11797" width="10.6640625" style="38" customWidth="1"/>
+    <col min="11798" max="11798" width="10.5546875" style="38" customWidth="1"/>
+    <col min="11799" max="11799" width="13.5546875" style="38" customWidth="1"/>
+    <col min="11800" max="11800" width="11.109375" style="38" customWidth="1"/>
+    <col min="11801" max="11801" width="11.88671875" style="38" customWidth="1"/>
+    <col min="11802" max="11802" width="10.5546875" style="38" customWidth="1"/>
+    <col min="11803" max="11803" width="10.6640625" style="38" customWidth="1"/>
+    <col min="11804" max="11804" width="10.5546875" style="38" customWidth="1"/>
+    <col min="11805" max="11805" width="13.5546875" style="38" customWidth="1"/>
+    <col min="11806" max="11806" width="12.44140625" style="38" customWidth="1"/>
+    <col min="11807" max="12035" width="9.109375" style="38"/>
+    <col min="12036" max="12036" width="30.109375" style="38" customWidth="1"/>
+    <col min="12037" max="12037" width="33.33203125" style="38" customWidth="1"/>
+    <col min="12038" max="12038" width="11" style="38" customWidth="1"/>
+    <col min="12039" max="12039" width="12.5546875" style="38" customWidth="1"/>
+    <col min="12040" max="12040" width="11.5546875" style="38" customWidth="1"/>
+    <col min="12041" max="12041" width="10.6640625" style="38" customWidth="1"/>
+    <col min="12042" max="12042" width="11.33203125" style="38" customWidth="1"/>
+    <col min="12043" max="12043" width="11.109375" style="38" customWidth="1"/>
+    <col min="12044" max="12044" width="11.6640625" style="38" customWidth="1"/>
+    <col min="12045" max="12045" width="11.44140625" style="38" customWidth="1"/>
+    <col min="12046" max="12048" width="10.6640625" style="38" customWidth="1"/>
+    <col min="12049" max="12051" width="10.5546875" style="38" customWidth="1"/>
+    <col min="12052" max="12052" width="11" style="38" customWidth="1"/>
+    <col min="12053" max="12053" width="10.6640625" style="38" customWidth="1"/>
+    <col min="12054" max="12054" width="10.5546875" style="38" customWidth="1"/>
+    <col min="12055" max="12055" width="13.5546875" style="38" customWidth="1"/>
+    <col min="12056" max="12056" width="11.109375" style="38" customWidth="1"/>
+    <col min="12057" max="12057" width="11.88671875" style="38" customWidth="1"/>
+    <col min="12058" max="12058" width="10.5546875" style="38" customWidth="1"/>
+    <col min="12059" max="12059" width="10.6640625" style="38" customWidth="1"/>
+    <col min="12060" max="12060" width="10.5546875" style="38" customWidth="1"/>
+    <col min="12061" max="12061" width="13.5546875" style="38" customWidth="1"/>
+    <col min="12062" max="12062" width="12.44140625" style="38" customWidth="1"/>
+    <col min="12063" max="12291" width="9.109375" style="38"/>
+    <col min="12292" max="12292" width="30.109375" style="38" customWidth="1"/>
+    <col min="12293" max="12293" width="33.33203125" style="38" customWidth="1"/>
+    <col min="12294" max="12294" width="11" style="38" customWidth="1"/>
+    <col min="12295" max="12295" width="12.5546875" style="38" customWidth="1"/>
+    <col min="12296" max="12296" width="11.5546875" style="38" customWidth="1"/>
+    <col min="12297" max="12297" width="10.6640625" style="38" customWidth="1"/>
+    <col min="12298" max="12298" width="11.33203125" style="38" customWidth="1"/>
+    <col min="12299" max="12299" width="11.109375" style="38" customWidth="1"/>
+    <col min="12300" max="12300" width="11.6640625" style="38" customWidth="1"/>
+    <col min="12301" max="12301" width="11.44140625" style="38" customWidth="1"/>
+    <col min="12302" max="12304" width="10.6640625" style="38" customWidth="1"/>
+    <col min="12305" max="12307" width="10.5546875" style="38" customWidth="1"/>
+    <col min="12308" max="12308" width="11" style="38" customWidth="1"/>
+    <col min="12309" max="12309" width="10.6640625" style="38" customWidth="1"/>
+    <col min="12310" max="12310" width="10.5546875" style="38" customWidth="1"/>
+    <col min="12311" max="12311" width="13.5546875" style="38" customWidth="1"/>
+    <col min="12312" max="12312" width="11.109375" style="38" customWidth="1"/>
+    <col min="12313" max="12313" width="11.88671875" style="38" customWidth="1"/>
+    <col min="12314" max="12314" width="10.5546875" style="38" customWidth="1"/>
+    <col min="12315" max="12315" width="10.6640625" style="38" customWidth="1"/>
+    <col min="12316" max="12316" width="10.5546875" style="38" customWidth="1"/>
+    <col min="12317" max="12317" width="13.5546875" style="38" customWidth="1"/>
+    <col min="12318" max="12318" width="12.44140625" style="38" customWidth="1"/>
+    <col min="12319" max="12547" width="9.109375" style="38"/>
+    <col min="12548" max="12548" width="30.109375" style="38" customWidth="1"/>
+    <col min="12549" max="12549" width="33.33203125" style="38" customWidth="1"/>
+    <col min="12550" max="12550" width="11" style="38" customWidth="1"/>
+    <col min="12551" max="12551" width="12.5546875" style="38" customWidth="1"/>
+    <col min="12552" max="12552" width="11.5546875" style="38" customWidth="1"/>
+    <col min="12553" max="12553" width="10.6640625" style="38" customWidth="1"/>
+    <col min="12554" max="12554" width="11.33203125" style="38" customWidth="1"/>
+    <col min="12555" max="12555" width="11.109375" style="38" customWidth="1"/>
+    <col min="12556" max="12556" width="11.6640625" style="38" customWidth="1"/>
+    <col min="12557" max="12557" width="11.44140625" style="38" customWidth="1"/>
+    <col min="12558" max="12560" width="10.6640625" style="38" customWidth="1"/>
+    <col min="12561" max="12563" width="10.5546875" style="38" customWidth="1"/>
+    <col min="12564" max="12564" width="11" style="38" customWidth="1"/>
+    <col min="12565" max="12565" width="10.6640625" style="38" customWidth="1"/>
+    <col min="12566" max="12566" width="10.5546875" style="38" customWidth="1"/>
+    <col min="12567" max="12567" width="13.5546875" style="38" customWidth="1"/>
+    <col min="12568" max="12568" width="11.109375" style="38" customWidth="1"/>
+    <col min="12569" max="12569" width="11.88671875" style="38" customWidth="1"/>
+    <col min="12570" max="12570" width="10.5546875" style="38" customWidth="1"/>
+    <col min="12571" max="12571" width="10.6640625" style="38" customWidth="1"/>
+    <col min="12572" max="12572" width="10.5546875" style="38" customWidth="1"/>
+    <col min="12573" max="12573" width="13.5546875" style="38" customWidth="1"/>
+    <col min="12574" max="12574" width="12.44140625" style="38" customWidth="1"/>
+    <col min="12575" max="12803" width="9.109375" style="38"/>
+    <col min="12804" max="12804" width="30.109375" style="38" customWidth="1"/>
+    <col min="12805" max="12805" width="33.33203125" style="38" customWidth="1"/>
+    <col min="12806" max="12806" width="11" style="38" customWidth="1"/>
+    <col min="12807" max="12807" width="12.5546875" style="38" customWidth="1"/>
+    <col min="12808" max="12808" width="11.5546875" style="38" customWidth="1"/>
+    <col min="12809" max="12809" width="10.6640625" style="38" customWidth="1"/>
+    <col min="12810" max="12810" width="11.33203125" style="38" customWidth="1"/>
+    <col min="12811" max="12811" width="11.109375" style="38" customWidth="1"/>
+    <col min="12812" max="12812" width="11.6640625" style="38" customWidth="1"/>
+    <col min="12813" max="12813" width="11.44140625" style="38" customWidth="1"/>
+    <col min="12814" max="12816" width="10.6640625" style="38" customWidth="1"/>
+    <col min="12817" max="12819" width="10.5546875" style="38" customWidth="1"/>
+    <col min="12820" max="12820" width="11" style="38" customWidth="1"/>
+    <col min="12821" max="12821" width="10.6640625" style="38" customWidth="1"/>
+    <col min="12822" max="12822" width="10.5546875" style="38" customWidth="1"/>
+    <col min="12823" max="12823" width="13.5546875" style="38" customWidth="1"/>
+    <col min="12824" max="12824" width="11.109375" style="38" customWidth="1"/>
+    <col min="12825" max="12825" width="11.88671875" style="38" customWidth="1"/>
+    <col min="12826" max="12826" width="10.5546875" style="38" customWidth="1"/>
+    <col min="12827" max="12827" width="10.6640625" style="38" customWidth="1"/>
+    <col min="12828" max="12828" width="10.5546875" style="38" customWidth="1"/>
+    <col min="12829" max="12829" width="13.5546875" style="38" customWidth="1"/>
+    <col min="12830" max="12830" width="12.44140625" style="38" customWidth="1"/>
+    <col min="12831" max="13059" width="9.109375" style="38"/>
+    <col min="13060" max="13060" width="30.109375" style="38" customWidth="1"/>
+    <col min="13061" max="13061" width="33.33203125" style="38" customWidth="1"/>
+    <col min="13062" max="13062" width="11" style="38" customWidth="1"/>
+    <col min="13063" max="13063" width="12.5546875" style="38" customWidth="1"/>
+    <col min="13064" max="13064" width="11.5546875" style="38" customWidth="1"/>
+    <col min="13065" max="13065" width="10.6640625" style="38" customWidth="1"/>
+    <col min="13066" max="13066" width="11.33203125" style="38" customWidth="1"/>
+    <col min="13067" max="13067" width="11.109375" style="38" customWidth="1"/>
+    <col min="13068" max="13068" width="11.6640625" style="38" customWidth="1"/>
+    <col min="13069" max="13069" width="11.44140625" style="38" customWidth="1"/>
+    <col min="13070" max="13072" width="10.6640625" style="38" customWidth="1"/>
+    <col min="13073" max="13075" width="10.5546875" style="38" customWidth="1"/>
+    <col min="13076" max="13076" width="11" style="38" customWidth="1"/>
+    <col min="13077" max="13077" width="10.6640625" style="38" customWidth="1"/>
+    <col min="13078" max="13078" width="10.5546875" style="38" customWidth="1"/>
+    <col min="13079" max="13079" width="13.5546875" style="38" customWidth="1"/>
+    <col min="13080" max="13080" width="11.109375" style="38" customWidth="1"/>
+    <col min="13081" max="13081" width="11.88671875" style="38" customWidth="1"/>
+    <col min="13082" max="13082" width="10.5546875" style="38" customWidth="1"/>
+    <col min="13083" max="13083" width="10.6640625" style="38" customWidth="1"/>
+    <col min="13084" max="13084" width="10.5546875" style="38" customWidth="1"/>
+    <col min="13085" max="13085" width="13.5546875" style="38" customWidth="1"/>
+    <col min="13086" max="13086" width="12.44140625" style="38" customWidth="1"/>
+    <col min="13087" max="13315" width="9.109375" style="38"/>
+    <col min="13316" max="13316" width="30.109375" style="38" customWidth="1"/>
+    <col min="13317" max="13317" width="33.33203125" style="38" customWidth="1"/>
+    <col min="13318" max="13318" width="11" style="38" customWidth="1"/>
+    <col min="13319" max="13319" width="12.5546875" style="38" customWidth="1"/>
+    <col min="13320" max="13320" width="11.5546875" style="38" customWidth="1"/>
+    <col min="13321" max="13321" width="10.6640625" style="38" customWidth="1"/>
+    <col min="13322" max="13322" width="11.33203125" style="38" customWidth="1"/>
+    <col min="13323" max="13323" width="11.109375" style="38" customWidth="1"/>
+    <col min="13324" max="13324" width="11.6640625" style="38" customWidth="1"/>
+    <col min="13325" max="13325" width="11.44140625" style="38" customWidth="1"/>
+    <col min="13326" max="13328" width="10.6640625" style="38" customWidth="1"/>
+    <col min="13329" max="13331" width="10.5546875" style="38" customWidth="1"/>
+    <col min="13332" max="13332" width="11" style="38" customWidth="1"/>
+    <col min="13333" max="13333" width="10.6640625" style="38" customWidth="1"/>
+    <col min="13334" max="13334" width="10.5546875" style="38" customWidth="1"/>
+    <col min="13335" max="13335" width="13.5546875" style="38" customWidth="1"/>
+    <col min="13336" max="13336" width="11.109375" style="38" customWidth="1"/>
+    <col min="13337" max="13337" width="11.88671875" style="38" customWidth="1"/>
+    <col min="13338" max="13338" width="10.5546875" style="38" customWidth="1"/>
+    <col min="13339" max="13339" width="10.6640625" style="38" customWidth="1"/>
+    <col min="13340" max="13340" width="10.5546875" style="38" customWidth="1"/>
+    <col min="13341" max="13341" width="13.5546875" style="38" customWidth="1"/>
+    <col min="13342" max="13342" width="12.44140625" style="38" customWidth="1"/>
+    <col min="13343" max="13571" width="9.109375" style="38"/>
+    <col min="13572" max="13572" width="30.109375" style="38" customWidth="1"/>
+    <col min="13573" max="13573" width="33.33203125" style="38" customWidth="1"/>
+    <col min="13574" max="13574" width="11" style="38" customWidth="1"/>
+    <col min="13575" max="13575" width="12.5546875" style="38" customWidth="1"/>
+    <col min="13576" max="13576" width="11.5546875" style="38" customWidth="1"/>
+    <col min="13577" max="13577" width="10.6640625" style="38" customWidth="1"/>
+    <col min="13578" max="13578" width="11.33203125" style="38" customWidth="1"/>
+    <col min="13579" max="13579" width="11.109375" style="38" customWidth="1"/>
+    <col min="13580" max="13580" width="11.6640625" style="38" customWidth="1"/>
+    <col min="13581" max="13581" width="11.44140625" style="38" customWidth="1"/>
+    <col min="13582" max="13584" width="10.6640625" style="38" customWidth="1"/>
+    <col min="13585" max="13587" width="10.5546875" style="38" customWidth="1"/>
+    <col min="13588" max="13588" width="11" style="38" customWidth="1"/>
+    <col min="13589" max="13589" width="10.6640625" style="38" customWidth="1"/>
+    <col min="13590" max="13590" width="10.5546875" style="38" customWidth="1"/>
+    <col min="13591" max="13591" width="13.5546875" style="38" customWidth="1"/>
+    <col min="13592" max="13592" width="11.109375" style="38" customWidth="1"/>
+    <col min="13593" max="13593" width="11.88671875" style="38" customWidth="1"/>
+    <col min="13594" max="13594" width="10.5546875" style="38" customWidth="1"/>
+    <col min="13595" max="13595" width="10.6640625" style="38" customWidth="1"/>
+    <col min="13596" max="13596" width="10.5546875" style="38" customWidth="1"/>
+    <col min="13597" max="13597" width="13.5546875" style="38" customWidth="1"/>
+    <col min="13598" max="13598" width="12.44140625" style="38" customWidth="1"/>
+    <col min="13599" max="13827" width="9.109375" style="38"/>
+    <col min="13828" max="13828" width="30.109375" style="38" customWidth="1"/>
+    <col min="13829" max="13829" width="33.33203125" style="38" customWidth="1"/>
+    <col min="13830" max="13830" width="11" style="38" customWidth="1"/>
+    <col min="13831" max="13831" width="12.5546875" style="38" customWidth="1"/>
+    <col min="13832" max="13832" width="11.5546875" style="38" customWidth="1"/>
+    <col min="13833" max="13833" width="10.6640625" style="38" customWidth="1"/>
+    <col min="13834" max="13834" width="11.33203125" style="38" customWidth="1"/>
+    <col min="13835" max="13835" width="11.109375" style="38" customWidth="1"/>
+    <col min="13836" max="13836" width="11.6640625" style="38" customWidth="1"/>
+    <col min="13837" max="13837" width="11.44140625" style="38" customWidth="1"/>
+    <col min="13838" max="13840" width="10.6640625" style="38" customWidth="1"/>
+    <col min="13841" max="13843" width="10.5546875" style="38" customWidth="1"/>
+    <col min="13844" max="13844" width="11" style="38" customWidth="1"/>
+    <col min="13845" max="13845" width="10.6640625" style="38" customWidth="1"/>
+    <col min="13846" max="13846" width="10.5546875" style="38" customWidth="1"/>
+    <col min="13847" max="13847" width="13.5546875" style="38" customWidth="1"/>
+    <col min="13848" max="13848" width="11.109375" style="38" customWidth="1"/>
+    <col min="13849" max="13849" width="11.88671875" style="38" customWidth="1"/>
+    <col min="13850" max="13850" width="10.5546875" style="38" customWidth="1"/>
+    <col min="13851" max="13851" width="10.6640625" style="38" customWidth="1"/>
+    <col min="13852" max="13852" width="10.5546875" style="38" customWidth="1"/>
+    <col min="13853" max="13853" width="13.5546875" style="38" customWidth="1"/>
+    <col min="13854" max="13854" width="12.44140625" style="38" customWidth="1"/>
+    <col min="13855" max="14083" width="9.109375" style="38"/>
+    <col min="14084" max="14084" width="30.109375" style="38" customWidth="1"/>
+    <col min="14085" max="14085" width="33.33203125" style="38" customWidth="1"/>
+    <col min="14086" max="14086" width="11" style="38" customWidth="1"/>
+    <col min="14087" max="14087" width="12.5546875" style="38" customWidth="1"/>
+    <col min="14088" max="14088" width="11.5546875" style="38" customWidth="1"/>
+    <col min="14089" max="14089" width="10.6640625" style="38" customWidth="1"/>
+    <col min="14090" max="14090" width="11.33203125" style="38" customWidth="1"/>
+    <col min="14091" max="14091" width="11.109375" style="38" customWidth="1"/>
+    <col min="14092" max="14092" width="11.6640625" style="38" customWidth="1"/>
+    <col min="14093" max="14093" width="11.44140625" style="38" customWidth="1"/>
+    <col min="14094" max="14096" width="10.6640625" style="38" customWidth="1"/>
+    <col min="14097" max="14099" width="10.5546875" style="38" customWidth="1"/>
+    <col min="14100" max="14100" width="11" style="38" customWidth="1"/>
+    <col min="14101" max="14101" width="10.6640625" style="38" customWidth="1"/>
+    <col min="14102" max="14102" width="10.5546875" style="38" customWidth="1"/>
+    <col min="14103" max="14103" width="13.5546875" style="38" customWidth="1"/>
+    <col min="14104" max="14104" width="11.109375" style="38" customWidth="1"/>
+    <col min="14105" max="14105" width="11.88671875" style="38" customWidth="1"/>
+    <col min="14106" max="14106" width="10.5546875" style="38" customWidth="1"/>
+    <col min="14107" max="14107" width="10.6640625" style="38" customWidth="1"/>
+    <col min="14108" max="14108" width="10.5546875" style="38" customWidth="1"/>
+    <col min="14109" max="14109" width="13.5546875" style="38" customWidth="1"/>
+    <col min="14110" max="14110" width="12.44140625" style="38" customWidth="1"/>
+    <col min="14111" max="14339" width="9.109375" style="38"/>
+    <col min="14340" max="14340" width="30.109375" style="38" customWidth="1"/>
+    <col min="14341" max="14341" width="33.33203125" style="38" customWidth="1"/>
+    <col min="14342" max="14342" width="11" style="38" customWidth="1"/>
+    <col min="14343" max="14343" width="12.5546875" style="38" customWidth="1"/>
+    <col min="14344" max="14344" width="11.5546875" style="38" customWidth="1"/>
+    <col min="14345" max="14345" width="10.6640625" style="38" customWidth="1"/>
+    <col min="14346" max="14346" width="11.33203125" style="38" customWidth="1"/>
+    <col min="14347" max="14347" width="11.109375" style="38" customWidth="1"/>
+    <col min="14348" max="14348" width="11.6640625" style="38" customWidth="1"/>
+    <col min="14349" max="14349" width="11.44140625" style="38" customWidth="1"/>
+    <col min="14350" max="14352" width="10.6640625" style="38" customWidth="1"/>
+    <col min="14353" max="14355" width="10.5546875" style="38" customWidth="1"/>
+    <col min="14356" max="14356" width="11" style="38" customWidth="1"/>
+    <col min="14357" max="14357" width="10.6640625" style="38" customWidth="1"/>
+    <col min="14358" max="14358" width="10.5546875" style="38" customWidth="1"/>
+    <col min="14359" max="14359" width="13.5546875" style="38" customWidth="1"/>
+    <col min="14360" max="14360" width="11.109375" style="38" customWidth="1"/>
+    <col min="14361" max="14361" width="11.88671875" style="38" customWidth="1"/>
+    <col min="14362" max="14362" width="10.5546875" style="38" customWidth="1"/>
+    <col min="14363" max="14363" width="10.6640625" style="38" customWidth="1"/>
+    <col min="14364" max="14364" width="10.5546875" style="38" customWidth="1"/>
+    <col min="14365" max="14365" width="13.5546875" style="38" customWidth="1"/>
+    <col min="14366" max="14366" width="12.44140625" style="38" customWidth="1"/>
+    <col min="14367" max="14595" width="9.109375" style="38"/>
+    <col min="14596" max="14596" width="30.109375" style="38" customWidth="1"/>
+    <col min="14597" max="14597" width="33.33203125" style="38" customWidth="1"/>
+    <col min="14598" max="14598" width="11" style="38" customWidth="1"/>
+    <col min="14599" max="14599" width="12.5546875" style="38" customWidth="1"/>
+    <col min="14600" max="14600" width="11.5546875" style="38" customWidth="1"/>
+    <col min="14601" max="14601" width="10.6640625" style="38" customWidth="1"/>
+    <col min="14602" max="14602" width="11.33203125" style="38" customWidth="1"/>
+    <col min="14603" max="14603" width="11.109375" style="38" customWidth="1"/>
+    <col min="14604" max="14604" width="11.6640625" style="38" customWidth="1"/>
+    <col min="14605" max="14605" width="11.44140625" style="38" customWidth="1"/>
+    <col min="14606" max="14608" width="10.6640625" style="38" customWidth="1"/>
+    <col min="14609" max="14611" width="10.5546875" style="38" customWidth="1"/>
+    <col min="14612" max="14612" width="11" style="38" customWidth="1"/>
+    <col min="14613" max="14613" width="10.6640625" style="38" customWidth="1"/>
+    <col min="14614" max="14614" width="10.5546875" style="38" customWidth="1"/>
+    <col min="14615" max="14615" width="13.5546875" style="38" customWidth="1"/>
+    <col min="14616" max="14616" width="11.109375" style="38" customWidth="1"/>
+    <col min="14617" max="14617" width="11.88671875" style="38" customWidth="1"/>
+    <col min="14618" max="14618" width="10.5546875" style="38" customWidth="1"/>
+    <col min="14619" max="14619" width="10.6640625" style="38" customWidth="1"/>
+    <col min="14620" max="14620" width="10.5546875" style="38" customWidth="1"/>
+    <col min="14621" max="14621" width="13.5546875" style="38" customWidth="1"/>
+    <col min="14622" max="14622" width="12.44140625" style="38" customWidth="1"/>
+    <col min="14623" max="14851" width="9.109375" style="38"/>
+    <col min="14852" max="14852" width="30.109375" style="38" customWidth="1"/>
+    <col min="14853" max="14853" width="33.33203125" style="38" customWidth="1"/>
+    <col min="14854" max="14854" width="11" style="38" customWidth="1"/>
+    <col min="14855" max="14855" width="12.5546875" style="38" customWidth="1"/>
+    <col min="14856" max="14856" width="11.5546875" style="38" customWidth="1"/>
+    <col min="14857" max="14857" width="10.6640625" style="38" customWidth="1"/>
+    <col min="14858" max="14858" width="11.33203125" style="38" customWidth="1"/>
+    <col min="14859" max="14859" width="11.109375" style="38" customWidth="1"/>
+    <col min="14860" max="14860" width="11.6640625" style="38" customWidth="1"/>
+    <col min="14861" max="14861" width="11.44140625" style="38" customWidth="1"/>
+    <col min="14862" max="14864" width="10.6640625" style="38" customWidth="1"/>
+    <col min="14865" max="14867" width="10.5546875" style="38" customWidth="1"/>
+    <col min="14868" max="14868" width="11" style="38" customWidth="1"/>
+    <col min="14869" max="14869" width="10.6640625" style="38" customWidth="1"/>
+    <col min="14870" max="14870" width="10.5546875" style="38" customWidth="1"/>
+    <col min="14871" max="14871" width="13.5546875" style="38" customWidth="1"/>
+    <col min="14872" max="14872" width="11.109375" style="38" customWidth="1"/>
+    <col min="14873" max="14873" width="11.88671875" style="38" customWidth="1"/>
+    <col min="14874" max="14874" width="10.5546875" style="38" customWidth="1"/>
+    <col min="14875" max="14875" width="10.6640625" style="38" customWidth="1"/>
+    <col min="14876" max="14876" width="10.5546875" style="38" customWidth="1"/>
+    <col min="14877" max="14877" width="13.5546875" style="38" customWidth="1"/>
+    <col min="14878" max="14878" width="12.44140625" style="38" customWidth="1"/>
+    <col min="14879" max="15107" width="9.109375" style="38"/>
+    <col min="15108" max="15108" width="30.109375" style="38" customWidth="1"/>
+    <col min="15109" max="15109" width="33.33203125" style="38" customWidth="1"/>
+    <col min="15110" max="15110" width="11" style="38" customWidth="1"/>
+    <col min="15111" max="15111" width="12.5546875" style="38" customWidth="1"/>
+    <col min="15112" max="15112" width="11.5546875" style="38" customWidth="1"/>
+    <col min="15113" max="15113" width="10.6640625" style="38" customWidth="1"/>
+    <col min="15114" max="15114" width="11.33203125" style="38" customWidth="1"/>
+    <col min="15115" max="15115" width="11.109375" style="38" customWidth="1"/>
+    <col min="15116" max="15116" width="11.6640625" style="38" customWidth="1"/>
+    <col min="15117" max="15117" width="11.44140625" style="38" customWidth="1"/>
+    <col min="15118" max="15120" width="10.6640625" style="38" customWidth="1"/>
+    <col min="15121" max="15123" width="10.5546875" style="38" customWidth="1"/>
+    <col min="15124" max="15124" width="11" style="38" customWidth="1"/>
+    <col min="15125" max="15125" width="10.6640625" style="38" customWidth="1"/>
+    <col min="15126" max="15126" width="10.5546875" style="38" customWidth="1"/>
+    <col min="15127" max="15127" width="13.5546875" style="38" customWidth="1"/>
+    <col min="15128" max="15128" width="11.109375" style="38" customWidth="1"/>
+    <col min="15129" max="15129" width="11.88671875" style="38" customWidth="1"/>
+    <col min="15130" max="15130" width="10.5546875" style="38" customWidth="1"/>
+    <col min="15131" max="15131" width="10.6640625" style="38" customWidth="1"/>
+    <col min="15132" max="15132" width="10.5546875" style="38" customWidth="1"/>
+    <col min="15133" max="15133" width="13.5546875" style="38" customWidth="1"/>
+    <col min="15134" max="15134" width="12.44140625" style="38" customWidth="1"/>
+    <col min="15135" max="15363" width="9.109375" style="38"/>
+    <col min="15364" max="15364" width="30.109375" style="38" customWidth="1"/>
+    <col min="15365" max="15365" width="33.33203125" style="38" customWidth="1"/>
+    <col min="15366" max="15366" width="11" style="38" customWidth="1"/>
+    <col min="15367" max="15367" width="12.5546875" style="38" customWidth="1"/>
+    <col min="15368" max="15368" width="11.5546875" style="38" customWidth="1"/>
+    <col min="15369" max="15369" width="10.6640625" style="38" customWidth="1"/>
+    <col min="15370" max="15370" width="11.33203125" style="38" customWidth="1"/>
+    <col min="15371" max="15371" width="11.109375" style="38" customWidth="1"/>
+    <col min="15372" max="15372" width="11.6640625" style="38" customWidth="1"/>
+    <col min="15373" max="15373" width="11.44140625" style="38" customWidth="1"/>
+    <col min="15374" max="15376" width="10.6640625" style="38" customWidth="1"/>
+    <col min="15377" max="15379" width="10.5546875" style="38" customWidth="1"/>
+    <col min="15380" max="15380" width="11" style="38" customWidth="1"/>
+    <col min="15381" max="15381" width="10.6640625" style="38" customWidth="1"/>
+    <col min="15382" max="15382" width="10.5546875" style="38" customWidth="1"/>
+    <col min="15383" max="15383" width="13.5546875" style="38" customWidth="1"/>
+    <col min="15384" max="15384" width="11.109375" style="38" customWidth="1"/>
+    <col min="15385" max="15385" width="11.88671875" style="38" customWidth="1"/>
+    <col min="15386" max="15386" width="10.5546875" style="38" customWidth="1"/>
+    <col min="15387" max="15387" width="10.6640625" style="38" customWidth="1"/>
+    <col min="15388" max="15388" width="10.5546875" style="38" customWidth="1"/>
+    <col min="15389" max="15389" width="13.5546875" style="38" customWidth="1"/>
+    <col min="15390" max="15390" width="12.44140625" style="38" customWidth="1"/>
+    <col min="15391" max="15619" width="9.109375" style="38"/>
+    <col min="15620" max="15620" width="30.109375" style="38" customWidth="1"/>
+    <col min="15621" max="15621" width="33.33203125" style="38" customWidth="1"/>
+    <col min="15622" max="15622" width="11" style="38" customWidth="1"/>
+    <col min="15623" max="15623" width="12.5546875" style="38" customWidth="1"/>
+    <col min="15624" max="15624" width="11.5546875" style="38" customWidth="1"/>
+    <col min="15625" max="15625" width="10.6640625" style="38" customWidth="1"/>
+    <col min="15626" max="15626" width="11.33203125" style="38" customWidth="1"/>
+    <col min="15627" max="15627" width="11.109375" style="38" customWidth="1"/>
+    <col min="15628" max="15628" width="11.6640625" style="38" customWidth="1"/>
+    <col min="15629" max="15629" width="11.44140625" style="38" customWidth="1"/>
+    <col min="15630" max="15632" width="10.6640625" style="38" customWidth="1"/>
+    <col min="15633" max="15635" width="10.5546875" style="38" customWidth="1"/>
+    <col min="15636" max="15636" width="11" style="38" customWidth="1"/>
+    <col min="15637" max="15637" width="10.6640625" style="38" customWidth="1"/>
+    <col min="15638" max="15638" width="10.5546875" style="38" customWidth="1"/>
+    <col min="15639" max="15639" width="13.5546875" style="38" customWidth="1"/>
+    <col min="15640" max="15640" width="11.109375" style="38" customWidth="1"/>
+    <col min="15641" max="15641" width="11.88671875" style="38" customWidth="1"/>
+    <col min="15642" max="15642" width="10.5546875" style="38" customWidth="1"/>
+    <col min="15643" max="15643" width="10.6640625" style="38" customWidth="1"/>
+    <col min="15644" max="15644" width="10.5546875" style="38" customWidth="1"/>
+    <col min="15645" max="15645" width="13.5546875" style="38" customWidth="1"/>
+    <col min="15646" max="15646" width="12.44140625" style="38" customWidth="1"/>
+    <col min="15647" max="15875" width="9.109375" style="38"/>
+    <col min="15876" max="15876" width="30.109375" style="38" customWidth="1"/>
+    <col min="15877" max="15877" width="33.33203125" style="38" customWidth="1"/>
+    <col min="15878" max="15878" width="11" style="38" customWidth="1"/>
+    <col min="15879" max="15879" width="12.5546875" style="38" customWidth="1"/>
+    <col min="15880" max="15880" width="11.5546875" style="38" customWidth="1"/>
+    <col min="15881" max="15881" width="10.6640625" style="38" customWidth="1"/>
+    <col min="15882" max="15882" width="11.33203125" style="38" customWidth="1"/>
+    <col min="15883" max="15883" width="11.109375" style="38" customWidth="1"/>
+    <col min="15884" max="15884" width="11.6640625" style="38" customWidth="1"/>
+    <col min="15885" max="15885" width="11.44140625" style="38" customWidth="1"/>
+    <col min="15886" max="15888" width="10.6640625" style="38" customWidth="1"/>
+    <col min="15889" max="15891" width="10.5546875" style="38" customWidth="1"/>
+    <col min="15892" max="15892" width="11" style="38" customWidth="1"/>
+    <col min="15893" max="15893" width="10.6640625" style="38" customWidth="1"/>
+    <col min="15894" max="15894" width="10.5546875" style="38" customWidth="1"/>
+    <col min="15895" max="15895" width="13.5546875" style="38" customWidth="1"/>
+    <col min="15896" max="15896" width="11.109375" style="38" customWidth="1"/>
+    <col min="15897" max="15897" width="11.88671875" style="38" customWidth="1"/>
+    <col min="15898" max="15898" width="10.5546875" style="38" customWidth="1"/>
+    <col min="15899" max="15899" width="10.6640625" style="38" customWidth="1"/>
+    <col min="15900" max="15900" width="10.5546875" style="38" customWidth="1"/>
+    <col min="15901" max="15901" width="13.5546875" style="38" customWidth="1"/>
+    <col min="15902" max="15902" width="12.44140625" style="38" customWidth="1"/>
+    <col min="15903" max="16131" width="9.109375" style="38"/>
+    <col min="16132" max="16132" width="30.109375" style="38" customWidth="1"/>
+    <col min="16133" max="16133" width="33.33203125" style="38" customWidth="1"/>
+    <col min="16134" max="16134" width="11" style="38" customWidth="1"/>
+    <col min="16135" max="16135" width="12.5546875" style="38" customWidth="1"/>
+    <col min="16136" max="16136" width="11.5546875" style="38" customWidth="1"/>
+    <col min="16137" max="16137" width="10.6640625" style="38" customWidth="1"/>
+    <col min="16138" max="16138" width="11.33203125" style="38" customWidth="1"/>
+    <col min="16139" max="16139" width="11.109375" style="38" customWidth="1"/>
+    <col min="16140" max="16140" width="11.6640625" style="38" customWidth="1"/>
+    <col min="16141" max="16141" width="11.44140625" style="38" customWidth="1"/>
+    <col min="16142" max="16144" width="10.6640625" style="38" customWidth="1"/>
+    <col min="16145" max="16147" width="10.5546875" style="38" customWidth="1"/>
+    <col min="16148" max="16148" width="11" style="38" customWidth="1"/>
+    <col min="16149" max="16149" width="10.6640625" style="38" customWidth="1"/>
+    <col min="16150" max="16150" width="10.5546875" style="38" customWidth="1"/>
+    <col min="16151" max="16151" width="13.5546875" style="38" customWidth="1"/>
+    <col min="16152" max="16152" width="11.109375" style="38" customWidth="1"/>
+    <col min="16153" max="16153" width="11.88671875" style="38" customWidth="1"/>
+    <col min="16154" max="16154" width="10.5546875" style="38" customWidth="1"/>
+    <col min="16155" max="16155" width="10.6640625" style="38" customWidth="1"/>
+    <col min="16156" max="16156" width="10.5546875" style="38" customWidth="1"/>
+    <col min="16157" max="16157" width="13.5546875" style="38" customWidth="1"/>
+    <col min="16158" max="16158" width="12.44140625" style="38" customWidth="1"/>
+    <col min="16159" max="16384" width="9.109375" style="38"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A1" s="67" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
-      <c r="V1" s="78"/>
-      <c r="W1" s="78"/>
-      <c r="X1" s="78"/>
-      <c r="Y1" s="78"/>
-      <c r="Z1" s="78"/>
-      <c r="AA1" s="78"/>
-      <c r="AB1" s="78"/>
-    </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A2" s="78" t="s">
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="67"/>
+      <c r="N1" s="67"/>
+      <c r="O1" s="67"/>
+      <c r="P1" s="67"/>
+      <c r="Q1" s="67"/>
+      <c r="R1" s="67"/>
+      <c r="S1" s="67"/>
+      <c r="T1" s="67"/>
+      <c r="U1" s="67"/>
+      <c r="V1" s="67"/>
+      <c r="W1" s="67"/>
+      <c r="X1" s="67"/>
+      <c r="Y1" s="67"/>
+      <c r="Z1" s="67"/>
+      <c r="AA1" s="67"/>
+      <c r="AB1" s="67"/>
+      <c r="AC1" s="67"/>
+      <c r="AD1" s="67"/>
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A2" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
-      <c r="M2" s="78"/>
-      <c r="N2" s="78"/>
-      <c r="O2" s="78"/>
-      <c r="P2" s="78"/>
-      <c r="Q2" s="78"/>
-      <c r="R2" s="78"/>
-      <c r="S2" s="78"/>
-      <c r="T2" s="78"/>
-      <c r="U2" s="78"/>
-      <c r="V2" s="78"/>
-      <c r="W2" s="78"/>
-      <c r="X2" s="78"/>
-      <c r="Y2" s="78"/>
-      <c r="Z2" s="78"/>
-      <c r="AA2" s="78"/>
-      <c r="AB2" s="78"/>
-    </row>
-    <row r="3" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="79" t="s">
-        <v>190</v>
-      </c>
-      <c r="B3" s="79"/>
-      <c r="C3" s="79"/>
-      <c r="D3" s="79"/>
-      <c r="G3" s="77" t="s">
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
+      <c r="N2" s="67"/>
+      <c r="O2" s="67"/>
+      <c r="P2" s="67"/>
+      <c r="Q2" s="67"/>
+      <c r="R2" s="67"/>
+      <c r="S2" s="67"/>
+      <c r="T2" s="67"/>
+      <c r="U2" s="67"/>
+      <c r="V2" s="67"/>
+      <c r="W2" s="67"/>
+      <c r="X2" s="67"/>
+      <c r="Y2" s="67"/>
+      <c r="Z2" s="67"/>
+      <c r="AA2" s="67"/>
+      <c r="AB2" s="67"/>
+      <c r="AC2" s="67"/>
+      <c r="AD2" s="67"/>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A3" s="68" t="s">
+        <v>189</v>
+      </c>
+      <c r="B3" s="68"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="G3" s="80" t="s">
         <v>32</v>
       </c>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
-      <c r="K3" s="77"/>
-      <c r="L3" s="77"/>
-      <c r="M3" s="77"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
-      <c r="V3" s="77" t="s">
+      <c r="H3" s="80"/>
+      <c r="I3" s="80"/>
+      <c r="J3" s="80"/>
+      <c r="K3" s="80"/>
+      <c r="L3" s="80"/>
+      <c r="M3" s="80"/>
+      <c r="N3" s="80"/>
+      <c r="O3" s="80"/>
+      <c r="P3" s="80"/>
+      <c r="Q3" s="80"/>
+      <c r="R3" s="80"/>
+      <c r="S3" s="63"/>
+      <c r="T3" s="63"/>
+      <c r="U3" s="63"/>
+      <c r="V3" s="63"/>
+      <c r="W3" s="63"/>
+      <c r="X3" s="80" t="s">
         <v>30</v>
       </c>
-      <c r="W3" s="77"/>
-      <c r="X3" s="77"/>
-      <c r="Y3" s="77"/>
-      <c r="Z3" s="77"/>
-      <c r="AA3" s="77"/>
-      <c r="AB3" s="90"/>
-    </row>
-    <row r="4" spans="1:29" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="69" t="s">
+      <c r="Y3" s="80"/>
+      <c r="Z3" s="80"/>
+      <c r="AA3" s="80"/>
+      <c r="AB3" s="80"/>
+      <c r="AC3" s="80"/>
+      <c r="AD3" s="94"/>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A4" s="72" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="69" t="s">
+      <c r="B4" s="72" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="66" t="s">
+      <c r="C4" s="69" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="69" t="s">
         <v>77</v>
       </c>
-      <c r="D4" s="66"/>
-      <c r="E4" s="66"/>
-      <c r="F4" s="66" t="s">
+      <c r="G4" s="69"/>
+      <c r="H4" s="69" t="s">
+        <v>53</v>
+      </c>
+      <c r="I4" s="69"/>
+      <c r="J4" s="70" t="s">
+        <v>81</v>
+      </c>
+      <c r="K4" s="71"/>
+      <c r="L4" s="70" t="s">
+        <v>59</v>
+      </c>
+      <c r="M4" s="71"/>
+      <c r="N4" s="69" t="s">
+        <v>133</v>
+      </c>
+      <c r="O4" s="69"/>
+      <c r="P4" s="69" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q4" s="69"/>
+      <c r="R4" s="73" t="s">
         <v>78</v>
       </c>
-      <c r="G4" s="66"/>
-      <c r="H4" s="66" t="s">
-        <v>53</v>
-      </c>
-      <c r="I4" s="66"/>
-      <c r="J4" s="67" t="s">
-        <v>82</v>
-      </c>
-      <c r="K4" s="68"/>
-      <c r="L4" s="67" t="s">
-        <v>59</v>
-      </c>
-      <c r="M4" s="68"/>
-      <c r="N4" s="66" t="s">
-        <v>134</v>
-      </c>
-      <c r="O4" s="66"/>
-      <c r="P4" s="66" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q4" s="66"/>
-      <c r="R4" s="70" t="s">
+      <c r="S4" s="76"/>
+      <c r="T4" s="70" t="s">
+        <v>194</v>
+      </c>
+      <c r="U4" s="71"/>
+      <c r="V4" s="73" t="s">
+        <v>56</v>
+      </c>
+      <c r="W4" s="76"/>
+      <c r="X4" s="73" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y4" s="92"/>
+      <c r="Z4" s="73" t="s">
         <v>79</v>
       </c>
-      <c r="S4" s="73"/>
-      <c r="T4" s="70" t="s">
-        <v>56</v>
-      </c>
-      <c r="U4" s="73"/>
-      <c r="V4" s="70" t="s">
-        <v>44</v>
-      </c>
-      <c r="W4" s="92"/>
-      <c r="X4" s="70" t="s">
+      <c r="AA4" s="76"/>
+      <c r="AB4" s="93" t="s">
         <v>80</v>
       </c>
-      <c r="Y4" s="73"/>
-      <c r="Z4" s="66" t="s">
-        <v>81</v>
-      </c>
-      <c r="AA4" s="66"/>
-      <c r="AB4" s="69" t="s">
+      <c r="AC4" s="93"/>
+      <c r="AD4" s="72" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A5" s="69"/>
-      <c r="B5" s="69"/>
+    <row r="5" spans="1:31" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A5" s="72"/>
+      <c r="B5" s="72"/>
       <c r="C5" s="10" t="s">
         <v>19</v>
       </c>
@@ -4063,13 +4103,13 @@
       <c r="V5" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="W5" s="34" t="s">
+      <c r="W5" s="10" t="s">
         <v>23</v>
       </c>
       <c r="X5" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="Y5" s="10" t="s">
+      <c r="Y5" s="33" t="s">
         <v>23</v>
       </c>
       <c r="Z5" s="10" t="s">
@@ -4078,129 +4118,143 @@
       <c r="AA5" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="AB5" s="69"/>
-    </row>
-    <row r="6" spans="1:29" s="41" customFormat="1" ht="60" x14ac:dyDescent="0.3">
-      <c r="A6" s="69"/>
-      <c r="B6" s="69"/>
-      <c r="C6" s="37" t="s">
+      <c r="AB5" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC5" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD5" s="72"/>
+    </row>
+    <row r="6" spans="1:31" s="40" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A6" s="72"/>
+      <c r="B6" s="72"/>
+      <c r="C6" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="37" t="s">
+      <c r="D6" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="37" t="s">
+      <c r="E6" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="37" t="s">
+      <c r="F6" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="G6" s="37" t="s">
+      <c r="G6" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="37" t="s">
+      <c r="H6" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="37" t="s">
+      <c r="I6" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="J6" s="37" t="s">
+      <c r="J6" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="K6" s="37" t="s">
+      <c r="K6" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="L6" s="37" t="s">
+      <c r="L6" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="M6" s="37" t="s">
+      <c r="M6" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="N6" s="37" t="s">
+      <c r="N6" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="O6" s="37" t="s">
+      <c r="O6" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="P6" s="37" t="s">
+      <c r="P6" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="Q6" s="37" t="s">
+      <c r="Q6" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="R6" s="37" t="s">
+      <c r="R6" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="S6" s="37" t="s">
+      <c r="S6" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="T6" s="37" t="s">
+      <c r="T6" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="U6" s="37" t="s">
+      <c r="U6" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="V6" s="37" t="s">
+      <c r="V6" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="W6" s="37" t="s">
+      <c r="W6" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="X6" s="37" t="s">
+      <c r="X6" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="Y6" s="37" t="s">
+      <c r="Y6" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="Z6" s="37" t="s">
+      <c r="Z6" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="AA6" s="37" t="s">
+      <c r="AA6" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="AB6" s="37" t="s">
+      <c r="AB6" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="AC6" s="40"/>
-    </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC6" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD6" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE6" s="39"/>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" s="91" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="78"/>
-      <c r="C7" s="78"/>
-      <c r="D7" s="78"/>
-      <c r="E7" s="78"/>
-      <c r="F7" s="75"/>
-      <c r="G7" s="75"/>
-      <c r="H7" s="75"/>
-      <c r="I7" s="75"/>
-      <c r="J7" s="75"/>
-      <c r="K7" s="75"/>
-      <c r="L7" s="75"/>
-      <c r="M7" s="75"/>
-      <c r="N7" s="75"/>
-      <c r="O7" s="75"/>
-      <c r="P7" s="75"/>
-      <c r="Q7" s="75"/>
-      <c r="R7" s="75"/>
-      <c r="S7" s="75"/>
-      <c r="T7" s="75"/>
-      <c r="U7" s="75"/>
-      <c r="V7" s="75"/>
-      <c r="W7" s="75"/>
-      <c r="X7" s="75"/>
-      <c r="Y7" s="75"/>
-      <c r="Z7" s="75"/>
-      <c r="AA7" s="75"/>
-      <c r="AB7" s="75"/>
-    </row>
-    <row r="8" spans="1:29" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="30" t="s">
-        <v>83</v>
+      <c r="B7" s="67"/>
+      <c r="C7" s="67"/>
+      <c r="D7" s="67"/>
+      <c r="E7" s="67"/>
+      <c r="F7" s="78"/>
+      <c r="G7" s="78"/>
+      <c r="H7" s="78"/>
+      <c r="I7" s="78"/>
+      <c r="J7" s="78"/>
+      <c r="K7" s="78"/>
+      <c r="L7" s="78"/>
+      <c r="M7" s="78"/>
+      <c r="N7" s="78"/>
+      <c r="O7" s="78"/>
+      <c r="P7" s="78"/>
+      <c r="Q7" s="78"/>
+      <c r="R7" s="78"/>
+      <c r="S7" s="78"/>
+      <c r="T7" s="78"/>
+      <c r="U7" s="78"/>
+      <c r="V7" s="78"/>
+      <c r="W7" s="78"/>
+      <c r="X7" s="78"/>
+      <c r="Y7" s="78"/>
+      <c r="Z7" s="78"/>
+      <c r="AA7" s="78"/>
+      <c r="AB7" s="78"/>
+      <c r="AC7" s="78"/>
+      <c r="AD7" s="78"/>
+    </row>
+    <row r="8" spans="1:31" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A8" s="29" t="s">
+        <v>82</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C8" s="10"/>
       <c r="D8" s="10"/>
@@ -4219,36 +4273,38 @@
       </c>
       <c r="N8" s="10"/>
       <c r="O8" s="10"/>
-      <c r="P8" s="43" t="s">
-        <v>132</v>
+      <c r="P8" s="42" t="s">
+        <v>131</v>
       </c>
       <c r="Q8" s="10"/>
       <c r="R8" s="10"/>
       <c r="S8" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="T8" s="10" t="s">
+      <c r="T8" s="10"/>
+      <c r="U8" s="10"/>
+      <c r="V8" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="U8" s="10"/>
-      <c r="V8" s="10"/>
       <c r="W8" s="10"/>
       <c r="X8" s="10"/>
-      <c r="Y8" s="10" t="s">
-        <v>41</v>
-      </c>
+      <c r="Y8" s="10"/>
       <c r="Z8" s="10"/>
       <c r="AA8" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB8" s="10"/>
+      <c r="AC8" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AB8" s="10"/>
-    </row>
-    <row r="9" spans="1:29" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="30" t="s">
-        <v>84</v>
-      </c>
-      <c r="B9" s="30" t="s">
-        <v>87</v>
+      <c r="AD8" s="10"/>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A9" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="29" t="s">
+        <v>86</v>
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="10"/>
@@ -4282,13 +4338,15 @@
       <c r="Z9" s="10"/>
       <c r="AA9" s="10"/>
       <c r="AB9" s="10"/>
-    </row>
-    <row r="10" spans="1:29" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="B10" s="30" t="s">
-        <v>186</v>
+      <c r="AC9" s="10"/>
+      <c r="AD9" s="10"/>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A10" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="B10" s="29" t="s">
+        <v>185</v>
       </c>
       <c r="C10" s="10"/>
       <c r="D10" s="10"/>
@@ -4309,7 +4367,7 @@
       <c r="O10" s="10"/>
       <c r="P10" s="10"/>
       <c r="Q10" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="R10" s="10"/>
       <c r="S10" s="10" t="s">
@@ -4320,21 +4378,23 @@
       <c r="V10" s="10"/>
       <c r="W10" s="10"/>
       <c r="X10" s="10"/>
-      <c r="Y10" s="10" t="s">
-        <v>39</v>
-      </c>
+      <c r="Y10" s="10"/>
       <c r="Z10" s="10"/>
       <c r="AA10" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB10" s="10"/>
+      <c r="AC10" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="AB10" s="10"/>
-    </row>
-    <row r="11" spans="1:29" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="B11" s="30" t="s">
-        <v>187</v>
+      <c r="AD10" s="10"/>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A11" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" s="29" t="s">
+        <v>186</v>
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="10"/>
@@ -4355,22 +4415,24 @@
       <c r="S11" s="10"/>
       <c r="T11" s="10"/>
       <c r="U11" s="10"/>
-      <c r="V11" s="10" t="s">
+      <c r="V11" s="10"/>
+      <c r="W11" s="10"/>
+      <c r="X11" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="W11" s="10"/>
-      <c r="X11" s="10"/>
       <c r="Y11" s="10"/>
       <c r="Z11" s="10"/>
       <c r="AA11" s="10"/>
       <c r="AB11" s="10"/>
-    </row>
-    <row r="12" spans="1:29" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="53" t="s">
-        <v>101</v>
-      </c>
-      <c r="B12" s="30" t="s">
-        <v>103</v>
+      <c r="AC11" s="10"/>
+      <c r="AD11" s="10"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A12" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="B12" s="29" t="s">
+        <v>102</v>
       </c>
       <c r="C12" s="10"/>
       <c r="D12" s="10"/>
@@ -4397,16 +4459,18 @@
       <c r="Y12" s="10"/>
       <c r="Z12" s="10"/>
       <c r="AA12" s="10"/>
-      <c r="AB12" s="10" t="s">
+      <c r="AB12" s="10"/>
+      <c r="AC12" s="10"/>
+      <c r="AD12" s="10" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="53" t="s">
-        <v>102</v>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A13" s="52" t="s">
+        <v>101</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="10"/>
@@ -4436,13 +4500,15 @@
       <c r="Z13" s="10"/>
       <c r="AA13" s="10"/>
       <c r="AB13" s="10"/>
-    </row>
-    <row r="14" spans="1:29" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="53" t="s">
-        <v>83</v>
+      <c r="AC13" s="10"/>
+      <c r="AD13" s="10"/>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A14" s="52" t="s">
+        <v>82</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C14" s="10"/>
       <c r="D14" s="10"/>
@@ -4456,7 +4522,7 @@
       <c r="L14" s="10"/>
       <c r="M14" s="10"/>
       <c r="N14" s="10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O14" s="10"/>
       <c r="P14" s="10"/>
@@ -4472,45 +4538,49 @@
       <c r="Z14" s="10"/>
       <c r="AA14" s="10"/>
       <c r="AB14" s="10"/>
-    </row>
-    <row r="15" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="66" t="s">
+      <c r="AC14" s="10"/>
+      <c r="AD14" s="10"/>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A15" s="69" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="66"/>
-      <c r="C15" s="66"/>
-      <c r="D15" s="66"/>
-      <c r="E15" s="66"/>
-      <c r="F15" s="66"/>
-      <c r="G15" s="66"/>
-      <c r="H15" s="66"/>
-      <c r="I15" s="66"/>
-      <c r="J15" s="66"/>
-      <c r="K15" s="66"/>
-      <c r="L15" s="66"/>
-      <c r="M15" s="66"/>
-      <c r="N15" s="66"/>
-      <c r="O15" s="66"/>
-      <c r="P15" s="66"/>
-      <c r="Q15" s="66"/>
-      <c r="R15" s="66"/>
-      <c r="S15" s="66"/>
-      <c r="T15" s="66"/>
-      <c r="U15" s="66"/>
-      <c r="V15" s="66"/>
-      <c r="W15" s="66"/>
-      <c r="X15" s="66"/>
-      <c r="Y15" s="66"/>
-      <c r="Z15" s="66"/>
-      <c r="AA15" s="66"/>
-      <c r="AB15" s="66"/>
-    </row>
-    <row r="16" spans="1:29" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="69"/>
+      <c r="C15" s="69"/>
+      <c r="D15" s="69"/>
+      <c r="E15" s="69"/>
+      <c r="F15" s="69"/>
+      <c r="G15" s="69"/>
+      <c r="H15" s="69"/>
+      <c r="I15" s="69"/>
+      <c r="J15" s="69"/>
+      <c r="K15" s="69"/>
+      <c r="L15" s="69"/>
+      <c r="M15" s="69"/>
+      <c r="N15" s="69"/>
+      <c r="O15" s="69"/>
+      <c r="P15" s="69"/>
+      <c r="Q15" s="69"/>
+      <c r="R15" s="69"/>
+      <c r="S15" s="69"/>
+      <c r="T15" s="69"/>
+      <c r="U15" s="69"/>
+      <c r="V15" s="69"/>
+      <c r="W15" s="69"/>
+      <c r="X15" s="69"/>
+      <c r="Y15" s="69"/>
+      <c r="Z15" s="69"/>
+      <c r="AA15" s="69"/>
+      <c r="AB15" s="69"/>
+      <c r="AC15" s="69"/>
+      <c r="AD15" s="69"/>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16" s="24" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C16" s="13"/>
       <c r="D16" s="13"/>
@@ -4540,13 +4610,15 @@
       <c r="Z16" s="13"/>
       <c r="AA16" s="13"/>
       <c r="AB16" s="13"/>
-    </row>
-    <row r="17" spans="1:28" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AC16" s="13"/>
+      <c r="AD16" s="13"/>
+    </row>
+    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C17" s="15"/>
       <c r="D17" s="15"/>
@@ -4576,13 +4648,15 @@
       <c r="Z17" s="15"/>
       <c r="AA17" s="15"/>
       <c r="AB17" s="15"/>
-    </row>
-    <row r="18" spans="1:28" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AC17" s="15"/>
+      <c r="AD17" s="15"/>
+    </row>
+    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="18" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C18" s="15"/>
       <c r="D18" s="15"/>
@@ -4604,21 +4678,23 @@
       <c r="T18" s="15"/>
       <c r="U18" s="15"/>
       <c r="V18" s="15"/>
-      <c r="W18" s="15" t="s">
+      <c r="W18" s="15"/>
+      <c r="X18" s="15"/>
+      <c r="Y18" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="X18" s="15"/>
-      <c r="Y18" s="15"/>
       <c r="Z18" s="15"/>
       <c r="AA18" s="15"/>
       <c r="AB18" s="15"/>
-    </row>
-    <row r="19" spans="1:28" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="30" t="s">
-        <v>89</v>
+      <c r="AC18" s="15"/>
+      <c r="AD18" s="15"/>
+    </row>
+    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A19" s="29" t="s">
+        <v>88</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C19" s="15"/>
       <c r="D19" s="15"/>
@@ -4640,21 +4716,23 @@
       <c r="T19" s="15"/>
       <c r="U19" s="15"/>
       <c r="V19" s="15"/>
-      <c r="W19" s="15" t="s">
+      <c r="W19" s="15"/>
+      <c r="X19" s="15"/>
+      <c r="Y19" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="X19" s="15"/>
-      <c r="Y19" s="15"/>
       <c r="Z19" s="15"/>
       <c r="AA19" s="15"/>
       <c r="AB19" s="15"/>
-    </row>
-    <row r="20" spans="1:28" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="30" t="s">
-        <v>90</v>
+      <c r="AC19" s="15"/>
+      <c r="AD19" s="15"/>
+    </row>
+    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A20" s="29" t="s">
+        <v>89</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C20" s="15"/>
       <c r="D20" s="15"/>
@@ -4676,21 +4754,23 @@
       <c r="T20" s="15"/>
       <c r="U20" s="15"/>
       <c r="V20" s="15"/>
-      <c r="W20" s="15" t="s">
+      <c r="W20" s="15"/>
+      <c r="X20" s="15"/>
+      <c r="Y20" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="X20" s="15"/>
-      <c r="Y20" s="15"/>
       <c r="Z20" s="15"/>
       <c r="AA20" s="15"/>
       <c r="AB20" s="15"/>
-    </row>
-    <row r="21" spans="1:28" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AC20" s="15"/>
+      <c r="AD20" s="15"/>
+    </row>
+    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C21" s="15"/>
       <c r="D21" s="15"/>
@@ -4711,22 +4791,24 @@
       <c r="S21" s="15"/>
       <c r="T21" s="15"/>
       <c r="U21" s="15"/>
-      <c r="V21" s="15" t="s">
+      <c r="V21" s="15"/>
+      <c r="W21" s="15"/>
+      <c r="X21" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="W21" s="15"/>
-      <c r="X21" s="15"/>
       <c r="Y21" s="15"/>
       <c r="Z21" s="15"/>
       <c r="AA21" s="15"/>
       <c r="AB21" s="15"/>
-    </row>
-    <row r="22" spans="1:28" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AC21" s="15"/>
+      <c r="AD21" s="15"/>
+    </row>
+    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="18" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C22" s="16"/>
       <c r="D22" s="15"/>
@@ -4747,22 +4829,24 @@
       <c r="S22" s="15"/>
       <c r="T22" s="15"/>
       <c r="U22" s="15"/>
-      <c r="V22" s="15" t="s">
+      <c r="V22" s="15"/>
+      <c r="W22" s="15"/>
+      <c r="X22" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="W22" s="15"/>
-      <c r="X22" s="15"/>
       <c r="Y22" s="15"/>
       <c r="Z22" s="15"/>
       <c r="AA22" s="15"/>
       <c r="AB22" s="15"/>
-    </row>
-    <row r="23" spans="1:28" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="30" t="s">
-        <v>91</v>
+      <c r="AC22" s="15"/>
+      <c r="AD22" s="15"/>
+    </row>
+    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A23" s="29" t="s">
+        <v>90</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C23" s="17"/>
       <c r="D23" s="17"/>
@@ -4792,13 +4876,15 @@
       <c r="Z23" s="13"/>
       <c r="AA23" s="13"/>
       <c r="AB23" s="13"/>
-    </row>
-    <row r="24" spans="1:28" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AC23" s="13"/>
+      <c r="AD23" s="13"/>
+    </row>
+    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="24" t="s">
-        <v>85</v>
-      </c>
-      <c r="B24" s="33" t="s">
-        <v>189</v>
+        <v>84</v>
+      </c>
+      <c r="B24" s="32" t="s">
+        <v>188</v>
       </c>
       <c r="C24" s="13"/>
       <c r="D24" s="17"/>
@@ -4817,26 +4903,28 @@
       <c r="O24" s="13"/>
       <c r="P24" s="13"/>
       <c r="Q24" s="13" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R24" s="13"/>
       <c r="S24" s="13"/>
       <c r="T24" s="13"/>
       <c r="U24" s="13"/>
-      <c r="V24" s="17"/>
+      <c r="V24" s="13"/>
       <c r="W24" s="13"/>
-      <c r="X24" s="13"/>
+      <c r="X24" s="17"/>
       <c r="Y24" s="13"/>
       <c r="Z24" s="13"/>
       <c r="AA24" s="13"/>
       <c r="AB24" s="13"/>
-    </row>
-    <row r="25" spans="1:28" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AC24" s="13"/>
+      <c r="AD24" s="13"/>
+    </row>
+    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="B25" s="33" t="s">
-        <v>100</v>
+        <v>91</v>
+      </c>
+      <c r="B25" s="32" t="s">
+        <v>99</v>
       </c>
       <c r="C25" s="15"/>
       <c r="D25" s="16"/>
@@ -4857,22 +4945,24 @@
       <c r="S25" s="15"/>
       <c r="T25" s="15"/>
       <c r="U25" s="15"/>
-      <c r="V25" s="16"/>
+      <c r="V25" s="15"/>
       <c r="W25" s="15"/>
-      <c r="X25" s="15"/>
+      <c r="X25" s="16"/>
       <c r="Y25" s="15"/>
       <c r="Z25" s="15"/>
-      <c r="AA25" s="15" t="s">
+      <c r="AA25" s="15"/>
+      <c r="AB25" s="15"/>
+      <c r="AC25" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="AB25" s="15"/>
-    </row>
-    <row r="26" spans="1:28" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AD25" s="15"/>
+    </row>
+    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="B26" s="33" t="s">
-        <v>110</v>
+        <v>104</v>
+      </c>
+      <c r="B26" s="32" t="s">
+        <v>109</v>
       </c>
       <c r="C26" s="15"/>
       <c r="D26" s="16"/>
@@ -4889,26 +4979,28 @@
       <c r="O26" s="15"/>
       <c r="P26" s="15"/>
       <c r="Q26" s="15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="R26" s="15"/>
       <c r="S26" s="15"/>
       <c r="T26" s="15"/>
       <c r="U26" s="15"/>
-      <c r="V26" s="16"/>
+      <c r="V26" s="15"/>
       <c r="W26" s="15"/>
-      <c r="X26" s="15"/>
+      <c r="X26" s="16"/>
       <c r="Y26" s="15"/>
       <c r="Z26" s="15"/>
       <c r="AA26" s="15"/>
       <c r="AB26" s="15"/>
-    </row>
-    <row r="27" spans="1:28" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AC26" s="15"/>
+      <c r="AD26" s="15"/>
+    </row>
+    <row r="27" spans="1:30" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A27" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="B27" s="33" t="s">
-        <v>111</v>
+        <v>105</v>
+      </c>
+      <c r="B27" s="32" t="s">
+        <v>110</v>
       </c>
       <c r="C27" s="15"/>
       <c r="D27" s="16"/>
@@ -4924,27 +5016,29 @@
       <c r="N27" s="15"/>
       <c r="O27" s="15"/>
       <c r="P27" s="15"/>
-      <c r="Q27" s="44" t="s">
-        <v>137</v>
+      <c r="Q27" s="43" t="s">
+        <v>136</v>
       </c>
       <c r="R27" s="15"/>
       <c r="S27" s="15"/>
       <c r="T27" s="15"/>
       <c r="U27" s="15"/>
-      <c r="V27" s="16"/>
+      <c r="V27" s="15"/>
       <c r="W27" s="15"/>
-      <c r="X27" s="15"/>
+      <c r="X27" s="16"/>
       <c r="Y27" s="15"/>
       <c r="Z27" s="15"/>
       <c r="AA27" s="15"/>
       <c r="AB27" s="15"/>
-    </row>
-    <row r="28" spans="1:28" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AC27" s="15"/>
+      <c r="AD27" s="15"/>
+    </row>
+    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="B28" s="33" t="s">
-        <v>112</v>
+        <v>106</v>
+      </c>
+      <c r="B28" s="32" t="s">
+        <v>111</v>
       </c>
       <c r="C28" s="15"/>
       <c r="D28" s="16"/>
@@ -4961,26 +5055,28 @@
       <c r="O28" s="15"/>
       <c r="P28" s="15"/>
       <c r="Q28" s="15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="R28" s="15"/>
       <c r="S28" s="15"/>
       <c r="T28" s="15"/>
       <c r="U28" s="15"/>
-      <c r="V28" s="16"/>
+      <c r="V28" s="15"/>
       <c r="W28" s="15"/>
-      <c r="X28" s="15"/>
+      <c r="X28" s="16"/>
       <c r="Y28" s="15"/>
       <c r="Z28" s="15"/>
       <c r="AA28" s="15"/>
       <c r="AB28" s="15"/>
-    </row>
-    <row r="29" spans="1:28" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AC28" s="15"/>
+      <c r="AD28" s="15"/>
+    </row>
+    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="B29" s="33" t="s">
-        <v>113</v>
+        <v>122</v>
+      </c>
+      <c r="B29" s="32" t="s">
+        <v>112</v>
       </c>
       <c r="C29" s="15"/>
       <c r="D29" s="16"/>
@@ -4996,27 +5092,29 @@
       <c r="N29" s="15"/>
       <c r="O29" s="15"/>
       <c r="P29" s="15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q29" s="15"/>
       <c r="R29" s="15"/>
       <c r="S29" s="15"/>
       <c r="T29" s="15"/>
       <c r="U29" s="15"/>
-      <c r="V29" s="16"/>
+      <c r="V29" s="15"/>
       <c r="W29" s="15"/>
-      <c r="X29" s="15"/>
+      <c r="X29" s="16"/>
       <c r="Y29" s="15"/>
       <c r="Z29" s="15"/>
       <c r="AA29" s="15"/>
       <c r="AB29" s="15"/>
-    </row>
-    <row r="30" spans="1:28" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AC29" s="15"/>
+      <c r="AD29" s="15"/>
+    </row>
+    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="B30" s="33" t="s">
-        <v>114</v>
+        <v>107</v>
+      </c>
+      <c r="B30" s="32" t="s">
+        <v>113</v>
       </c>
       <c r="C30" s="13"/>
       <c r="D30" s="17"/>
@@ -5039,22 +5137,24 @@
       <c r="S30" s="13"/>
       <c r="T30" s="13"/>
       <c r="U30" s="13"/>
-      <c r="V30" s="17"/>
+      <c r="V30" s="13"/>
       <c r="W30" s="13"/>
-      <c r="X30" s="13"/>
+      <c r="X30" s="17"/>
       <c r="Y30" s="13"/>
       <c r="Z30" s="13"/>
       <c r="AA30" s="13"/>
-      <c r="AB30" s="13" t="s">
+      <c r="AB30" s="13"/>
+      <c r="AC30" s="13"/>
+      <c r="AD30" s="13" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="31" spans="1:28" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="B31" s="33" t="s">
-        <v>115</v>
+        <v>108</v>
+      </c>
+      <c r="B31" s="32" t="s">
+        <v>114</v>
       </c>
       <c r="C31" s="13"/>
       <c r="D31" s="17"/>
@@ -5077,20 +5177,22 @@
       <c r="S31" s="13"/>
       <c r="T31" s="13"/>
       <c r="U31" s="13"/>
-      <c r="V31" s="17"/>
+      <c r="V31" s="13"/>
       <c r="W31" s="13"/>
-      <c r="X31" s="13"/>
+      <c r="X31" s="17"/>
       <c r="Y31" s="13"/>
       <c r="Z31" s="13"/>
       <c r="AA31" s="13"/>
       <c r="AB31" s="13"/>
-    </row>
-    <row r="32" spans="1:28" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AC31" s="13"/>
+      <c r="AD31" s="13"/>
+    </row>
+    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="B32" s="33" t="s">
-        <v>116</v>
+        <v>90</v>
+      </c>
+      <c r="B32" s="32" t="s">
+        <v>115</v>
       </c>
       <c r="C32" s="13"/>
       <c r="D32" s="17"/>
@@ -5113,20 +5215,22 @@
       <c r="S32" s="13"/>
       <c r="T32" s="13"/>
       <c r="U32" s="13"/>
-      <c r="V32" s="17"/>
+      <c r="V32" s="13"/>
       <c r="W32" s="13"/>
-      <c r="X32" s="13"/>
+      <c r="X32" s="17"/>
       <c r="Y32" s="13"/>
       <c r="Z32" s="13"/>
       <c r="AA32" s="13"/>
       <c r="AB32" s="13"/>
-    </row>
-    <row r="33" spans="1:28" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AC32" s="13"/>
+      <c r="AD32" s="13"/>
+    </row>
+    <row r="33" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="B33" s="33" t="s">
-        <v>117</v>
+        <v>100</v>
+      </c>
+      <c r="B33" s="32" t="s">
+        <v>116</v>
       </c>
       <c r="C33" s="13"/>
       <c r="D33" s="17"/>
@@ -5149,20 +5253,22 @@
       <c r="S33" s="13"/>
       <c r="T33" s="13"/>
       <c r="U33" s="13"/>
-      <c r="V33" s="17"/>
+      <c r="V33" s="13"/>
       <c r="W33" s="13"/>
-      <c r="X33" s="13"/>
+      <c r="X33" s="17"/>
       <c r="Y33" s="13"/>
       <c r="Z33" s="13"/>
       <c r="AA33" s="13"/>
       <c r="AB33" s="13"/>
-    </row>
-    <row r="34" spans="1:28" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="B34" s="33" t="s">
-        <v>118</v>
+      <c r="AC33" s="13"/>
+      <c r="AD33" s="13"/>
+    </row>
+    <row r="34" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A34" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="B34" s="32" t="s">
+        <v>117</v>
       </c>
       <c r="C34" s="13"/>
       <c r="D34" s="17"/>
@@ -5185,20 +5291,22 @@
       <c r="S34" s="13"/>
       <c r="T34" s="13"/>
       <c r="U34" s="13"/>
-      <c r="V34" s="17"/>
+      <c r="V34" s="13"/>
       <c r="W34" s="13"/>
-      <c r="X34" s="13"/>
+      <c r="X34" s="17"/>
       <c r="Y34" s="13"/>
       <c r="Z34" s="13"/>
       <c r="AA34" s="13"/>
       <c r="AB34" s="13"/>
-    </row>
-    <row r="35" spans="1:28" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AC34" s="13"/>
+      <c r="AD34" s="13"/>
+    </row>
+    <row r="35" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="B35" s="33" t="s">
-        <v>119</v>
+        <v>105</v>
+      </c>
+      <c r="B35" s="32" t="s">
+        <v>118</v>
       </c>
       <c r="C35" s="13"/>
       <c r="D35" s="17"/>
@@ -5221,20 +5329,22 @@
       <c r="S35" s="13"/>
       <c r="T35" s="13"/>
       <c r="U35" s="13"/>
-      <c r="V35" s="17"/>
+      <c r="V35" s="13"/>
       <c r="W35" s="13"/>
-      <c r="X35" s="13"/>
+      <c r="X35" s="17"/>
       <c r="Y35" s="13"/>
       <c r="Z35" s="13"/>
       <c r="AA35" s="13"/>
       <c r="AB35" s="13"/>
-    </row>
-    <row r="36" spans="1:28" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="53" t="s">
-        <v>91</v>
-      </c>
-      <c r="B36" s="33" t="s">
-        <v>129</v>
+      <c r="AC35" s="13"/>
+      <c r="AD35" s="13"/>
+    </row>
+    <row r="36" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A36" s="52" t="s">
+        <v>90</v>
+      </c>
+      <c r="B36" s="32" t="s">
+        <v>128</v>
       </c>
       <c r="C36" s="13"/>
       <c r="D36" s="17"/>
@@ -5257,20 +5367,21 @@
         <v>39</v>
       </c>
       <c r="U36" s="13"/>
-      <c r="V36" s="17"/>
       <c r="W36" s="13"/>
-      <c r="X36" s="13"/>
+      <c r="X36" s="17"/>
       <c r="Y36" s="13"/>
       <c r="Z36" s="13"/>
       <c r="AA36" s="13"/>
       <c r="AB36" s="13"/>
-    </row>
-    <row r="37" spans="1:28" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="53" t="s">
-        <v>86</v>
-      </c>
-      <c r="B37" s="33" t="s">
-        <v>191</v>
+      <c r="AC36" s="13"/>
+      <c r="AD36" s="13"/>
+    </row>
+    <row r="37" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A37" s="52" t="s">
+        <v>85</v>
+      </c>
+      <c r="B37" s="32" t="s">
+        <v>190</v>
       </c>
       <c r="C37" s="13"/>
       <c r="D37" s="17"/>
@@ -5292,21 +5403,23 @@
       <c r="T37" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="U37" s="13"/>
-      <c r="V37" s="17"/>
-      <c r="W37" s="13"/>
-      <c r="X37" s="13"/>
+      <c r="U37" s="64"/>
+      <c r="V37" s="66"/>
+      <c r="W37" s="65"/>
+      <c r="X37" s="17"/>
       <c r="Y37" s="13"/>
       <c r="Z37" s="13"/>
       <c r="AA37" s="13"/>
       <c r="AB37" s="13"/>
-    </row>
-    <row r="38" spans="1:28" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="B38" s="33" t="s">
-        <v>114</v>
+      <c r="AC37" s="13"/>
+      <c r="AD37" s="13"/>
+    </row>
+    <row r="38" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A38" s="52" t="s">
+        <v>120</v>
+      </c>
+      <c r="B38" s="32" t="s">
+        <v>113</v>
       </c>
       <c r="C38" s="13"/>
       <c r="D38" s="17"/>
@@ -5328,21 +5441,23 @@
       <c r="R38" s="13"/>
       <c r="S38" s="13"/>
       <c r="T38" s="13"/>
-      <c r="U38" s="39"/>
-      <c r="V38" s="17"/>
-      <c r="W38" s="13"/>
-      <c r="X38" s="13"/>
+      <c r="U38" s="13"/>
+      <c r="V38" s="15"/>
+      <c r="W38" s="38"/>
+      <c r="X38" s="17"/>
       <c r="Y38" s="13"/>
       <c r="Z38" s="13"/>
       <c r="AA38" s="13"/>
       <c r="AB38" s="13"/>
-    </row>
-    <row r="39" spans="1:28" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="B39" s="33" t="s">
-        <v>124</v>
+      <c r="AC38" s="13"/>
+      <c r="AD38" s="13"/>
+    </row>
+    <row r="39" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A39" s="52" t="s">
+        <v>120</v>
+      </c>
+      <c r="B39" s="32" t="s">
+        <v>123</v>
       </c>
       <c r="C39" s="13"/>
       <c r="D39" s="17"/>
@@ -5365,20 +5480,22 @@
       <c r="S39" s="13"/>
       <c r="T39" s="13"/>
       <c r="U39" s="13"/>
-      <c r="V39" s="17"/>
+      <c r="V39" s="13"/>
       <c r="W39" s="13"/>
-      <c r="X39" s="13"/>
+      <c r="X39" s="17"/>
       <c r="Y39" s="13"/>
       <c r="Z39" s="13"/>
       <c r="AA39" s="13"/>
       <c r="AB39" s="13"/>
-    </row>
-    <row r="40" spans="1:28" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="53" t="s">
-        <v>106</v>
-      </c>
-      <c r="B40" s="39" t="s">
-        <v>125</v>
+      <c r="AC39" s="13"/>
+      <c r="AD39" s="13"/>
+    </row>
+    <row r="40" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A40" s="52" t="s">
+        <v>105</v>
+      </c>
+      <c r="B40" s="38" t="s">
+        <v>124</v>
       </c>
       <c r="C40" s="13"/>
       <c r="D40" s="17"/>
@@ -5401,20 +5518,22 @@
       <c r="S40" s="13"/>
       <c r="T40" s="13"/>
       <c r="U40" s="13"/>
-      <c r="V40" s="17"/>
+      <c r="V40" s="13"/>
       <c r="W40" s="13"/>
-      <c r="X40" s="13"/>
+      <c r="X40" s="17"/>
       <c r="Y40" s="13"/>
       <c r="Z40" s="13"/>
       <c r="AA40" s="13"/>
       <c r="AB40" s="13"/>
-    </row>
-    <row r="41" spans="1:28" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="53" t="s">
-        <v>122</v>
-      </c>
-      <c r="B41" s="33" t="s">
-        <v>126</v>
+      <c r="AC40" s="13"/>
+      <c r="AD40" s="13"/>
+    </row>
+    <row r="41" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A41" s="52" t="s">
+        <v>121</v>
+      </c>
+      <c r="B41" s="32" t="s">
+        <v>125</v>
       </c>
       <c r="C41" s="13"/>
       <c r="D41" s="17"/>
@@ -5435,22 +5554,24 @@
       <c r="S41" s="13"/>
       <c r="T41" s="13"/>
       <c r="U41" s="13"/>
-      <c r="V41" s="17"/>
+      <c r="V41" s="13"/>
       <c r="W41" s="13"/>
-      <c r="X41" s="13"/>
-      <c r="Y41" s="13" t="s">
+      <c r="X41" s="17"/>
+      <c r="Y41" s="13"/>
+      <c r="Z41" s="13"/>
+      <c r="AA41" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="Z41" s="13"/>
-      <c r="AA41" s="13"/>
       <c r="AB41" s="13"/>
-    </row>
-    <row r="42" spans="1:28" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AC41" s="13"/>
+      <c r="AD41" s="13"/>
+    </row>
+    <row r="42" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="24" t="s">
-        <v>84</v>
-      </c>
-      <c r="B42" s="33" t="s">
-        <v>127</v>
+        <v>83</v>
+      </c>
+      <c r="B42" s="32" t="s">
+        <v>126</v>
       </c>
       <c r="C42" s="13"/>
       <c r="D42" s="17"/>
@@ -5471,22 +5592,24 @@
       <c r="S42" s="13"/>
       <c r="T42" s="13"/>
       <c r="U42" s="13"/>
-      <c r="V42" s="17"/>
+      <c r="V42" s="13"/>
       <c r="W42" s="13"/>
-      <c r="X42" s="13"/>
-      <c r="Y42" s="13" t="s">
+      <c r="X42" s="17"/>
+      <c r="Y42" s="13"/>
+      <c r="Z42" s="13"/>
+      <c r="AA42" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="Z42" s="13"/>
-      <c r="AA42" s="13"/>
       <c r="AB42" s="13"/>
-    </row>
-    <row r="43" spans="1:28" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="53" t="s">
-        <v>107</v>
-      </c>
-      <c r="B43" s="33" t="s">
-        <v>112</v>
+      <c r="AC42" s="13"/>
+      <c r="AD42" s="13"/>
+    </row>
+    <row r="43" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A43" s="52" t="s">
+        <v>106</v>
+      </c>
+      <c r="B43" s="32" t="s">
+        <v>111</v>
       </c>
       <c r="C43" s="13"/>
       <c r="D43" s="17"/>
@@ -5500,7 +5623,7 @@
       <c r="L43" s="13"/>
       <c r="M43" s="13"/>
       <c r="N43" s="13" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O43" s="13"/>
       <c r="P43" s="13"/>
@@ -5509,20 +5632,22 @@
       <c r="S43" s="13"/>
       <c r="T43" s="13"/>
       <c r="U43" s="13"/>
-      <c r="V43" s="17"/>
+      <c r="V43" s="13"/>
       <c r="W43" s="13"/>
-      <c r="X43" s="13"/>
+      <c r="X43" s="17"/>
       <c r="Y43" s="13"/>
       <c r="Z43" s="13"/>
       <c r="AA43" s="13"/>
       <c r="AB43" s="13"/>
-    </row>
-    <row r="44" spans="1:28" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="53" t="s">
-        <v>91</v>
-      </c>
-      <c r="B44" s="33" t="s">
-        <v>128</v>
+      <c r="AC43" s="13"/>
+      <c r="AD43" s="13"/>
+    </row>
+    <row r="44" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A44" s="52" t="s">
+        <v>90</v>
+      </c>
+      <c r="B44" s="32" t="s">
+        <v>127</v>
       </c>
       <c r="C44" s="13"/>
       <c r="D44" s="17"/>
@@ -5536,7 +5661,7 @@
       <c r="L44" s="13"/>
       <c r="M44" s="13"/>
       <c r="N44" s="13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O44" s="13"/>
       <c r="P44" s="13"/>
@@ -5545,20 +5670,22 @@
       <c r="S44" s="13"/>
       <c r="T44" s="13"/>
       <c r="U44" s="13"/>
-      <c r="V44" s="17"/>
+      <c r="V44" s="13"/>
       <c r="W44" s="13"/>
-      <c r="X44" s="13"/>
+      <c r="X44" s="17"/>
       <c r="Y44" s="13"/>
       <c r="Z44" s="13"/>
       <c r="AA44" s="13"/>
       <c r="AB44" s="13"/>
-    </row>
-    <row r="45" spans="1:28" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="53" t="s">
-        <v>123</v>
-      </c>
-      <c r="B45" s="39" t="s">
-        <v>130</v>
+      <c r="AC44" s="13"/>
+      <c r="AD44" s="13"/>
+    </row>
+    <row r="45" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A45" s="52" t="s">
+        <v>122</v>
+      </c>
+      <c r="B45" s="38" t="s">
+        <v>129</v>
       </c>
       <c r="C45" s="13"/>
       <c r="D45" s="17"/>
@@ -5577,96 +5704,110 @@
       <c r="Q45" s="13"/>
       <c r="R45" s="13"/>
       <c r="S45" s="13"/>
-      <c r="T45" s="13" t="s">
+      <c r="T45" s="13"/>
+      <c r="U45" s="13"/>
+      <c r="V45" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="U45" s="13"/>
-      <c r="V45" s="17"/>
       <c r="W45" s="13"/>
-      <c r="X45" s="13"/>
+      <c r="X45" s="17"/>
       <c r="Y45" s="13"/>
       <c r="Z45" s="13"/>
       <c r="AA45" s="13"/>
       <c r="AB45" s="13"/>
-    </row>
-    <row r="46" spans="1:28" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="53"/>
+      <c r="AC45" s="13"/>
+      <c r="AD45" s="13"/>
+    </row>
+    <row r="46" spans="1:30" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A46" s="52"/>
       <c r="B46" s="22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C46" s="25"/>
       <c r="D46" s="25"/>
       <c r="E46" s="25"/>
       <c r="F46" s="25"/>
-      <c r="G46" s="42"/>
-      <c r="H46" s="42"/>
-      <c r="I46" s="42"/>
-      <c r="J46" s="42"/>
-      <c r="K46" s="42"/>
-      <c r="L46" s="42"/>
-      <c r="M46" s="42"/>
-      <c r="N46" s="42"/>
-      <c r="O46" s="42"/>
+      <c r="G46" s="41"/>
+      <c r="H46" s="41"/>
+      <c r="I46" s="41"/>
+      <c r="J46" s="41"/>
+      <c r="K46" s="41"/>
+      <c r="L46" s="41"/>
+      <c r="M46" s="41"/>
+      <c r="N46" s="41"/>
+      <c r="O46" s="41"/>
       <c r="P46" s="25"/>
       <c r="Q46" s="25"/>
       <c r="R46" s="25"/>
       <c r="S46" s="25"/>
       <c r="T46" s="25"/>
       <c r="U46" s="25"/>
-      <c r="V46" s="61"/>
-      <c r="W46" s="63"/>
-      <c r="X46" s="62"/>
-      <c r="Y46" s="25"/>
-      <c r="Z46" s="25"/>
+      <c r="V46" s="25"/>
+      <c r="W46" s="25"/>
+      <c r="X46" s="60"/>
+      <c r="Y46" s="62"/>
+      <c r="Z46" s="61"/>
       <c r="AA46" s="25"/>
       <c r="AB46" s="25"/>
-    </row>
-    <row r="47" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A47" s="79"/>
-      <c r="B47" s="79"/>
-      <c r="C47" s="79"/>
-      <c r="D47" s="79"/>
-      <c r="E47" s="79"/>
-      <c r="F47" s="79"/>
-      <c r="G47" s="79"/>
-      <c r="H47" s="79"/>
-      <c r="I47" s="79"/>
-      <c r="J47" s="79"/>
-      <c r="K47" s="79"/>
-      <c r="L47" s="79"/>
-      <c r="M47" s="79"/>
-      <c r="N47" s="79"/>
-      <c r="O47" s="79"/>
-      <c r="P47" s="79"/>
-      <c r="Q47" s="79"/>
-      <c r="R47" s="79"/>
-      <c r="S47" s="79"/>
-      <c r="T47" s="79"/>
-      <c r="U47" s="79"/>
-      <c r="V47" s="79"/>
-      <c r="W47" s="79"/>
-      <c r="X47" s="79"/>
-      <c r="Y47" s="79"/>
-      <c r="Z47" s="79"/>
-      <c r="AA47" s="79"/>
-      <c r="AB47" s="79"/>
-    </row>
-    <row r="48" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A48" s="50" t="s">
-        <v>194</v>
+      <c r="AC46" s="25"/>
+      <c r="AD46" s="25"/>
+    </row>
+    <row r="47" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A47" s="68"/>
+      <c r="B47" s="68"/>
+      <c r="C47" s="68"/>
+      <c r="D47" s="68"/>
+      <c r="E47" s="68"/>
+      <c r="F47" s="68"/>
+      <c r="G47" s="68"/>
+      <c r="H47" s="68"/>
+      <c r="I47" s="68"/>
+      <c r="J47" s="68"/>
+      <c r="K47" s="68"/>
+      <c r="L47" s="68"/>
+      <c r="M47" s="68"/>
+      <c r="N47" s="68"/>
+      <c r="O47" s="68"/>
+      <c r="P47" s="68"/>
+      <c r="Q47" s="68"/>
+      <c r="R47" s="68"/>
+      <c r="S47" s="68"/>
+      <c r="T47" s="68"/>
+      <c r="U47" s="68"/>
+      <c r="V47" s="68"/>
+      <c r="W47" s="68"/>
+      <c r="X47" s="68"/>
+      <c r="Y47" s="68"/>
+      <c r="Z47" s="68"/>
+      <c r="AA47" s="68"/>
+      <c r="AB47" s="68"/>
+      <c r="AC47" s="68"/>
+      <c r="AD47" s="68"/>
+    </row>
+    <row r="48" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A48" s="49" t="s">
+        <v>193</v>
       </c>
       <c r="B48" s="7"/>
-      <c r="AA48" s="39"/>
+      <c r="AC48" s="38"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
-    <mergeCell ref="A7:AB7"/>
-    <mergeCell ref="A15:AB15"/>
-    <mergeCell ref="A47:AB47"/>
+  <mergeCells count="24">
+    <mergeCell ref="AB4:AC4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A2:AD2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="X3:AD3"/>
+    <mergeCell ref="G3:R3"/>
+    <mergeCell ref="Z4:AA4"/>
+    <mergeCell ref="A7:AD7"/>
+    <mergeCell ref="A15:AD15"/>
+    <mergeCell ref="A47:AD47"/>
     <mergeCell ref="N4:O4"/>
     <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="AB4:AB5"/>
+    <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="AD4:AD5"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="B4:B6"/>
     <mergeCell ref="C4:E4"/>
@@ -5674,15 +5815,8 @@
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="R4:S4"/>
     <mergeCell ref="L4:M4"/>
+    <mergeCell ref="V4:W4"/>
     <mergeCell ref="T4:U4"/>
-    <mergeCell ref="Z4:AA4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="A2:AB2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="V3:AB3"/>
-    <mergeCell ref="G3:R3"/>
-    <mergeCell ref="X4:Y4"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="Q27" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
@@ -5694,11 +5828,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:Y29"/>
+  <dimension ref="A1:Y30"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.44140625" style="50" customWidth="1"/>
-    <col min="2" max="2" width="27.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.44140625" style="49" customWidth="1"/>
+    <col min="2" max="2" width="20" style="7" customWidth="1"/>
     <col min="3" max="3" width="5.33203125" style="20" customWidth="1"/>
     <col min="4" max="4" width="5.88671875" style="19" customWidth="1"/>
     <col min="5" max="5" width="7.88671875" style="19" customWidth="1"/>
@@ -7233,152 +7367,152 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="67" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
-      <c r="V1" s="78"/>
-      <c r="W1" s="78"/>
-      <c r="X1" s="78"/>
-      <c r="Y1" s="78"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="67"/>
+      <c r="N1" s="67"/>
+      <c r="O1" s="67"/>
+      <c r="P1" s="67"/>
+      <c r="Q1" s="67"/>
+      <c r="R1" s="67"/>
+      <c r="S1" s="67"/>
+      <c r="T1" s="67"/>
+      <c r="U1" s="67"/>
+      <c r="V1" s="67"/>
+      <c r="W1" s="67"/>
+      <c r="X1" s="67"/>
+      <c r="Y1" s="67"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A2" s="78" t="s">
+      <c r="A2" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
-      <c r="M2" s="78"/>
-      <c r="N2" s="78"/>
-      <c r="O2" s="78"/>
-      <c r="P2" s="78"/>
-      <c r="Q2" s="78"/>
-      <c r="R2" s="78"/>
-      <c r="S2" s="78"/>
-      <c r="T2" s="78"/>
-      <c r="U2" s="78"/>
-      <c r="V2" s="78"/>
-      <c r="W2" s="78"/>
-      <c r="X2" s="78"/>
-      <c r="Y2" s="78"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
+      <c r="N2" s="67"/>
+      <c r="O2" s="67"/>
+      <c r="P2" s="67"/>
+      <c r="Q2" s="67"/>
+      <c r="R2" s="67"/>
+      <c r="S2" s="67"/>
+      <c r="T2" s="67"/>
+      <c r="U2" s="67"/>
+      <c r="V2" s="67"/>
+      <c r="W2" s="67"/>
+      <c r="X2" s="67"/>
+      <c r="Y2" s="67"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3" s="79" t="s">
-        <v>140</v>
-      </c>
-      <c r="B3" s="79"/>
-      <c r="C3" s="79"/>
-      <c r="D3" s="79"/>
+      <c r="A3" s="68" t="s">
+        <v>139</v>
+      </c>
+      <c r="B3" s="68"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
-      <c r="G3" s="78" t="s">
+      <c r="G3" s="67" t="s">
         <v>32</v>
       </c>
-      <c r="H3" s="78"/>
-      <c r="I3" s="78"/>
-      <c r="J3" s="78"/>
-      <c r="K3" s="78"/>
-      <c r="L3" s="78"/>
-      <c r="M3" s="78"/>
-      <c r="N3" s="78"/>
-      <c r="O3" s="78"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="67"/>
+      <c r="K3" s="67"/>
+      <c r="L3" s="67"/>
+      <c r="M3" s="67"/>
+      <c r="N3" s="67"/>
+      <c r="O3" s="67"/>
       <c r="P3" s="8"/>
       <c r="Q3" s="8"/>
       <c r="R3" s="8"/>
-      <c r="S3" s="78" t="s">
+      <c r="S3" s="67" t="s">
+        <v>140</v>
+      </c>
+      <c r="T3" s="67"/>
+      <c r="U3" s="67"/>
+      <c r="V3" s="67"/>
+      <c r="W3" s="67"/>
+      <c r="X3" s="67"/>
+      <c r="Y3" s="67"/>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A4" s="75" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="72" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="69" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="69" t="s">
+        <v>53</v>
+      </c>
+      <c r="G4" s="69"/>
+      <c r="H4" s="69" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" s="69"/>
+      <c r="J4" s="69" t="s">
+        <v>54</v>
+      </c>
+      <c r="K4" s="69"/>
+      <c r="L4" s="70" t="s">
+        <v>59</v>
+      </c>
+      <c r="M4" s="71"/>
+      <c r="N4" s="72" t="s">
+        <v>55</v>
+      </c>
+      <c r="O4" s="72"/>
+      <c r="P4" s="69" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q4" s="69"/>
+      <c r="R4" s="73" t="s">
+        <v>44</v>
+      </c>
+      <c r="S4" s="74"/>
+      <c r="T4" s="69" t="s">
+        <v>57</v>
+      </c>
+      <c r="U4" s="69"/>
+      <c r="V4" s="72" t="s">
+        <v>142</v>
+      </c>
+      <c r="W4" s="72"/>
+      <c r="X4" s="73" t="s">
         <v>141</v>
       </c>
-      <c r="T3" s="78"/>
-      <c r="U3" s="78"/>
-      <c r="V3" s="78"/>
-      <c r="W3" s="78"/>
-      <c r="X3" s="78"/>
-      <c r="Y3" s="78"/>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A4" s="72" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="69" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="66" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="66"/>
-      <c r="E4" s="66"/>
-      <c r="F4" s="66" t="s">
-        <v>53</v>
-      </c>
-      <c r="G4" s="66"/>
-      <c r="H4" s="66" t="s">
-        <v>40</v>
-      </c>
-      <c r="I4" s="66"/>
-      <c r="J4" s="66" t="s">
-        <v>54</v>
-      </c>
-      <c r="K4" s="66"/>
-      <c r="L4" s="67" t="s">
-        <v>59</v>
-      </c>
-      <c r="M4" s="68"/>
-      <c r="N4" s="69" t="s">
-        <v>55</v>
-      </c>
-      <c r="O4" s="69"/>
-      <c r="P4" s="66" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q4" s="66"/>
-      <c r="R4" s="70" t="s">
-        <v>44</v>
-      </c>
-      <c r="S4" s="71"/>
-      <c r="T4" s="66" t="s">
-        <v>57</v>
-      </c>
-      <c r="U4" s="66"/>
-      <c r="V4" s="69" t="s">
-        <v>143</v>
-      </c>
-      <c r="W4" s="69"/>
-      <c r="X4" s="70" t="s">
-        <v>142</v>
-      </c>
-      <c r="Y4" s="73"/>
+      <c r="Y4" s="76"/>
     </row>
     <row r="5" spans="1:25" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A5" s="72"/>
-      <c r="B5" s="69"/>
+      <c r="A5" s="75"/>
+      <c r="B5" s="72"/>
       <c r="C5" s="10" t="s">
         <v>19</v>
       </c>
@@ -7450,113 +7584,113 @@
       </c>
     </row>
     <row r="6" spans="1:25" s="11" customFormat="1" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="72"/>
-      <c r="B6" s="69"/>
-      <c r="C6" s="32" t="s">
+      <c r="A6" s="75"/>
+      <c r="B6" s="72"/>
+      <c r="C6" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="32" t="s">
+      <c r="D6" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="32" t="s">
+      <c r="E6" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="32" t="s">
+      <c r="F6" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="G6" s="32" t="s">
+      <c r="G6" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="32" t="s">
+      <c r="H6" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="32" t="s">
+      <c r="I6" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="J6" s="32" t="s">
+      <c r="J6" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="K6" s="32" t="s">
+      <c r="K6" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="L6" s="32" t="s">
+      <c r="L6" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="M6" s="32" t="s">
+      <c r="M6" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="N6" s="32" t="s">
+      <c r="N6" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="O6" s="32" t="s">
+      <c r="O6" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="P6" s="32" t="s">
+      <c r="P6" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="Q6" s="32" t="s">
+      <c r="Q6" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="R6" s="32" t="s">
+      <c r="R6" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="S6" s="32" t="s">
+      <c r="S6" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="T6" s="32" t="s">
+      <c r="T6" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="U6" s="32" t="s">
+      <c r="U6" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="V6" s="32" t="s">
+      <c r="V6" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="W6" s="32" t="s">
+      <c r="W6" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="X6" s="32" t="s">
+      <c r="X6" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="Y6" s="32" t="s">
+      <c r="Y6" s="31" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A7" s="74" t="s">
+      <c r="A7" s="77" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="75"/>
-      <c r="C7" s="75"/>
-      <c r="D7" s="75"/>
-      <c r="E7" s="75"/>
-      <c r="F7" s="75"/>
-      <c r="G7" s="75"/>
-      <c r="H7" s="75"/>
-      <c r="I7" s="75"/>
-      <c r="J7" s="75"/>
-      <c r="K7" s="75"/>
-      <c r="L7" s="75"/>
-      <c r="M7" s="75"/>
-      <c r="N7" s="75"/>
-      <c r="O7" s="75"/>
-      <c r="P7" s="75"/>
-      <c r="Q7" s="75"/>
-      <c r="R7" s="75"/>
-      <c r="S7" s="75"/>
-      <c r="T7" s="75"/>
-      <c r="U7" s="75"/>
-      <c r="V7" s="75"/>
-      <c r="W7" s="75"/>
-      <c r="X7" s="75"/>
-      <c r="Y7" s="75"/>
-    </row>
-    <row r="8" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="45" t="s">
-        <v>144</v>
+      <c r="B7" s="78"/>
+      <c r="C7" s="78"/>
+      <c r="D7" s="78"/>
+      <c r="E7" s="78"/>
+      <c r="F7" s="78"/>
+      <c r="G7" s="78"/>
+      <c r="H7" s="78"/>
+      <c r="I7" s="78"/>
+      <c r="J7" s="78"/>
+      <c r="K7" s="78"/>
+      <c r="L7" s="78"/>
+      <c r="M7" s="78"/>
+      <c r="N7" s="78"/>
+      <c r="O7" s="78"/>
+      <c r="P7" s="78"/>
+      <c r="Q7" s="78"/>
+      <c r="R7" s="78"/>
+      <c r="S7" s="78"/>
+      <c r="T7" s="78"/>
+      <c r="U7" s="78"/>
+      <c r="V7" s="78"/>
+      <c r="W7" s="78"/>
+      <c r="X7" s="78"/>
+      <c r="Y7" s="78"/>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A8" s="44" t="s">
+        <v>143</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C8" s="10"/>
       <c r="D8" s="10"/>
@@ -7584,12 +7718,12 @@
       <c r="X8" s="10"/>
       <c r="Y8" s="10"/>
     </row>
-    <row r="9" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="46" t="s">
-        <v>145</v>
-      </c>
-      <c r="B9" s="30" t="s">
-        <v>158</v>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A9" s="45" t="s">
+        <v>144</v>
+      </c>
+      <c r="B9" s="29" t="s">
+        <v>157</v>
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="10"/>
@@ -7597,7 +7731,7 @@
       <c r="F9" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="38"/>
+      <c r="G9" s="37"/>
       <c r="H9" s="10"/>
       <c r="I9" s="10"/>
       <c r="J9" s="10"/>
@@ -7619,12 +7753,12 @@
       <c r="X9" s="10"/>
       <c r="Y9" s="10"/>
     </row>
-    <row r="10" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="46" t="s">
-        <v>146</v>
-      </c>
-      <c r="B10" s="30" t="s">
-        <v>151</v>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A10" s="45" t="s">
+        <v>145</v>
+      </c>
+      <c r="B10" s="29" t="s">
+        <v>150</v>
       </c>
       <c r="C10" s="10"/>
       <c r="D10" s="10"/>
@@ -7632,11 +7766,11 @@
       <c r="F10" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="G10" s="38"/>
+      <c r="G10" s="37"/>
       <c r="H10" s="10"/>
       <c r="I10" s="10"/>
       <c r="J10" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K10" s="10"/>
       <c r="L10" s="10"/>
@@ -7658,12 +7792,12 @@
       <c r="X10" s="10"/>
       <c r="Y10" s="10"/>
     </row>
-    <row r="11" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="51" t="s">
-        <v>159</v>
-      </c>
-      <c r="B11" s="30" t="s">
-        <v>152</v>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A11" s="50" t="s">
+        <v>158</v>
+      </c>
+      <c r="B11" s="29" t="s">
+        <v>151</v>
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="10"/>
@@ -7686,19 +7820,19 @@
       <c r="S11" s="10"/>
       <c r="T11" s="10"/>
       <c r="U11" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="V11" s="10"/>
       <c r="W11" s="10"/>
       <c r="X11" s="10"/>
       <c r="Y11" s="10"/>
     </row>
-    <row r="12" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="57" t="s">
-        <v>107</v>
-      </c>
-      <c r="B12" s="30" t="s">
-        <v>153</v>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A12" s="56" t="s">
+        <v>106</v>
+      </c>
+      <c r="B12" s="29" t="s">
+        <v>152</v>
       </c>
       <c r="C12" s="10"/>
       <c r="D12" s="10"/>
@@ -7708,7 +7842,7 @@
       <c r="H12" s="10"/>
       <c r="I12" s="10"/>
       <c r="J12" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K12" s="10"/>
       <c r="L12" s="10"/>
@@ -7723,19 +7857,19 @@
       <c r="S12" s="10"/>
       <c r="T12" s="10"/>
       <c r="U12" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="V12" s="10"/>
       <c r="W12" s="10"/>
       <c r="X12" s="10"/>
       <c r="Y12" s="10"/>
     </row>
-    <row r="13" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="56" t="s">
-        <v>106</v>
-      </c>
-      <c r="B13" s="30" t="s">
-        <v>154</v>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A13" s="55" t="s">
+        <v>105</v>
+      </c>
+      <c r="B13" s="29" t="s">
+        <v>153</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="10"/>
@@ -7765,21 +7899,21 @@
       <c r="X13" s="10"/>
       <c r="Y13" s="10"/>
     </row>
-    <row r="14" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="47" t="s">
-        <v>123</v>
-      </c>
-      <c r="B14" s="30" t="s">
-        <v>155</v>
+    <row r="14" spans="1:25" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A14" s="55" t="s">
+        <v>197</v>
+      </c>
+      <c r="B14" s="29" t="s">
+        <v>195</v>
       </c>
       <c r="C14" s="10"/>
       <c r="D14" s="10"/>
-      <c r="E14" s="10" t="s">
-        <v>39</v>
-      </c>
+      <c r="E14" s="10"/>
       <c r="F14" s="10"/>
       <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
+      <c r="H14" s="10" t="s">
+        <v>41</v>
+      </c>
       <c r="I14" s="10"/>
       <c r="J14" s="10"/>
       <c r="K14" s="10"/>
@@ -7798,17 +7932,17 @@
       <c r="X14" s="10"/>
       <c r="Y14" s="10"/>
     </row>
-    <row r="15" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="47" t="s">
-        <v>123</v>
-      </c>
-      <c r="B15" s="30" t="s">
-        <v>156</v>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A15" s="46" t="s">
+        <v>122</v>
+      </c>
+      <c r="B15" s="29" t="s">
+        <v>154</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="10"/>
       <c r="E15" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F15" s="10"/>
       <c r="G15" s="10"/>
@@ -7831,19 +7965,19 @@
       <c r="X15" s="10"/>
       <c r="Y15" s="10"/>
     </row>
-    <row r="16" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="48" t="s">
-        <v>147</v>
-      </c>
-      <c r="B16" s="48" t="s">
-        <v>147</v>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A16" s="46" t="s">
+        <v>122</v>
+      </c>
+      <c r="B16" s="29" t="s">
+        <v>155</v>
       </c>
       <c r="C16" s="10"/>
       <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10" t="s">
+      <c r="E16" s="10" t="s">
         <v>41</v>
       </c>
+      <c r="F16" s="10"/>
       <c r="G16" s="10"/>
       <c r="H16" s="10"/>
       <c r="I16" s="10"/>
@@ -7864,107 +7998,107 @@
       <c r="X16" s="10"/>
       <c r="Y16" s="10"/>
     </row>
-    <row r="17" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="76" t="s">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A17" s="47" t="s">
+        <v>146</v>
+      </c>
+      <c r="B17" s="47" t="s">
+        <v>146</v>
+      </c>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="10"/>
+      <c r="O17" s="10"/>
+      <c r="P17" s="10"/>
+      <c r="Q17" s="10"/>
+      <c r="R17" s="10"/>
+      <c r="S17" s="10"/>
+      <c r="T17" s="10"/>
+      <c r="U17" s="10"/>
+      <c r="V17" s="10"/>
+      <c r="W17" s="10"/>
+      <c r="X17" s="10"/>
+      <c r="Y17" s="10"/>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A18" s="79" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="77"/>
-      <c r="C17" s="77"/>
-      <c r="D17" s="77"/>
-      <c r="E17" s="77"/>
-      <c r="F17" s="77"/>
-      <c r="G17" s="77"/>
-      <c r="H17" s="77"/>
-      <c r="I17" s="77"/>
-      <c r="J17" s="77"/>
-      <c r="K17" s="77"/>
-      <c r="L17" s="77"/>
-      <c r="M17" s="77"/>
-      <c r="N17" s="77"/>
-      <c r="O17" s="77"/>
-      <c r="P17" s="77"/>
-      <c r="Q17" s="77"/>
-      <c r="R17" s="77"/>
-      <c r="S17" s="77"/>
-      <c r="T17" s="77"/>
-      <c r="U17" s="77"/>
-      <c r="V17" s="77"/>
-      <c r="W17" s="77"/>
-      <c r="X17" s="77"/>
-      <c r="Y17" s="77"/>
-    </row>
-    <row r="18" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="48" t="s">
-        <v>88</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="13"/>
-      <c r="M18" s="13"/>
-      <c r="N18" s="13"/>
-      <c r="O18" s="13"/>
-      <c r="P18" s="13"/>
-      <c r="Q18" s="13"/>
-      <c r="R18" s="13" t="s">
+      <c r="B18" s="80"/>
+      <c r="C18" s="80"/>
+      <c r="D18" s="80"/>
+      <c r="E18" s="80"/>
+      <c r="F18" s="80"/>
+      <c r="G18" s="80"/>
+      <c r="H18" s="80"/>
+      <c r="I18" s="80"/>
+      <c r="J18" s="80"/>
+      <c r="K18" s="80"/>
+      <c r="L18" s="80"/>
+      <c r="M18" s="80"/>
+      <c r="N18" s="80"/>
+      <c r="O18" s="80"/>
+      <c r="P18" s="80"/>
+      <c r="Q18" s="80"/>
+      <c r="R18" s="80"/>
+      <c r="S18" s="80"/>
+      <c r="T18" s="80"/>
+      <c r="U18" s="80"/>
+      <c r="V18" s="80"/>
+      <c r="W18" s="80"/>
+      <c r="X18" s="80"/>
+      <c r="Y18" s="80"/>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A19" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="13"/>
+      <c r="K19" s="13"/>
+      <c r="L19" s="13"/>
+      <c r="M19" s="13"/>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13"/>
+      <c r="P19" s="13"/>
+      <c r="Q19" s="13"/>
+      <c r="R19" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="S18" s="13"/>
-      <c r="T18" s="13"/>
-      <c r="U18" s="13"/>
-      <c r="V18" s="13"/>
-      <c r="W18" s="13"/>
-      <c r="X18" s="13"/>
-      <c r="Y18" s="13"/>
-    </row>
-    <row r="19" spans="1:25" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="48" t="s">
-        <v>148</v>
-      </c>
-      <c r="B19" s="18" t="s">
-        <v>192</v>
-      </c>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="15"/>
-      <c r="L19" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="M19" s="15"/>
-      <c r="N19" s="15"/>
-      <c r="O19" s="15"/>
-      <c r="P19" s="15"/>
-      <c r="Q19" s="15"/>
-      <c r="R19" s="15"/>
-      <c r="S19" s="15"/>
-      <c r="T19" s="15"/>
-      <c r="U19" s="15"/>
-      <c r="V19" s="15"/>
-      <c r="W19" s="15"/>
-      <c r="X19" s="15"/>
-      <c r="Y19" s="15"/>
-    </row>
-    <row r="20" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="48" t="s">
-        <v>91</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>161</v>
+      <c r="S19" s="13"/>
+      <c r="T19" s="13"/>
+      <c r="U19" s="13"/>
+      <c r="V19" s="13"/>
+      <c r="W19" s="13"/>
+      <c r="X19" s="13"/>
+      <c r="Y19" s="13"/>
+    </row>
+    <row r="20" spans="1:25" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A20" s="47" t="s">
+        <v>147</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>191</v>
       </c>
       <c r="C20" s="15"/>
       <c r="D20" s="15"/>
@@ -7976,7 +8110,7 @@
       <c r="J20" s="15"/>
       <c r="K20" s="15"/>
       <c r="L20" s="15" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M20" s="15"/>
       <c r="N20" s="15"/>
@@ -7992,12 +8126,12 @@
       <c r="X20" s="15"/>
       <c r="Y20" s="15"/>
     </row>
-    <row r="21" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="48" t="s">
-        <v>84</v>
-      </c>
-      <c r="B21" s="18" t="s">
-        <v>193</v>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A21" s="47" t="s">
+        <v>90</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>160</v>
       </c>
       <c r="C21" s="15"/>
       <c r="D21" s="15"/>
@@ -8008,7 +8142,9 @@
       <c r="I21" s="15"/>
       <c r="J21" s="15"/>
       <c r="K21" s="15"/>
-      <c r="L21" s="15"/>
+      <c r="L21" s="15" t="s">
+        <v>41</v>
+      </c>
       <c r="M21" s="15"/>
       <c r="N21" s="15"/>
       <c r="O21" s="15"/>
@@ -8019,20 +8155,16 @@
       <c r="T21" s="15"/>
       <c r="U21" s="15"/>
       <c r="V21" s="15"/>
-      <c r="W21" s="15" t="s">
-        <v>41</v>
-      </c>
+      <c r="W21" s="15"/>
       <c r="X21" s="15"/>
-      <c r="Y21" s="15" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="55" t="s">
-        <v>149</v>
-      </c>
-      <c r="B22" s="24" t="s">
-        <v>162</v>
+      <c r="Y21" s="15"/>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A22" s="47" t="s">
+        <v>83</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>192</v>
       </c>
       <c r="C22" s="15"/>
       <c r="D22" s="15"/>
@@ -8054,18 +8186,20 @@
       <c r="T22" s="15"/>
       <c r="U22" s="15"/>
       <c r="V22" s="15"/>
-      <c r="W22" s="15"/>
+      <c r="W22" s="15" t="s">
+        <v>41</v>
+      </c>
       <c r="X22" s="15"/>
       <c r="Y22" s="15" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="23" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="45" t="s">
-        <v>150</v>
-      </c>
-      <c r="B23" s="18" t="s">
-        <v>163</v>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A23" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="B23" s="24" t="s">
+        <v>161</v>
       </c>
       <c r="C23" s="15"/>
       <c r="D23" s="15"/>
@@ -8090,99 +8224,144 @@
       <c r="W23" s="15"/>
       <c r="X23" s="15"/>
       <c r="Y23" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A24" s="44" t="s">
+        <v>149</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="15"/>
+      <c r="J24" s="15"/>
+      <c r="K24" s="15"/>
+      <c r="L24" s="15"/>
+      <c r="M24" s="15"/>
+      <c r="N24" s="15"/>
+      <c r="O24" s="15"/>
+      <c r="P24" s="15"/>
+      <c r="Q24" s="15"/>
+      <c r="R24" s="15"/>
+      <c r="S24" s="15"/>
+      <c r="T24" s="15"/>
+      <c r="U24" s="15"/>
+      <c r="V24" s="15"/>
+      <c r="W24" s="15"/>
+      <c r="X24" s="15"/>
+      <c r="Y24" s="15" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="45"/>
-      <c r="B24" s="22" t="s">
+    <row r="25" spans="1:25" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A25" s="44"/>
+      <c r="B25" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="25"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="25"/>
-      <c r="F24" s="25"/>
-      <c r="G24" s="26"/>
-      <c r="H24" s="25"/>
-      <c r="I24" s="25"/>
-      <c r="J24" s="25"/>
-      <c r="K24" s="25"/>
-      <c r="L24" s="25"/>
-      <c r="M24" s="25"/>
-      <c r="N24" s="25"/>
-      <c r="O24" s="25"/>
-      <c r="P24" s="25"/>
-      <c r="Q24" s="25"/>
-      <c r="R24" s="25"/>
-      <c r="S24" s="25"/>
-      <c r="T24" s="25"/>
-      <c r="U24" s="25"/>
-      <c r="V24" s="27"/>
-      <c r="W24" s="25"/>
-      <c r="X24" s="25"/>
-      <c r="Y24" s="25"/>
-    </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A25" s="65"/>
-      <c r="B25" s="65"/>
-      <c r="C25" s="65"/>
-      <c r="D25" s="65"/>
-      <c r="E25" s="65"/>
-      <c r="F25" s="65"/>
-      <c r="G25" s="65"/>
-      <c r="H25" s="65"/>
-      <c r="I25" s="65"/>
-      <c r="J25" s="65"/>
-      <c r="K25" s="65"/>
-      <c r="L25" s="65"/>
-      <c r="M25" s="65"/>
-      <c r="N25" s="65"/>
-      <c r="O25" s="65"/>
-      <c r="P25" s="65"/>
-      <c r="Q25" s="65"/>
-      <c r="R25" s="65"/>
-      <c r="S25" s="65"/>
-      <c r="T25" s="65"/>
-      <c r="U25" s="65"/>
-      <c r="V25" s="65"/>
-      <c r="W25" s="65"/>
-      <c r="X25" s="65"/>
-      <c r="Y25" s="65"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="41"/>
+      <c r="H25" s="25"/>
+      <c r="I25" s="25"/>
+      <c r="J25" s="25"/>
+      <c r="K25" s="25"/>
+      <c r="L25" s="25"/>
+      <c r="M25" s="25"/>
+      <c r="N25" s="25"/>
+      <c r="O25" s="25"/>
+      <c r="P25" s="25"/>
+      <c r="Q25" s="25"/>
+      <c r="R25" s="25"/>
+      <c r="S25" s="25"/>
+      <c r="T25" s="25"/>
+      <c r="U25" s="25"/>
+      <c r="V25" s="26"/>
+      <c r="W25" s="25"/>
+      <c r="X25" s="25"/>
+      <c r="Y25" s="25"/>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A26" s="49" t="s">
+      <c r="A26" s="68"/>
+      <c r="B26" s="68"/>
+      <c r="C26" s="68"/>
+      <c r="D26" s="68"/>
+      <c r="E26" s="68"/>
+      <c r="F26" s="68"/>
+      <c r="G26" s="68"/>
+      <c r="H26" s="68"/>
+      <c r="I26" s="68"/>
+      <c r="J26" s="68"/>
+      <c r="K26" s="68"/>
+      <c r="L26" s="68"/>
+      <c r="M26" s="68"/>
+      <c r="N26" s="68"/>
+      <c r="O26" s="68"/>
+      <c r="P26" s="68"/>
+      <c r="Q26" s="68"/>
+      <c r="R26" s="68"/>
+      <c r="S26" s="68"/>
+      <c r="T26" s="68"/>
+      <c r="U26" s="68"/>
+      <c r="V26" s="68"/>
+      <c r="W26" s="68"/>
+      <c r="X26" s="68"/>
+      <c r="Y26" s="68"/>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A27" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="S26" s="7"/>
-      <c r="T26" s="7"/>
-      <c r="U26" s="7"/>
-      <c r="V26" s="8"/>
-      <c r="W26" s="8" t="s">
+      <c r="B27" s="38"/>
+      <c r="C27" s="30"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="8"/>
+      <c r="N27" s="8"/>
+      <c r="O27" s="8"/>
+      <c r="P27" s="8"/>
+      <c r="Q27" s="8"/>
+      <c r="R27" s="8"/>
+      <c r="S27" s="38"/>
+      <c r="T27" s="38"/>
+      <c r="U27" s="38"/>
+      <c r="V27" s="8"/>
+      <c r="W27" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="X26" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="Y26" s="8"/>
-    </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A27" s="50" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B29" s="7" t="s">
-        <v>166</v>
+      <c r="X27" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="Y27" s="8"/>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A28" s="49" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="B30" s="7" t="s">
+        <v>165</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A1:Y1"/>
-    <mergeCell ref="A2:Y2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="G3:O3"/>
-    <mergeCell ref="S3:Y3"/>
-    <mergeCell ref="A25:Y25"/>
+    <mergeCell ref="A26:Y26"/>
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="L4:M4"/>
@@ -8197,7 +8376,12 @@
     <mergeCell ref="T4:U4"/>
     <mergeCell ref="V4:W4"/>
     <mergeCell ref="A7:Y7"/>
-    <mergeCell ref="A17:Y17"/>
+    <mergeCell ref="A18:Y18"/>
+    <mergeCell ref="A1:Y1"/>
+    <mergeCell ref="A2:Y2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="G3:O3"/>
+    <mergeCell ref="S3:Y3"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.1875" right="0.31496062992125984" top="0.35433070866141736" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
